--- a/Consolidado_Bridge_2026.xlsx
+++ b/Consolidado_Bridge_2026.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08d87aadaabdc2cb/Desktop/BRIDGE/consolidado/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08d87aadaabdc2cb/Documentos/nwb/bridge/dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="837" documentId="8_{C607EACA-C650-4A5E-95C7-07DDA7668303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4406A480-FF8E-4C7E-8C64-649F283E12E9}"/>
+  <xr:revisionPtr revIDLastSave="838" documentId="8_{C607EACA-C650-4A5E-95C7-07DDA7668303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE72869-470E-40DC-A65E-4CFAF38599A7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEFB68E0-0739-433A-A945-0FEA615287DD}"/>
   </bookViews>
   <sheets>
-    <sheet name="2025 Consolidado" sheetId="1" r:id="rId1"/>
+    <sheet name="2026 Consolidado" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025 Consolidado'!$A$1:$P$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026 Consolidado'!$A$1:$P$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -945,10 +945,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Consolidado_Bridge_2026.xlsx
+++ b/Consolidado_Bridge_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08d87aadaabdc2cb/Documentos/nwb/bridge/dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="838" documentId="8_{C607EACA-C650-4A5E-95C7-07DDA7668303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE72869-470E-40DC-A65E-4CFAF38599A7}"/>
+  <xr:revisionPtr revIDLastSave="867" documentId="8_{C607EACA-C650-4A5E-95C7-07DDA7668303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E49C948F-4BC3-4AEC-8649-E5672CE4553E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEFB68E0-0739-433A-A945-0FEA615287DD}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2026 Consolidado" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026 Consolidado'!$A$1:$P$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026 Consolidado'!$A$1:$P$158</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="515">
   <si>
     <t>Quando</t>
   </si>
@@ -858,6 +858,732 @@
   </si>
   <si>
     <t>21 99396-7979</t>
+  </si>
+  <si>
+    <t>01/02/2026</t>
+  </si>
+  <si>
+    <t>Rafael Souza De Oliveira</t>
+  </si>
+  <si>
+    <t>21 96527-9376</t>
+  </si>
+  <si>
+    <t>Enviei mensagem via WhatsApp</t>
+  </si>
+  <si>
+    <t>Pedro Luca</t>
+  </si>
+  <si>
+    <t>Grajau</t>
+  </si>
+  <si>
+    <t>21 97278-5556</t>
+  </si>
+  <si>
+    <t>Sim, por efusão</t>
+  </si>
+  <si>
+    <t>Matheus Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barra Da Tijuca </t>
+  </si>
+  <si>
+    <t>21 99470-2727</t>
+  </si>
+  <si>
+    <t>Samuel Mendes</t>
+  </si>
+  <si>
+    <t>Duque De Caxias / RJ</t>
+  </si>
+  <si>
+    <t>21 96656-1113</t>
+  </si>
+  <si>
+    <t>Andre Castelo Branco</t>
+  </si>
+  <si>
+    <t>21 99623-8386</t>
+  </si>
+  <si>
+    <t>Sim, por aspersão</t>
+  </si>
+  <si>
+    <t>Ray Siqueira De Oliveira</t>
+  </si>
+  <si>
+    <t>21 97470-2220</t>
+  </si>
+  <si>
+    <t>Alex Nina</t>
+  </si>
+  <si>
+    <t>98 98544-4137</t>
+  </si>
+  <si>
+    <t>07/02/2026</t>
+  </si>
+  <si>
+    <t>Caio Dos Santos Araújo</t>
+  </si>
+  <si>
+    <t>21 96403-7407</t>
+  </si>
+  <si>
+    <t>Luana Silva Do Amaral</t>
+  </si>
+  <si>
+    <t>21 96768-8179</t>
+  </si>
+  <si>
+    <t>Encaminhada ao GC copacabana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristiane Mariano </t>
+  </si>
+  <si>
+    <t>Decianne Ester Medeiros Azevedo</t>
+  </si>
+  <si>
+    <t>21 99116-0600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enviada mensagem </t>
+  </si>
+  <si>
+    <t xml:space="preserve">não </t>
+  </si>
+  <si>
+    <t>Carolina Costa Nicoliello</t>
+  </si>
+  <si>
+    <t>22 99977-3485</t>
+  </si>
+  <si>
+    <t>Lidiane Benica</t>
+  </si>
+  <si>
+    <t>Grajaú</t>
+  </si>
+  <si>
+    <t>21 96961-8749</t>
+  </si>
+  <si>
+    <t>Encaminhada para Rajana</t>
+  </si>
+  <si>
+    <t>Fernanda Ferreira Fernandes</t>
+  </si>
+  <si>
+    <t>21 99777-2413</t>
+  </si>
+  <si>
+    <t>ângela Beatriz Mendes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duque De Caxias </t>
+  </si>
+  <si>
+    <t>21 99201-9094</t>
+  </si>
+  <si>
+    <t>Monique Amorim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lagoa </t>
+  </si>
+  <si>
+    <t>21 98203-7888</t>
+  </si>
+  <si>
+    <t>Tentando encaminhar ao GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silvana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leblon </t>
+  </si>
+  <si>
+    <t>21 98221-5290</t>
+  </si>
+  <si>
+    <t>Isabela Magalhães Prates</t>
+  </si>
+  <si>
+    <t>Maracanã</t>
+  </si>
+  <si>
+    <t>21 98115-7251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encaminhada para Jenaina </t>
+  </si>
+  <si>
+    <t>sim</t>
+  </si>
+  <si>
+    <t>Julia Loja</t>
+  </si>
+  <si>
+    <t>21 98109-9992</t>
+  </si>
+  <si>
+    <t>Thalita Cutrim</t>
+  </si>
+  <si>
+    <t>98 98437-9096</t>
+  </si>
+  <si>
+    <t>Encaminhada para o GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cida Salles </t>
+  </si>
+  <si>
+    <t>Ana Luísa</t>
+  </si>
+  <si>
+    <t>21 99683-7161</t>
+  </si>
+  <si>
+    <t>Adrielly Lorena</t>
+  </si>
+  <si>
+    <t>91 98455-8323</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
+    <t>Letícia Nogueira Barreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gávea </t>
+  </si>
+  <si>
+    <t>21 98285-9289</t>
+  </si>
+  <si>
+    <t>Jacqueline Castro Cordeiro</t>
+  </si>
+  <si>
+    <t>21 97283-0728</t>
+  </si>
+  <si>
+    <t>08/02/2026</t>
+  </si>
+  <si>
+    <t>Joao Vitor</t>
+  </si>
+  <si>
+    <t>21 98872-9388</t>
+  </si>
+  <si>
+    <t>Enviei Mensagem Via WhatsApp</t>
+  </si>
+  <si>
+    <t>David De Oliveira Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tijuca </t>
+  </si>
+  <si>
+    <t>21 97679-1234</t>
+  </si>
+  <si>
+    <t>João Luiz Da Silva Leal Júnior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lins </t>
+  </si>
+  <si>
+    <t>21 99406-1140</t>
+  </si>
+  <si>
+    <t>Guilherme Miliosi</t>
+  </si>
+  <si>
+    <t>Icaraí</t>
+  </si>
+  <si>
+    <t>Niterói / RJ</t>
+  </si>
+  <si>
+    <t>21 99205-8563</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>culto</t>
+  </si>
+  <si>
+    <t>Juan Fernandes Deodato Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rio Comprido </t>
+  </si>
+  <si>
+    <t>21 99337-6279</t>
+  </si>
+  <si>
+    <t>Piers Penfold</t>
+  </si>
+  <si>
+    <t>21 99686-1661</t>
+  </si>
+  <si>
+    <t>Gabriela Amorim</t>
+  </si>
+  <si>
+    <t>21 96849-1455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle Mariano </t>
+  </si>
+  <si>
+    <t>Manuela Rosa</t>
+  </si>
+  <si>
+    <t>21 99843-7396</t>
+  </si>
+  <si>
+    <t>Monica De Oliveira</t>
+  </si>
+  <si>
+    <t>21 97045-2309</t>
+  </si>
+  <si>
+    <t>Não quer ir ao gc no momento</t>
+  </si>
+  <si>
+    <t>Quelen Nunes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nossa Senhora De Lurdes </t>
+  </si>
+  <si>
+    <t>Santa Maria  / --</t>
+  </si>
+  <si>
+    <t>21 96966-3705</t>
+  </si>
+  <si>
+    <t>Raimunda Do Carmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lins De Vasconcelos </t>
+  </si>
+  <si>
+    <t>21 9922-3616</t>
+  </si>
+  <si>
+    <t>Encaminhada para o gc Tijuca 2</t>
+  </si>
+  <si>
+    <t>Kamilly Victoria Motta Chaves De Oliveira</t>
+  </si>
+  <si>
+    <t>21 99424-5390</t>
+  </si>
+  <si>
+    <t>Scarlet Vieira Sack</t>
+  </si>
+  <si>
+    <t>69 99204-4092</t>
+  </si>
+  <si>
+    <t>Carolina Magdaleno</t>
+  </si>
+  <si>
+    <t>21 99636-0621</t>
+  </si>
+  <si>
+    <t>Gisela Carvalho</t>
+  </si>
+  <si>
+    <t>União Estável</t>
+  </si>
+  <si>
+    <t>21 99134-0729</t>
+  </si>
+  <si>
+    <t>Juliana Vieira Gomea</t>
+  </si>
+  <si>
+    <t>21 9299-8050</t>
+  </si>
+  <si>
+    <t>Geovana Rodrigues</t>
+  </si>
+  <si>
+    <t>21 96551-1156</t>
+  </si>
+  <si>
+    <t>Paloma Nascimento Alves</t>
+  </si>
+  <si>
+    <t>21 97591-5476</t>
+  </si>
+  <si>
+    <t>Camily Lima</t>
+  </si>
+  <si>
+    <t>21 96657-7162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero errado </t>
+  </si>
+  <si>
+    <t>Dayana Melo Sampaio</t>
+  </si>
+  <si>
+    <t>21 98144-7994</t>
+  </si>
+  <si>
+    <t>15/02/2026</t>
+  </si>
+  <si>
+    <t>Douglas Figueiredo Dos Santos</t>
+  </si>
+  <si>
+    <t>Alvarez</t>
+  </si>
+  <si>
+    <t>Nova Iguaçu / RJ</t>
+  </si>
+  <si>
+    <t>21 97059-3330</t>
+  </si>
+  <si>
+    <t>Enviei Mensagem via WhatsApp</t>
+  </si>
+  <si>
+    <t>culto - domingo</t>
+  </si>
+  <si>
+    <t>Fellype Gabriel Gomes Medina</t>
+  </si>
+  <si>
+    <t>Leme</t>
+  </si>
+  <si>
+    <t>21 21974-5795</t>
+  </si>
+  <si>
+    <t>Telefone errado</t>
+  </si>
+  <si>
+    <t>Neuza Maria Inácio</t>
+  </si>
+  <si>
+    <t>21 96527-4066</t>
+  </si>
+  <si>
+    <t>Zulmira</t>
+  </si>
+  <si>
+    <t>Francisca Liliane</t>
+  </si>
+  <si>
+    <t>21 96684-6429</t>
+  </si>
+  <si>
+    <t>Não sou batizado</t>
+  </si>
+  <si>
+    <t>Caroline Inácio Gomes</t>
+  </si>
+  <si>
+    <t>21 99978-7788</t>
+  </si>
+  <si>
+    <t>Alda Cavalcante</t>
+  </si>
+  <si>
+    <t>21 96530-7627</t>
+  </si>
+  <si>
+    <t>22/02/2026</t>
+  </si>
+  <si>
+    <t>Matheus Pereira</t>
+  </si>
+  <si>
+    <t>21 98455-5031</t>
+  </si>
+  <si>
+    <t>Envien mensagem via WhatsApp</t>
+  </si>
+  <si>
+    <t>Pablo César Teixeira Nascimento</t>
+  </si>
+  <si>
+    <t>21 99721-4014</t>
+  </si>
+  <si>
+    <t>Ronaldo Bastos</t>
+  </si>
+  <si>
+    <t>São Conrado</t>
+  </si>
+  <si>
+    <t>21 98521-6042</t>
+  </si>
+  <si>
+    <t>José Gabriel Brum Armas</t>
+  </si>
+  <si>
+    <t>21 9950-6550</t>
+  </si>
+  <si>
+    <t>Francisco Arruda</t>
+  </si>
+  <si>
+    <t>21 99911-0120</t>
+  </si>
+  <si>
+    <t>William De Azevedo</t>
+  </si>
+  <si>
+    <t>21 98464-8178</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>Leandro Nunes Falcao</t>
+  </si>
+  <si>
+    <t>21 98760-5450</t>
+  </si>
+  <si>
+    <t>Raphael Fernandes</t>
+  </si>
+  <si>
+    <t>Santa Teresa</t>
+  </si>
+  <si>
+    <t>21 98428-4013</t>
+  </si>
+  <si>
+    <t>Loruama Dos Santos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Paula </t>
+  </si>
+  <si>
+    <t>Niterói  / --</t>
+  </si>
+  <si>
+    <t>21 99167-9588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encaminhada para gc em niteroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricia Vieira </t>
+  </si>
+  <si>
+    <t>Joice Gonçalves Da Silva</t>
+  </si>
+  <si>
+    <t>21 98197-7353</t>
+  </si>
+  <si>
+    <t>Encaminhada para o GC Pink Leblon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adriane </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estácio </t>
+  </si>
+  <si>
+    <t>21 98316-3835</t>
+  </si>
+  <si>
+    <t>Enviada mensagem</t>
+  </si>
+  <si>
+    <t>Ozana Schuindt</t>
+  </si>
+  <si>
+    <t>Rio De Janeirob / --</t>
+  </si>
+  <si>
+    <t>21 96697-6517</t>
+  </si>
+  <si>
+    <t>Livia Coelho De Souza</t>
+  </si>
+  <si>
+    <t>21 97458-5849</t>
+  </si>
+  <si>
+    <t>Suely Alves</t>
+  </si>
+  <si>
+    <t>Taquara</t>
+  </si>
+  <si>
+    <t>21 98846-4489</t>
+  </si>
+  <si>
+    <t>Está no ao gc barrinha</t>
+  </si>
+  <si>
+    <t>Débora Costa</t>
+  </si>
+  <si>
+    <t>21 97132-1117</t>
+  </si>
+  <si>
+    <t>Ana Gonçalves</t>
+  </si>
+  <si>
+    <t>21 98107-3770</t>
+  </si>
+  <si>
+    <t>Tentando emcaminhar ao GC</t>
+  </si>
+  <si>
+    <t>Jeniffer Pinheiro</t>
+  </si>
+  <si>
+    <t>21 96720-4473</t>
+  </si>
+  <si>
+    <t>Lara Tarsila</t>
+  </si>
+  <si>
+    <t>Santo Cristo</t>
+  </si>
+  <si>
+    <t>21 99423-9889</t>
+  </si>
+  <si>
+    <t>Mayara Kerolem Divino Balbino</t>
+  </si>
+  <si>
+    <t>35 99955-0961</t>
+  </si>
+  <si>
+    <t>Ana Queiros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardim </t>
+  </si>
+  <si>
+    <t>21 99349-6446</t>
+  </si>
+  <si>
+    <t>Maria Vitória Agostinho</t>
+  </si>
+  <si>
+    <t>55 9960-9306</t>
+  </si>
+  <si>
+    <t>Andressa Ramos</t>
+  </si>
+  <si>
+    <t>21 98292-2277</t>
+  </si>
+  <si>
+    <t>Suzane Xavier</t>
+  </si>
+  <si>
+    <t>21 97282-5651</t>
+  </si>
+  <si>
+    <t>Andrea Alves De Azevedo</t>
+  </si>
+  <si>
+    <t>21 98812-7878</t>
+  </si>
+  <si>
+    <t>Tatiana Teles Da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Cristo </t>
+  </si>
+  <si>
+    <t>21 99968-3775</t>
+  </si>
+  <si>
+    <t>é de outra igreja</t>
+  </si>
+  <si>
+    <t>Eliedna Duarte</t>
+  </si>
+  <si>
+    <t>Avenida Pavaozinho 11</t>
+  </si>
+  <si>
+    <t>21 99402-5101</t>
+  </si>
+  <si>
+    <t>Indo ao 27+</t>
+  </si>
+  <si>
+    <t>Alexia Batista De Oliveira</t>
+  </si>
+  <si>
+    <t>21 97250-2369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encaminhada ao gc maes </t>
+  </si>
+  <si>
+    <t>Luanda Rodrigues</t>
+  </si>
+  <si>
+    <t>24 98182-5643</t>
+  </si>
+  <si>
+    <t>Encaminhada ao gc</t>
+  </si>
+  <si>
+    <t>Ana Paula</t>
+  </si>
+  <si>
+    <t>24 99983-2797</t>
+  </si>
+  <si>
+    <t>Encaminhada ao 27+</t>
+  </si>
+  <si>
+    <t>Claudia Silva</t>
+  </si>
+  <si>
+    <t>21 96961-4138</t>
+  </si>
+  <si>
+    <t>Luciene Lourenço</t>
+  </si>
+  <si>
+    <t>31 98589-0248</t>
+  </si>
+  <si>
+    <t>Mariana De Paiva Moura Ferreira</t>
+  </si>
+  <si>
+    <t>Andaraí</t>
+  </si>
+  <si>
+    <t>21 99819-9356</t>
+  </si>
+  <si>
+    <t>Camille Da Silva</t>
+  </si>
+  <si>
+    <t>21 96806-9685</t>
+  </si>
+  <si>
+    <t>Encaminhada ao Nexteen</t>
   </si>
 </sst>
 </file>
@@ -945,6 +1671,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5086,142 +5816,4111 @@
         <v>64</v>
       </c>
     </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D102" s="4"/>
-    </row>
-    <row r="118" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D118" s="4"/>
-    </row>
-    <row r="128" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M128" s="1"/>
-      <c r="N128"/>
-    </row>
-    <row r="129" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M129" s="1"/>
-      <c r="N129"/>
-    </row>
-    <row r="130" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M130" s="1"/>
-      <c r="N130"/>
-    </row>
-    <row r="131" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M131" s="1"/>
-      <c r="N131"/>
-    </row>
-    <row r="132" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M132" s="1"/>
-      <c r="N132"/>
-    </row>
-    <row r="133" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M133" s="1"/>
-      <c r="N133"/>
-    </row>
-    <row r="134" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M134" s="1"/>
-      <c r="N134"/>
-    </row>
-    <row r="135" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M135" s="1"/>
-      <c r="N135"/>
-    </row>
-    <row r="136" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M136" s="1"/>
-      <c r="N136"/>
-    </row>
-    <row r="137" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M137" s="1"/>
-      <c r="N137"/>
-    </row>
-    <row r="138" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M138" s="1"/>
-      <c r="N138"/>
-    </row>
-    <row r="139" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M139" s="1"/>
-      <c r="N139"/>
-    </row>
-    <row r="140" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M140" s="1"/>
-      <c r="N140"/>
-    </row>
-    <row r="141" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M141" s="1"/>
-      <c r="N141"/>
-    </row>
-    <row r="142" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M142" s="1"/>
-      <c r="N142"/>
-    </row>
-    <row r="143" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M143" s="1"/>
-      <c r="N143"/>
-    </row>
-    <row r="144" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M144" s="1"/>
-      <c r="N144"/>
-    </row>
-    <row r="145" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D145" s="4"/>
-      <c r="M145" s="1"/>
-      <c r="N145"/>
-    </row>
-    <row r="146" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M146" s="1"/>
-      <c r="N146"/>
-    </row>
-    <row r="147" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M147" s="1"/>
-      <c r="N147"/>
-    </row>
-    <row r="148" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M148" s="1"/>
-      <c r="N148"/>
-    </row>
-    <row r="149" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M149" s="1"/>
-      <c r="N149"/>
-    </row>
-    <row r="150" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M150" s="1"/>
-      <c r="N150"/>
-    </row>
-    <row r="151" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M151" s="1"/>
-      <c r="N151"/>
-    </row>
-    <row r="152" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M152" s="1"/>
-      <c r="N152"/>
-    </row>
-    <row r="153" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M153" s="1"/>
-      <c r="N153"/>
-    </row>
-    <row r="154" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M154" s="1"/>
-      <c r="N154"/>
-    </row>
-    <row r="155" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M155" s="1"/>
-      <c r="N155"/>
-    </row>
-    <row r="156" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M156" s="1"/>
-      <c r="N156"/>
-    </row>
-    <row r="157" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M157" s="1"/>
-      <c r="N157"/>
-    </row>
-    <row r="158" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="M158" s="1"/>
-      <c r="N158"/>
-    </row>
-    <row r="159" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>273</v>
+      </c>
+      <c r="B77" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" t="s">
+        <v>274</v>
+      </c>
+      <c r="E77" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" t="s">
+        <v>45</v>
+      </c>
+      <c r="G77">
+        <v>29</v>
+      </c>
+      <c r="H77" t="s">
+        <v>36</v>
+      </c>
+      <c r="I77" t="s">
+        <v>33</v>
+      </c>
+      <c r="J77" t="s">
+        <v>275</v>
+      </c>
+      <c r="K77" t="s">
+        <v>25</v>
+      </c>
+      <c r="L77" t="s">
+        <v>81</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N77" t="s">
+        <v>276</v>
+      </c>
+      <c r="O77" t="s">
+        <v>28</v>
+      </c>
+      <c r="P77" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>273</v>
+      </c>
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" t="s">
+        <v>277</v>
+      </c>
+      <c r="E78" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" t="s">
+        <v>45</v>
+      </c>
+      <c r="G78">
+        <v>30</v>
+      </c>
+      <c r="H78" t="s">
+        <v>278</v>
+      </c>
+      <c r="I78" t="s">
+        <v>179</v>
+      </c>
+      <c r="J78" t="s">
+        <v>279</v>
+      </c>
+      <c r="K78" t="s">
+        <v>25</v>
+      </c>
+      <c r="L78" t="s">
+        <v>81</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="N78" t="s">
+        <v>276</v>
+      </c>
+      <c r="O78" t="s">
+        <v>25</v>
+      </c>
+      <c r="P78" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" t="s">
+        <v>281</v>
+      </c>
+      <c r="E79" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" t="s">
+        <v>45</v>
+      </c>
+      <c r="G79">
+        <v>30</v>
+      </c>
+      <c r="H79" t="s">
+        <v>282</v>
+      </c>
+      <c r="I79" t="s">
+        <v>89</v>
+      </c>
+      <c r="J79" t="s">
+        <v>283</v>
+      </c>
+      <c r="K79" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79" t="s">
+        <v>276</v>
+      </c>
+      <c r="O79" t="s">
+        <v>25</v>
+      </c>
+      <c r="P79" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>273</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" t="s">
+        <v>284</v>
+      </c>
+      <c r="E80" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" t="s">
+        <v>31</v>
+      </c>
+      <c r="G80">
+        <v>35</v>
+      </c>
+      <c r="H80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80" t="s">
+        <v>285</v>
+      </c>
+      <c r="J80" t="s">
+        <v>286</v>
+      </c>
+      <c r="K80" t="s">
+        <v>25</v>
+      </c>
+      <c r="L80" t="s">
+        <v>81</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N80" t="s">
+        <v>276</v>
+      </c>
+      <c r="O80" t="s">
+        <v>28</v>
+      </c>
+      <c r="P80" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>273</v>
+      </c>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" t="s">
+        <v>287</v>
+      </c>
+      <c r="E81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81">
+        <v>61</v>
+      </c>
+      <c r="H81" t="s">
+        <v>40</v>
+      </c>
+      <c r="I81" t="s">
+        <v>33</v>
+      </c>
+      <c r="J81" t="s">
+        <v>288</v>
+      </c>
+      <c r="K81" t="s">
+        <v>25</v>
+      </c>
+      <c r="L81" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="N81" t="s">
+        <v>276</v>
+      </c>
+      <c r="O81" t="s">
+        <v>28</v>
+      </c>
+      <c r="P81" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>273</v>
+      </c>
+      <c r="B82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" t="s">
+        <v>290</v>
+      </c>
+      <c r="E82" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" t="s">
+        <v>45</v>
+      </c>
+      <c r="G82">
+        <v>17</v>
+      </c>
+      <c r="H82" t="s">
+        <v>36</v>
+      </c>
+      <c r="I82" t="s">
+        <v>93</v>
+      </c>
+      <c r="J82" t="s">
+        <v>291</v>
+      </c>
+      <c r="K82" t="s">
+        <v>25</v>
+      </c>
+      <c r="L82" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82" t="s">
+        <v>276</v>
+      </c>
+      <c r="O82" t="s">
+        <v>28</v>
+      </c>
+      <c r="P82" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>273</v>
+      </c>
+      <c r="B83" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" t="s">
+        <v>38</v>
+      </c>
+      <c r="D83" t="s">
+        <v>292</v>
+      </c>
+      <c r="E83" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" t="s">
+        <v>45</v>
+      </c>
+      <c r="G83">
+        <v>30</v>
+      </c>
+      <c r="H83" t="s">
+        <v>115</v>
+      </c>
+      <c r="I83" t="s">
+        <v>179</v>
+      </c>
+      <c r="J83" t="s">
+        <v>293</v>
+      </c>
+      <c r="K83" t="s">
+        <v>25</v>
+      </c>
+      <c r="L83" t="s">
+        <v>81</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N83" t="s">
+        <v>276</v>
+      </c>
+      <c r="O83" t="s">
+        <v>28</v>
+      </c>
+      <c r="P83" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>294</v>
+      </c>
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" t="s">
+        <v>295</v>
+      </c>
+      <c r="E84" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" t="s">
+        <v>45</v>
+      </c>
+      <c r="G84">
+        <v>18</v>
+      </c>
+      <c r="H84" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84" t="s">
+        <v>54</v>
+      </c>
+      <c r="J84" t="s">
+        <v>296</v>
+      </c>
+      <c r="K84" t="s">
+        <v>25</v>
+      </c>
+      <c r="L84" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="N84" t="s">
+        <v>276</v>
+      </c>
+      <c r="O84" t="s">
+        <v>25</v>
+      </c>
+      <c r="P84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>273</v>
+      </c>
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" t="s">
+        <v>297</v>
+      </c>
+      <c r="E85" t="s">
+        <v>60</v>
+      </c>
+      <c r="F85" t="s">
+        <v>21</v>
+      </c>
+      <c r="G85">
+        <v>33</v>
+      </c>
+      <c r="H85" t="s">
+        <v>92</v>
+      </c>
+      <c r="I85" t="s">
+        <v>33</v>
+      </c>
+      <c r="J85" t="s">
+        <v>298</v>
+      </c>
+      <c r="K85" t="s">
+        <v>25</v>
+      </c>
+      <c r="L85" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N85" t="s">
+        <v>299</v>
+      </c>
+      <c r="O85" t="s">
+        <v>25</v>
+      </c>
+      <c r="P85" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>273</v>
+      </c>
+      <c r="B86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" t="s">
+        <v>301</v>
+      </c>
+      <c r="E86" t="s">
+        <v>60</v>
+      </c>
+      <c r="F86" t="s">
+        <v>45</v>
+      </c>
+      <c r="G86">
+        <v>28</v>
+      </c>
+      <c r="H86" t="s">
+        <v>57</v>
+      </c>
+      <c r="I86" t="s">
+        <v>33</v>
+      </c>
+      <c r="J86" t="s">
+        <v>302</v>
+      </c>
+      <c r="K86" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" t="s">
+        <v>75</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N86" t="s">
+        <v>303</v>
+      </c>
+      <c r="O86" t="s">
+        <v>304</v>
+      </c>
+      <c r="P86" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>273</v>
+      </c>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" t="s">
+        <v>305</v>
+      </c>
+      <c r="E87" t="s">
+        <v>60</v>
+      </c>
+      <c r="F87" t="s">
+        <v>45</v>
+      </c>
+      <c r="G87">
+        <v>30</v>
+      </c>
+      <c r="H87" t="s">
+        <v>36</v>
+      </c>
+      <c r="I87" t="s">
+        <v>33</v>
+      </c>
+      <c r="J87" t="s">
+        <v>306</v>
+      </c>
+      <c r="K87" t="s">
+        <v>25</v>
+      </c>
+      <c r="L87" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" t="s">
+        <v>303</v>
+      </c>
+      <c r="O87" t="s">
+        <v>304</v>
+      </c>
+      <c r="P87" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>273</v>
+      </c>
+      <c r="B88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" t="s">
+        <v>38</v>
+      </c>
+      <c r="D88" t="s">
+        <v>307</v>
+      </c>
+      <c r="E88" t="s">
+        <v>60</v>
+      </c>
+      <c r="F88" t="s">
+        <v>31</v>
+      </c>
+      <c r="G88">
+        <v>44</v>
+      </c>
+      <c r="H88" t="s">
+        <v>308</v>
+      </c>
+      <c r="I88" t="s">
+        <v>33</v>
+      </c>
+      <c r="J88" t="s">
+        <v>309</v>
+      </c>
+      <c r="K88" t="s">
+        <v>25</v>
+      </c>
+      <c r="L88" t="s">
+        <v>167</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N88" t="s">
+        <v>310</v>
+      </c>
+      <c r="O88" t="s">
+        <v>25</v>
+      </c>
+      <c r="P88" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>273</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" t="s">
+        <v>311</v>
+      </c>
+      <c r="E89" t="s">
+        <v>60</v>
+      </c>
+      <c r="F89" t="s">
+        <v>21</v>
+      </c>
+      <c r="G89">
+        <v>35</v>
+      </c>
+      <c r="H89" t="s">
+        <v>207</v>
+      </c>
+      <c r="I89" t="s">
+        <v>33</v>
+      </c>
+      <c r="J89" t="s">
+        <v>312</v>
+      </c>
+      <c r="K89" t="s">
+        <v>25</v>
+      </c>
+      <c r="L89" t="s">
+        <v>75</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>303</v>
+      </c>
+      <c r="O89" t="s">
+        <v>304</v>
+      </c>
+      <c r="P89" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>273</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" t="s">
+        <v>38</v>
+      </c>
+      <c r="D90" t="s">
+        <v>313</v>
+      </c>
+      <c r="E90" t="s">
+        <v>60</v>
+      </c>
+      <c r="F90" t="s">
+        <v>31</v>
+      </c>
+      <c r="G90">
+        <v>30</v>
+      </c>
+      <c r="H90" t="s">
+        <v>314</v>
+      </c>
+      <c r="I90" t="s">
+        <v>158</v>
+      </c>
+      <c r="J90" t="s">
+        <v>315</v>
+      </c>
+      <c r="K90" t="s">
+        <v>25</v>
+      </c>
+      <c r="L90" t="s">
+        <v>81</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N90" t="s">
+        <v>303</v>
+      </c>
+      <c r="O90" t="s">
+        <v>137</v>
+      </c>
+      <c r="P90" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>273</v>
+      </c>
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" t="s">
+        <v>38</v>
+      </c>
+      <c r="D91" t="s">
+        <v>316</v>
+      </c>
+      <c r="E91" t="s">
+        <v>60</v>
+      </c>
+      <c r="F91" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91">
+        <v>45</v>
+      </c>
+      <c r="H91" t="s">
+        <v>317</v>
+      </c>
+      <c r="I91" t="s">
+        <v>256</v>
+      </c>
+      <c r="J91" t="s">
+        <v>318</v>
+      </c>
+      <c r="K91" t="s">
+        <v>25</v>
+      </c>
+      <c r="L91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N91" t="s">
+        <v>319</v>
+      </c>
+      <c r="O91" t="s">
+        <v>172</v>
+      </c>
+      <c r="P91" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>273</v>
+      </c>
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>38</v>
+      </c>
+      <c r="D92" t="s">
+        <v>320</v>
+      </c>
+      <c r="E92" t="s">
+        <v>60</v>
+      </c>
+      <c r="F92" t="s">
+        <v>31</v>
+      </c>
+      <c r="G92">
+        <v>39</v>
+      </c>
+      <c r="H92" t="s">
+        <v>321</v>
+      </c>
+      <c r="I92" t="s">
+        <v>158</v>
+      </c>
+      <c r="J92" t="s">
+        <v>322</v>
+      </c>
+      <c r="K92" t="s">
+        <v>25</v>
+      </c>
+      <c r="L92" t="s">
+        <v>26</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N92" t="s">
+        <v>303</v>
+      </c>
+      <c r="O92" t="s">
+        <v>137</v>
+      </c>
+      <c r="P92" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>273</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>38</v>
+      </c>
+      <c r="D93" t="s">
+        <v>323</v>
+      </c>
+      <c r="E93" t="s">
+        <v>60</v>
+      </c>
+      <c r="F93" t="s">
+        <v>45</v>
+      </c>
+      <c r="G93">
+        <v>33</v>
+      </c>
+      <c r="H93" t="s">
+        <v>324</v>
+      </c>
+      <c r="I93" t="s">
+        <v>33</v>
+      </c>
+      <c r="J93" t="s">
+        <v>325</v>
+      </c>
+      <c r="K93" t="s">
+        <v>25</v>
+      </c>
+      <c r="L93" t="s">
+        <v>75</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N93" t="s">
+        <v>326</v>
+      </c>
+      <c r="O93" t="s">
+        <v>327</v>
+      </c>
+      <c r="P93" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>273</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" t="s">
+        <v>60</v>
+      </c>
+      <c r="F94" t="s">
+        <v>45</v>
+      </c>
+      <c r="G94">
+        <v>30</v>
+      </c>
+      <c r="H94" t="s">
+        <v>46</v>
+      </c>
+      <c r="I94" t="s">
+        <v>33</v>
+      </c>
+      <c r="J94" t="s">
+        <v>329</v>
+      </c>
+      <c r="K94" t="s">
+        <v>25</v>
+      </c>
+      <c r="L94" t="s">
+        <v>48</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N94" t="s">
+        <v>319</v>
+      </c>
+      <c r="O94" t="s">
+        <v>327</v>
+      </c>
+      <c r="P94" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>273</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" t="s">
+        <v>330</v>
+      </c>
+      <c r="E95" t="s">
+        <v>60</v>
+      </c>
+      <c r="F95" t="s">
+        <v>45</v>
+      </c>
+      <c r="G95">
+        <v>27</v>
+      </c>
+      <c r="H95" t="s">
+        <v>46</v>
+      </c>
+      <c r="I95" t="s">
+        <v>256</v>
+      </c>
+      <c r="J95" t="s">
+        <v>331</v>
+      </c>
+      <c r="K95" t="s">
+        <v>25</v>
+      </c>
+      <c r="L95" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N95" t="s">
+        <v>332</v>
+      </c>
+      <c r="O95" t="s">
+        <v>327</v>
+      </c>
+      <c r="P95" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>273</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>38</v>
+      </c>
+      <c r="D96" t="s">
+        <v>334</v>
+      </c>
+      <c r="E96" t="s">
+        <v>60</v>
+      </c>
+      <c r="F96" t="s">
+        <v>21</v>
+      </c>
+      <c r="G96">
+        <v>63</v>
+      </c>
+      <c r="H96" t="s">
+        <v>92</v>
+      </c>
+      <c r="I96" t="s">
+        <v>158</v>
+      </c>
+      <c r="J96" t="s">
+        <v>335</v>
+      </c>
+      <c r="K96" t="s">
+        <v>25</v>
+      </c>
+      <c r="L96" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N96" t="s">
+        <v>332</v>
+      </c>
+      <c r="O96" t="s">
+        <v>327</v>
+      </c>
+      <c r="P96" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>273</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>38</v>
+      </c>
+      <c r="D97" t="s">
+        <v>336</v>
+      </c>
+      <c r="E97" t="s">
+        <v>60</v>
+      </c>
+      <c r="F97" t="s">
+        <v>21</v>
+      </c>
+      <c r="G97">
+        <v>25</v>
+      </c>
+      <c r="H97" t="s">
+        <v>36</v>
+      </c>
+      <c r="I97" t="s">
+        <v>33</v>
+      </c>
+      <c r="J97" t="s">
+        <v>337</v>
+      </c>
+      <c r="K97" t="s">
+        <v>25</v>
+      </c>
+      <c r="L97" t="s">
+        <v>75</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="N97" t="s">
+        <v>332</v>
+      </c>
+      <c r="O97" t="s">
+        <v>327</v>
+      </c>
+      <c r="P97" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>338</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>38</v>
+      </c>
+      <c r="D98" t="s">
+        <v>339</v>
+      </c>
+      <c r="E98" t="s">
+        <v>60</v>
+      </c>
+      <c r="F98" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98">
+        <v>27</v>
+      </c>
+      <c r="H98" t="s">
+        <v>340</v>
+      </c>
+      <c r="I98" t="s">
+        <v>89</v>
+      </c>
+      <c r="J98" t="s">
+        <v>341</v>
+      </c>
+      <c r="K98" t="s">
+        <v>25</v>
+      </c>
+      <c r="L98" t="s">
+        <v>75</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N98" t="s">
+        <v>332</v>
+      </c>
+      <c r="O98" t="s">
+        <v>327</v>
+      </c>
+      <c r="P98" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>338</v>
+      </c>
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
+        <v>38</v>
+      </c>
+      <c r="D99" t="s">
+        <v>342</v>
+      </c>
+      <c r="E99" t="s">
+        <v>60</v>
+      </c>
+      <c r="F99" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99">
+        <v>40</v>
+      </c>
+      <c r="H99" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" t="s">
+        <v>54</v>
+      </c>
+      <c r="J99" t="s">
+        <v>343</v>
+      </c>
+      <c r="K99" t="s">
+        <v>25</v>
+      </c>
+      <c r="L99" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N99" t="s">
+        <v>332</v>
+      </c>
+      <c r="O99" t="s">
+        <v>327</v>
+      </c>
+      <c r="P99" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>344</v>
+      </c>
+      <c r="B100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" t="s">
+        <v>345</v>
+      </c>
+      <c r="E100" t="s">
+        <v>20</v>
+      </c>
+      <c r="F100" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s">
+        <v>33</v>
+      </c>
+      <c r="J100" t="s">
+        <v>346</v>
+      </c>
+      <c r="K100" t="s">
+        <v>25</v>
+      </c>
+      <c r="L100" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" t="s">
+        <v>347</v>
+      </c>
+      <c r="O100" t="s">
+        <v>28</v>
+      </c>
+      <c r="P100" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>344</v>
+      </c>
+      <c r="B101" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" t="s">
+        <v>38</v>
+      </c>
+      <c r="D101" t="s">
+        <v>348</v>
+      </c>
+      <c r="E101" t="s">
+        <v>20</v>
+      </c>
+      <c r="F101" t="s">
+        <v>31</v>
+      </c>
+      <c r="G101">
+        <v>30</v>
+      </c>
+      <c r="H101" t="s">
+        <v>349</v>
+      </c>
+      <c r="I101" t="s">
+        <v>54</v>
+      </c>
+      <c r="J101" t="s">
+        <v>350</v>
+      </c>
+      <c r="K101" t="s">
+        <v>25</v>
+      </c>
+      <c r="L101" t="s">
+        <v>26</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N101" t="s">
+        <v>347</v>
+      </c>
+      <c r="O101" t="s">
+        <v>25</v>
+      </c>
+      <c r="P101" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>344</v>
+      </c>
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D102" t="s">
+        <v>351</v>
+      </c>
+      <c r="E102" t="s">
+        <v>20</v>
+      </c>
+      <c r="F102" t="s">
+        <v>31</v>
+      </c>
+      <c r="G102">
+        <v>30</v>
+      </c>
+      <c r="H102" t="s">
+        <v>352</v>
+      </c>
+      <c r="I102" t="s">
+        <v>54</v>
+      </c>
+      <c r="J102" t="s">
+        <v>353</v>
+      </c>
+      <c r="K102" t="s">
+        <v>25</v>
+      </c>
+      <c r="L102" t="s">
+        <v>26</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N102" t="s">
+        <v>347</v>
+      </c>
+      <c r="O102" t="s">
+        <v>25</v>
+      </c>
+      <c r="P102" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>344</v>
+      </c>
+      <c r="B103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103" t="s">
+        <v>354</v>
+      </c>
+      <c r="E103" t="s">
+        <v>20</v>
+      </c>
+      <c r="F103" t="s">
+        <v>45</v>
+      </c>
+      <c r="G103">
+        <v>36</v>
+      </c>
+      <c r="H103" t="s">
+        <v>355</v>
+      </c>
+      <c r="I103" t="s">
+        <v>356</v>
+      </c>
+      <c r="J103" t="s">
+        <v>357</v>
+      </c>
+      <c r="K103" t="s">
+        <v>25</v>
+      </c>
+      <c r="L103" t="s">
+        <v>26</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N103" t="s">
+        <v>347</v>
+      </c>
+      <c r="O103" t="s">
+        <v>28</v>
+      </c>
+      <c r="P103" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>358</v>
+      </c>
+      <c r="B104" t="s">
+        <v>359</v>
+      </c>
+      <c r="C104" t="s">
+        <v>18</v>
+      </c>
+      <c r="D104" t="s">
+        <v>360</v>
+      </c>
+      <c r="E104" t="s">
+        <v>20</v>
+      </c>
+      <c r="F104" t="s">
+        <v>45</v>
+      </c>
+      <c r="G104">
+        <v>30</v>
+      </c>
+      <c r="H104" t="s">
+        <v>361</v>
+      </c>
+      <c r="I104" t="s">
+        <v>89</v>
+      </c>
+      <c r="J104" t="s">
+        <v>362</v>
+      </c>
+      <c r="K104" t="s">
+        <v>25</v>
+      </c>
+      <c r="L104" t="s">
+        <v>26</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" t="s">
+        <v>347</v>
+      </c>
+      <c r="O104" t="s">
+        <v>28</v>
+      </c>
+      <c r="P104" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>358</v>
+      </c>
+      <c r="B105" t="s">
+        <v>359</v>
+      </c>
+      <c r="C105" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" t="s">
+        <v>363</v>
+      </c>
+      <c r="E105" t="s">
+        <v>20</v>
+      </c>
+      <c r="F105" t="s">
+        <v>45</v>
+      </c>
+      <c r="G105">
+        <v>49</v>
+      </c>
+      <c r="H105" t="s">
+        <v>222</v>
+      </c>
+      <c r="I105" t="s">
+        <v>54</v>
+      </c>
+      <c r="J105" t="s">
+        <v>364</v>
+      </c>
+      <c r="K105" t="s">
+        <v>25</v>
+      </c>
+      <c r="L105" t="s">
+        <v>26</v>
+      </c>
+      <c r="M105" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" t="s">
+        <v>347</v>
+      </c>
+      <c r="O105" t="s">
+        <v>25</v>
+      </c>
+      <c r="P105" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>344</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>65</v>
+      </c>
+      <c r="D106" t="s">
+        <v>365</v>
+      </c>
+      <c r="E106" t="s">
+        <v>60</v>
+      </c>
+      <c r="F106" t="s">
+        <v>45</v>
+      </c>
+      <c r="G106">
+        <v>20</v>
+      </c>
+      <c r="H106" t="s">
+        <v>183</v>
+      </c>
+      <c r="I106" t="s">
+        <v>54</v>
+      </c>
+      <c r="J106" t="s">
+        <v>366</v>
+      </c>
+      <c r="K106" t="s">
+        <v>25</v>
+      </c>
+      <c r="L106" t="s">
+        <v>26</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N106" t="s">
+        <v>303</v>
+      </c>
+      <c r="O106" t="s">
+        <v>28</v>
+      </c>
+      <c r="P106" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>344</v>
+      </c>
+      <c r="B107" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" t="s">
+        <v>18</v>
+      </c>
+      <c r="D107" t="s">
+        <v>368</v>
+      </c>
+      <c r="E107" t="s">
+        <v>60</v>
+      </c>
+      <c r="F107" t="s">
+        <v>45</v>
+      </c>
+      <c r="G107">
+        <v>16</v>
+      </c>
+      <c r="H107" t="s">
+        <v>53</v>
+      </c>
+      <c r="I107" t="s">
+        <v>158</v>
+      </c>
+      <c r="J107" t="s">
+        <v>369</v>
+      </c>
+      <c r="K107" t="s">
+        <v>25</v>
+      </c>
+      <c r="L107" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" t="s">
+        <v>303</v>
+      </c>
+      <c r="O107" t="s">
+        <v>28</v>
+      </c>
+      <c r="P107" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>344</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>38</v>
+      </c>
+      <c r="D108" t="s">
+        <v>370</v>
+      </c>
+      <c r="E108" t="s">
+        <v>60</v>
+      </c>
+      <c r="F108" t="s">
+        <v>31</v>
+      </c>
+      <c r="G108">
+        <v>52</v>
+      </c>
+      <c r="H108" t="s">
+        <v>92</v>
+      </c>
+      <c r="I108" t="s">
+        <v>198</v>
+      </c>
+      <c r="J108" t="s">
+        <v>371</v>
+      </c>
+      <c r="K108" t="s">
+        <v>25</v>
+      </c>
+      <c r="L108" t="s">
+        <v>81</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N108" t="s">
+        <v>372</v>
+      </c>
+      <c r="O108" t="s">
+        <v>25</v>
+      </c>
+      <c r="P108" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>344</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" t="s">
+        <v>373</v>
+      </c>
+      <c r="E109" t="s">
+        <v>60</v>
+      </c>
+      <c r="F109" t="s">
+        <v>21</v>
+      </c>
+      <c r="G109">
+        <v>43</v>
+      </c>
+      <c r="H109" t="s">
+        <v>374</v>
+      </c>
+      <c r="I109" t="s">
+        <v>375</v>
+      </c>
+      <c r="J109" t="s">
+        <v>376</v>
+      </c>
+      <c r="K109" t="s">
+        <v>25</v>
+      </c>
+      <c r="L109" t="s">
+        <v>26</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>303</v>
+      </c>
+      <c r="O109" t="s">
+        <v>28</v>
+      </c>
+      <c r="P109" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>344</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
+        <v>38</v>
+      </c>
+      <c r="D110" t="s">
+        <v>377</v>
+      </c>
+      <c r="E110" t="s">
+        <v>60</v>
+      </c>
+      <c r="F110" t="s">
+        <v>31</v>
+      </c>
+      <c r="G110">
+        <v>47</v>
+      </c>
+      <c r="H110" t="s">
+        <v>378</v>
+      </c>
+      <c r="I110" t="s">
+        <v>198</v>
+      </c>
+      <c r="J110" t="s">
+        <v>379</v>
+      </c>
+      <c r="K110" t="s">
+        <v>25</v>
+      </c>
+      <c r="L110" t="s">
+        <v>26</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N110" t="s">
+        <v>380</v>
+      </c>
+      <c r="O110" t="s">
+        <v>25</v>
+      </c>
+      <c r="P110" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>344</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>18</v>
+      </c>
+      <c r="D111" t="s">
+        <v>381</v>
+      </c>
+      <c r="E111" t="s">
+        <v>60</v>
+      </c>
+      <c r="F111" t="s">
+        <v>45</v>
+      </c>
+      <c r="G111">
+        <v>30</v>
+      </c>
+      <c r="H111" t="s">
+        <v>92</v>
+      </c>
+      <c r="I111" t="s">
+        <v>54</v>
+      </c>
+      <c r="J111" t="s">
+        <v>382</v>
+      </c>
+      <c r="K111" t="s">
+        <v>25</v>
+      </c>
+      <c r="L111" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N111" t="s">
+        <v>319</v>
+      </c>
+      <c r="O111" t="s">
+        <v>25</v>
+      </c>
+      <c r="P111" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>344</v>
+      </c>
+      <c r="B112" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" t="s">
+        <v>38</v>
+      </c>
+      <c r="D112" t="s">
+        <v>383</v>
+      </c>
+      <c r="E112" t="s">
+        <v>60</v>
+      </c>
+      <c r="F112" t="s">
+        <v>45</v>
+      </c>
+      <c r="G112">
+        <v>44</v>
+      </c>
+      <c r="H112" t="s">
+        <v>102</v>
+      </c>
+      <c r="I112" t="s">
+        <v>33</v>
+      </c>
+      <c r="J112" t="s">
+        <v>384</v>
+      </c>
+      <c r="K112" t="s">
+        <v>25</v>
+      </c>
+      <c r="L112" t="s">
+        <v>251</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N112" t="s">
+        <v>303</v>
+      </c>
+      <c r="O112" t="s">
+        <v>28</v>
+      </c>
+      <c r="P112" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>344</v>
+      </c>
+      <c r="B113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" t="s">
+        <v>18</v>
+      </c>
+      <c r="D113" t="s">
+        <v>385</v>
+      </c>
+      <c r="E113" t="s">
+        <v>60</v>
+      </c>
+      <c r="F113" t="s">
+        <v>45</v>
+      </c>
+      <c r="G113">
+        <v>32</v>
+      </c>
+      <c r="H113" t="s">
+        <v>127</v>
+      </c>
+      <c r="I113" t="s">
+        <v>33</v>
+      </c>
+      <c r="J113" t="s">
+        <v>386</v>
+      </c>
+      <c r="K113" t="s">
+        <v>25</v>
+      </c>
+      <c r="L113" t="s">
+        <v>48</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" t="s">
+        <v>303</v>
+      </c>
+      <c r="O113" t="s">
+        <v>28</v>
+      </c>
+      <c r="P113" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>344</v>
+      </c>
+      <c r="B114" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" t="s">
+        <v>18</v>
+      </c>
+      <c r="D114" t="s">
+        <v>387</v>
+      </c>
+      <c r="E114" t="s">
+        <v>60</v>
+      </c>
+      <c r="F114" t="s">
+        <v>388</v>
+      </c>
+      <c r="G114">
+        <v>51</v>
+      </c>
+      <c r="H114" t="s">
+        <v>282</v>
+      </c>
+      <c r="I114" t="s">
+        <v>256</v>
+      </c>
+      <c r="J114" t="s">
+        <v>389</v>
+      </c>
+      <c r="K114" t="s">
+        <v>25</v>
+      </c>
+      <c r="L114" t="s">
+        <v>26</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N114" t="s">
+        <v>303</v>
+      </c>
+      <c r="O114" t="s">
+        <v>28</v>
+      </c>
+      <c r="P114" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>344</v>
+      </c>
+      <c r="B115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" t="s">
+        <v>65</v>
+      </c>
+      <c r="D115" t="s">
+        <v>390</v>
+      </c>
+      <c r="E115" t="s">
+        <v>60</v>
+      </c>
+      <c r="F115" t="s">
+        <v>21</v>
+      </c>
+      <c r="G115">
+        <v>42</v>
+      </c>
+      <c r="H115" t="s">
+        <v>36</v>
+      </c>
+      <c r="I115" t="s">
+        <v>33</v>
+      </c>
+      <c r="J115" t="s">
+        <v>391</v>
+      </c>
+      <c r="K115" t="s">
+        <v>25</v>
+      </c>
+      <c r="L115" t="s">
+        <v>48</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N115" t="s">
+        <v>303</v>
+      </c>
+      <c r="O115" t="s">
+        <v>28</v>
+      </c>
+      <c r="P115" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>358</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116" t="s">
+        <v>392</v>
+      </c>
+      <c r="E116" t="s">
+        <v>60</v>
+      </c>
+      <c r="F116" t="s">
+        <v>45</v>
+      </c>
+      <c r="G116">
+        <v>15</v>
+      </c>
+      <c r="H116" t="s">
+        <v>361</v>
+      </c>
+      <c r="I116" t="s">
+        <v>89</v>
+      </c>
+      <c r="J116" t="s">
+        <v>393</v>
+      </c>
+      <c r="K116" t="s">
+        <v>25</v>
+      </c>
+      <c r="L116" t="s">
+        <v>26</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N116" t="s">
+        <v>303</v>
+      </c>
+      <c r="O116" t="s">
+        <v>28</v>
+      </c>
+      <c r="P116" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>358</v>
+      </c>
+      <c r="B117" t="s">
+        <v>359</v>
+      </c>
+      <c r="C117" t="s">
+        <v>65</v>
+      </c>
+      <c r="D117" t="s">
+        <v>394</v>
+      </c>
+      <c r="E117" t="s">
+        <v>60</v>
+      </c>
+      <c r="F117" t="s">
+        <v>45</v>
+      </c>
+      <c r="G117">
+        <v>27</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" t="s">
+        <v>54</v>
+      </c>
+      <c r="J117" t="s">
+        <v>395</v>
+      </c>
+      <c r="K117" t="s">
+        <v>25</v>
+      </c>
+      <c r="L117" t="s">
+        <v>26</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N117" t="s">
+        <v>303</v>
+      </c>
+      <c r="O117" t="s">
+        <v>28</v>
+      </c>
+      <c r="P117" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>358</v>
+      </c>
+      <c r="B118" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D118" t="s">
+        <v>396</v>
+      </c>
+      <c r="E118" t="s">
+        <v>60</v>
+      </c>
+      <c r="F118" t="s">
+        <v>31</v>
+      </c>
+      <c r="G118">
+        <v>22</v>
+      </c>
+      <c r="H118" t="s">
+        <v>50</v>
+      </c>
+      <c r="I118" t="s">
+        <v>33</v>
+      </c>
+      <c r="J118" t="s">
+        <v>397</v>
+      </c>
+      <c r="K118" t="s">
+        <v>25</v>
+      </c>
+      <c r="L118" t="s">
+        <v>26</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N118" t="s">
+        <v>398</v>
+      </c>
+      <c r="O118" t="s">
+        <v>28</v>
+      </c>
+      <c r="P118" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>358</v>
+      </c>
+      <c r="B119" t="s">
+        <v>359</v>
+      </c>
+      <c r="C119" t="s">
+        <v>38</v>
+      </c>
+      <c r="D119" t="s">
+        <v>399</v>
+      </c>
+      <c r="E119" t="s">
+        <v>60</v>
+      </c>
+      <c r="F119" t="s">
+        <v>31</v>
+      </c>
+      <c r="G119">
+        <v>39</v>
+      </c>
+      <c r="H119" t="s">
+        <v>77</v>
+      </c>
+      <c r="I119" t="s">
+        <v>33</v>
+      </c>
+      <c r="J119" t="s">
+        <v>400</v>
+      </c>
+      <c r="K119" t="s">
+        <v>25</v>
+      </c>
+      <c r="L119" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N119" t="s">
+        <v>303</v>
+      </c>
+      <c r="O119" t="s">
+        <v>28</v>
+      </c>
+      <c r="P119" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>401</v>
+      </c>
+      <c r="B120" t="s">
+        <v>17</v>
+      </c>
+      <c r="C120" t="s">
+        <v>38</v>
+      </c>
+      <c r="D120" t="s">
+        <v>402</v>
+      </c>
+      <c r="E120" t="s">
+        <v>20</v>
+      </c>
+      <c r="F120" t="s">
+        <v>45</v>
+      </c>
+      <c r="G120">
+        <v>30</v>
+      </c>
+      <c r="H120" t="s">
+        <v>403</v>
+      </c>
+      <c r="I120" t="s">
+        <v>404</v>
+      </c>
+      <c r="J120" t="s">
+        <v>405</v>
+      </c>
+      <c r="K120" t="s">
+        <v>25</v>
+      </c>
+      <c r="L120" t="s">
+        <v>26</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N120" t="s">
+        <v>406</v>
+      </c>
+      <c r="O120" t="s">
+        <v>25</v>
+      </c>
+      <c r="P120" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>401</v>
+      </c>
+      <c r="B121" t="s">
+        <v>407</v>
+      </c>
+      <c r="C121" t="s">
+        <v>18</v>
+      </c>
+      <c r="D121" t="s">
+        <v>408</v>
+      </c>
+      <c r="E121" t="s">
+        <v>20</v>
+      </c>
+      <c r="F121" t="s">
+        <v>45</v>
+      </c>
+      <c r="G121">
+        <v>19</v>
+      </c>
+      <c r="H121" t="s">
+        <v>409</v>
+      </c>
+      <c r="I121" t="s">
+        <v>33</v>
+      </c>
+      <c r="J121" t="s">
+        <v>410</v>
+      </c>
+      <c r="K121" t="s">
+        <v>25</v>
+      </c>
+      <c r="L121" t="s">
+        <v>26</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N121" t="s">
+        <v>411</v>
+      </c>
+      <c r="O121" t="s">
+        <v>28</v>
+      </c>
+      <c r="P121" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>401</v>
+      </c>
+      <c r="B122" t="s">
+        <v>407</v>
+      </c>
+      <c r="C122" t="s">
+        <v>18</v>
+      </c>
+      <c r="D122" t="s">
+        <v>412</v>
+      </c>
+      <c r="E122" t="s">
+        <v>60</v>
+      </c>
+      <c r="F122" t="s">
+        <v>31</v>
+      </c>
+      <c r="G122">
+        <v>30</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" t="s">
+        <v>54</v>
+      </c>
+      <c r="J122" t="s">
+        <v>413</v>
+      </c>
+      <c r="K122" t="s">
+        <v>25</v>
+      </c>
+      <c r="L122" t="s">
+        <v>26</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N122" t="s">
+        <v>63</v>
+      </c>
+      <c r="O122" t="s">
+        <v>172</v>
+      </c>
+      <c r="P122" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>401</v>
+      </c>
+      <c r="B123" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" t="s">
+        <v>18</v>
+      </c>
+      <c r="D123" t="s">
+        <v>415</v>
+      </c>
+      <c r="E123" t="s">
+        <v>60</v>
+      </c>
+      <c r="F123" t="s">
+        <v>45</v>
+      </c>
+      <c r="G123">
+        <v>30</v>
+      </c>
+      <c r="H123" t="s">
+        <v>255</v>
+      </c>
+      <c r="I123" t="s">
+        <v>54</v>
+      </c>
+      <c r="J123" t="s">
+        <v>416</v>
+      </c>
+      <c r="K123" t="s">
+        <v>25</v>
+      </c>
+      <c r="L123" t="s">
+        <v>26</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="N123" t="s">
+        <v>63</v>
+      </c>
+      <c r="O123" t="s">
+        <v>25</v>
+      </c>
+      <c r="P123" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>401</v>
+      </c>
+      <c r="B124" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" t="s">
+        <v>38</v>
+      </c>
+      <c r="D124" t="s">
+        <v>418</v>
+      </c>
+      <c r="E124" t="s">
+        <v>60</v>
+      </c>
+      <c r="F124" t="s">
+        <v>31</v>
+      </c>
+      <c r="G124">
+        <v>33</v>
+      </c>
+      <c r="H124" t="s">
+        <v>40</v>
+      </c>
+      <c r="I124" t="s">
+        <v>33</v>
+      </c>
+      <c r="J124" t="s">
+        <v>419</v>
+      </c>
+      <c r="K124" t="s">
+        <v>25</v>
+      </c>
+      <c r="L124" t="s">
+        <v>48</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N124" t="s">
+        <v>303</v>
+      </c>
+      <c r="O124" t="s">
+        <v>28</v>
+      </c>
+      <c r="P124" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>401</v>
+      </c>
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" t="s">
+        <v>38</v>
+      </c>
+      <c r="D125" t="s">
+        <v>420</v>
+      </c>
+      <c r="E125" t="s">
+        <v>60</v>
+      </c>
+      <c r="F125" t="s">
+        <v>21</v>
+      </c>
+      <c r="G125">
+        <v>39</v>
+      </c>
+      <c r="H125" t="s">
+        <v>218</v>
+      </c>
+      <c r="I125" t="s">
+        <v>33</v>
+      </c>
+      <c r="J125" t="s">
+        <v>421</v>
+      </c>
+      <c r="K125" t="s">
+        <v>25</v>
+      </c>
+      <c r="L125" t="s">
+        <v>26</v>
+      </c>
+      <c r="M125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N125" t="s">
+        <v>303</v>
+      </c>
+      <c r="O125" t="s">
+        <v>28</v>
+      </c>
+      <c r="P125" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>422</v>
+      </c>
+      <c r="B126" t="s">
+        <v>407</v>
+      </c>
+      <c r="C126" t="s">
+        <v>38</v>
+      </c>
+      <c r="D126" t="s">
+        <v>423</v>
+      </c>
+      <c r="E126" t="s">
+        <v>20</v>
+      </c>
+      <c r="F126" t="s">
+        <v>45</v>
+      </c>
+      <c r="G126">
+        <v>40</v>
+      </c>
+      <c r="H126" t="s">
+        <v>50</v>
+      </c>
+      <c r="I126" t="s">
+        <v>33</v>
+      </c>
+      <c r="J126" t="s">
+        <v>424</v>
+      </c>
+      <c r="K126" t="s">
+        <v>25</v>
+      </c>
+      <c r="L126" t="s">
+        <v>26</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N126" t="s">
+        <v>425</v>
+      </c>
+      <c r="O126" t="s">
+        <v>25</v>
+      </c>
+      <c r="P126" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>422</v>
+      </c>
+      <c r="B127" t="s">
+        <v>407</v>
+      </c>
+      <c r="C127" t="s">
+        <v>38</v>
+      </c>
+      <c r="D127" t="s">
+        <v>426</v>
+      </c>
+      <c r="E127" t="s">
+        <v>20</v>
+      </c>
+      <c r="F127" t="s">
+        <v>45</v>
+      </c>
+      <c r="G127">
+        <v>30</v>
+      </c>
+      <c r="H127" t="s">
+        <v>349</v>
+      </c>
+      <c r="I127" t="s">
+        <v>54</v>
+      </c>
+      <c r="J127" t="s">
+        <v>427</v>
+      </c>
+      <c r="K127" t="s">
+        <v>25</v>
+      </c>
+      <c r="L127" t="s">
+        <v>26</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N127" t="s">
+        <v>425</v>
+      </c>
+      <c r="O127" t="s">
+        <v>25</v>
+      </c>
+      <c r="P127" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>422</v>
+      </c>
+      <c r="B128" t="s">
+        <v>407</v>
+      </c>
+      <c r="C128" t="s">
+        <v>38</v>
+      </c>
+      <c r="D128" t="s">
+        <v>428</v>
+      </c>
+      <c r="E128" t="s">
+        <v>20</v>
+      </c>
+      <c r="F128" t="s">
+        <v>45</v>
+      </c>
+      <c r="G128">
+        <v>23</v>
+      </c>
+      <c r="H128" t="s">
+        <v>429</v>
+      </c>
+      <c r="I128" t="s">
+        <v>33</v>
+      </c>
+      <c r="J128" t="s">
+        <v>430</v>
+      </c>
+      <c r="K128" t="s">
+        <v>25</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="M128" t="s">
+        <v>42</v>
+      </c>
+      <c r="N128" t="s">
+        <v>425</v>
+      </c>
+      <c r="O128" t="s">
+        <v>25</v>
+      </c>
+      <c r="P128" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>422</v>
+      </c>
+      <c r="B129" t="s">
+        <v>407</v>
+      </c>
+      <c r="C129" t="s">
+        <v>38</v>
+      </c>
+      <c r="D129" t="s">
+        <v>431</v>
+      </c>
+      <c r="E129" t="s">
+        <v>20</v>
+      </c>
+      <c r="F129" t="s">
+        <v>17</v>
+      </c>
+      <c r="G129">
+        <v>30</v>
+      </c>
+      <c r="H129" t="s">
+        <v>349</v>
+      </c>
+      <c r="I129" t="s">
+        <v>54</v>
+      </c>
+      <c r="J129" t="s">
+        <v>432</v>
+      </c>
+      <c r="K129" t="s">
+        <v>25</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M129" t="s">
+        <v>17</v>
+      </c>
+      <c r="N129" t="s">
+        <v>411</v>
+      </c>
+      <c r="O129" t="s">
+        <v>28</v>
+      </c>
+      <c r="P129" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>422</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>38</v>
+      </c>
+      <c r="D130" t="s">
+        <v>433</v>
+      </c>
+      <c r="E130" t="s">
+        <v>20</v>
+      </c>
+      <c r="F130" t="s">
+        <v>45</v>
+      </c>
+      <c r="G130">
+        <v>30</v>
+      </c>
+      <c r="H130" t="s">
+        <v>73</v>
+      </c>
+      <c r="I130" t="s">
+        <v>54</v>
+      </c>
+      <c r="J130" t="s">
+        <v>434</v>
+      </c>
+      <c r="K130" t="s">
+        <v>25</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M130" t="s">
+        <v>42</v>
+      </c>
+      <c r="N130" t="s">
+        <v>425</v>
+      </c>
+      <c r="O130" t="s">
+        <v>28</v>
+      </c>
+      <c r="P130" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>422</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" t="s">
+        <v>38</v>
+      </c>
+      <c r="D131" t="s">
+        <v>435</v>
+      </c>
+      <c r="E131" t="s">
+        <v>20</v>
+      </c>
+      <c r="F131" t="s">
+        <v>31</v>
+      </c>
+      <c r="G131">
+        <v>46</v>
+      </c>
+      <c r="H131" t="s">
+        <v>218</v>
+      </c>
+      <c r="I131" t="s">
+        <v>33</v>
+      </c>
+      <c r="J131" t="s">
+        <v>436</v>
+      </c>
+      <c r="K131" t="s">
+        <v>25</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M131" t="s">
+        <v>42</v>
+      </c>
+      <c r="N131" t="s">
+        <v>425</v>
+      </c>
+      <c r="O131" t="s">
+        <v>28</v>
+      </c>
+      <c r="P131" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>437</v>
+      </c>
+      <c r="B132" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" t="s">
+        <v>18</v>
+      </c>
+      <c r="D132" t="s">
+        <v>438</v>
+      </c>
+      <c r="E132" t="s">
+        <v>20</v>
+      </c>
+      <c r="F132" t="s">
+        <v>45</v>
+      </c>
+      <c r="G132">
+        <v>39</v>
+      </c>
+      <c r="H132" t="s">
+        <v>36</v>
+      </c>
+      <c r="I132" t="s">
+        <v>33</v>
+      </c>
+      <c r="J132" t="s">
+        <v>439</v>
+      </c>
+      <c r="K132" t="s">
+        <v>25</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M132" t="s">
+        <v>17</v>
+      </c>
+      <c r="N132" t="s">
+        <v>425</v>
+      </c>
+      <c r="O132" t="s">
+        <v>25</v>
+      </c>
+      <c r="P132" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>437</v>
+      </c>
+      <c r="B133" t="s">
+        <v>359</v>
+      </c>
+      <c r="C133" t="s">
+        <v>18</v>
+      </c>
+      <c r="D133" t="s">
+        <v>440</v>
+      </c>
+      <c r="E133" t="s">
+        <v>20</v>
+      </c>
+      <c r="F133" t="s">
+        <v>45</v>
+      </c>
+      <c r="G133">
+        <v>20</v>
+      </c>
+      <c r="H133" t="s">
+        <v>441</v>
+      </c>
+      <c r="I133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J133" t="s">
+        <v>442</v>
+      </c>
+      <c r="K133" t="s">
+        <v>25</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M133" t="s">
+        <v>17</v>
+      </c>
+      <c r="N133" t="s">
+        <v>425</v>
+      </c>
+      <c r="O133" t="s">
+        <v>28</v>
+      </c>
+      <c r="P133" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>422</v>
+      </c>
+      <c r="B134" t="s">
+        <v>407</v>
+      </c>
+      <c r="C134" t="s">
+        <v>38</v>
+      </c>
+      <c r="D134" t="s">
+        <v>443</v>
+      </c>
+      <c r="E134" t="s">
+        <v>60</v>
+      </c>
+      <c r="F134" t="s">
+        <v>45</v>
+      </c>
+      <c r="G134">
+        <v>32</v>
+      </c>
+      <c r="H134" t="s">
+        <v>444</v>
+      </c>
+      <c r="I134" t="s">
+        <v>445</v>
+      </c>
+      <c r="J134" t="s">
+        <v>446</v>
+      </c>
+      <c r="K134" t="s">
+        <v>25</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M134" t="s">
+        <v>268</v>
+      </c>
+      <c r="N134" t="s">
+        <v>447</v>
+      </c>
+      <c r="O134" t="s">
+        <v>25</v>
+      </c>
+      <c r="P134" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>422</v>
+      </c>
+      <c r="B135" t="s">
+        <v>407</v>
+      </c>
+      <c r="C135" t="s">
+        <v>38</v>
+      </c>
+      <c r="D135" t="s">
+        <v>449</v>
+      </c>
+      <c r="E135" t="s">
+        <v>60</v>
+      </c>
+      <c r="F135" t="s">
+        <v>45</v>
+      </c>
+      <c r="G135">
+        <v>40</v>
+      </c>
+      <c r="H135" t="s">
+        <v>36</v>
+      </c>
+      <c r="I135" t="s">
+        <v>33</v>
+      </c>
+      <c r="J135" t="s">
+        <v>450</v>
+      </c>
+      <c r="K135" t="s">
+        <v>25</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="M135" t="s">
+        <v>42</v>
+      </c>
+      <c r="N135" t="s">
+        <v>451</v>
+      </c>
+      <c r="O135" t="s">
+        <v>25</v>
+      </c>
+      <c r="P135" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>422</v>
+      </c>
+      <c r="B136" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" t="s">
+        <v>38</v>
+      </c>
+      <c r="D136" t="s">
+        <v>452</v>
+      </c>
+      <c r="E136" t="s">
+        <v>60</v>
+      </c>
+      <c r="F136" t="s">
+        <v>45</v>
+      </c>
+      <c r="G136">
+        <v>30</v>
+      </c>
+      <c r="H136" t="s">
+        <v>453</v>
+      </c>
+      <c r="I136" t="s">
+        <v>33</v>
+      </c>
+      <c r="J136" t="s">
+        <v>454</v>
+      </c>
+      <c r="K136" t="s">
+        <v>25</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M136" t="s">
+        <v>42</v>
+      </c>
+      <c r="N136" t="s">
+        <v>455</v>
+      </c>
+      <c r="O136" t="s">
+        <v>28</v>
+      </c>
+      <c r="P136" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>422</v>
+      </c>
+      <c r="B137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" t="s">
+        <v>38</v>
+      </c>
+      <c r="D137" t="s">
+        <v>456</v>
+      </c>
+      <c r="E137" t="s">
+        <v>60</v>
+      </c>
+      <c r="F137" t="s">
+        <v>21</v>
+      </c>
+      <c r="G137">
+        <v>52</v>
+      </c>
+      <c r="H137" t="s">
+        <v>115</v>
+      </c>
+      <c r="I137" t="s">
+        <v>457</v>
+      </c>
+      <c r="J137" t="s">
+        <v>458</v>
+      </c>
+      <c r="K137" t="s">
+        <v>25</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="M137" t="s">
+        <v>268</v>
+      </c>
+      <c r="N137" t="s">
+        <v>455</v>
+      </c>
+      <c r="O137" t="s">
+        <v>28</v>
+      </c>
+      <c r="P137" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>422</v>
+      </c>
+      <c r="B138" t="s">
+        <v>17</v>
+      </c>
+      <c r="C138" t="s">
+        <v>18</v>
+      </c>
+      <c r="D138" t="s">
+        <v>459</v>
+      </c>
+      <c r="E138" t="s">
+        <v>60</v>
+      </c>
+      <c r="F138" t="s">
+        <v>45</v>
+      </c>
+      <c r="G138">
+        <v>83</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" t="s">
+        <v>179</v>
+      </c>
+      <c r="J138" t="s">
+        <v>460</v>
+      </c>
+      <c r="K138" t="s">
+        <v>25</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M138" t="s">
+        <v>42</v>
+      </c>
+      <c r="N138" t="s">
+        <v>455</v>
+      </c>
+      <c r="O138" t="s">
+        <v>28</v>
+      </c>
+      <c r="P138" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>422</v>
+      </c>
+      <c r="B139" t="s">
+        <v>407</v>
+      </c>
+      <c r="C139" t="s">
+        <v>38</v>
+      </c>
+      <c r="D139" t="s">
+        <v>461</v>
+      </c>
+      <c r="E139" t="s">
+        <v>60</v>
+      </c>
+      <c r="F139" t="s">
+        <v>45</v>
+      </c>
+      <c r="G139">
+        <v>67</v>
+      </c>
+      <c r="H139" t="s">
+        <v>462</v>
+      </c>
+      <c r="I139" t="s">
+        <v>33</v>
+      </c>
+      <c r="J139" t="s">
+        <v>463</v>
+      </c>
+      <c r="K139" t="s">
+        <v>25</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M139" t="s">
+        <v>42</v>
+      </c>
+      <c r="N139" t="s">
+        <v>464</v>
+      </c>
+      <c r="O139" t="s">
+        <v>25</v>
+      </c>
+      <c r="P139" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>422</v>
+      </c>
+      <c r="B140" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" t="s">
+        <v>38</v>
+      </c>
+      <c r="D140" t="s">
+        <v>465</v>
+      </c>
+      <c r="E140" t="s">
+        <v>60</v>
+      </c>
+      <c r="F140" t="s">
+        <v>31</v>
+      </c>
+      <c r="G140">
+        <v>39</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" t="s">
+        <v>54</v>
+      </c>
+      <c r="J140" t="s">
+        <v>466</v>
+      </c>
+      <c r="K140" t="s">
+        <v>25</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M140" t="s">
+        <v>42</v>
+      </c>
+      <c r="N140" t="s">
+        <v>455</v>
+      </c>
+      <c r="O140" t="s">
+        <v>28</v>
+      </c>
+      <c r="P140" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>422</v>
+      </c>
+      <c r="B141" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141" t="s">
+        <v>18</v>
+      </c>
+      <c r="D141" t="s">
+        <v>467</v>
+      </c>
+      <c r="E141" t="s">
+        <v>60</v>
+      </c>
+      <c r="F141" t="s">
+        <v>45</v>
+      </c>
+      <c r="G141">
+        <v>14</v>
+      </c>
+      <c r="H141" t="s">
+        <v>321</v>
+      </c>
+      <c r="I141" t="s">
+        <v>179</v>
+      </c>
+      <c r="J141" t="s">
+        <v>468</v>
+      </c>
+      <c r="K141" t="s">
+        <v>25</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M141" t="s">
+        <v>17</v>
+      </c>
+      <c r="N141" t="s">
+        <v>469</v>
+      </c>
+      <c r="O141" t="s">
+        <v>25</v>
+      </c>
+      <c r="P141" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>422</v>
+      </c>
+      <c r="B142" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" t="s">
+        <v>38</v>
+      </c>
+      <c r="D142" t="s">
+        <v>470</v>
+      </c>
+      <c r="E142" t="s">
+        <v>60</v>
+      </c>
+      <c r="F142" t="s">
+        <v>31</v>
+      </c>
+      <c r="G142">
+        <v>36</v>
+      </c>
+      <c r="H142" t="s">
+        <v>57</v>
+      </c>
+      <c r="I142" t="s">
+        <v>33</v>
+      </c>
+      <c r="J142" t="s">
+        <v>471</v>
+      </c>
+      <c r="K142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M142" t="s">
+        <v>42</v>
+      </c>
+      <c r="N142" t="s">
+        <v>451</v>
+      </c>
+      <c r="O142" t="s">
+        <v>25</v>
+      </c>
+      <c r="P142" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>422</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>38</v>
+      </c>
+      <c r="D143" t="s">
+        <v>472</v>
+      </c>
+      <c r="E143" t="s">
+        <v>60</v>
+      </c>
+      <c r="F143" t="s">
+        <v>45</v>
+      </c>
+      <c r="G143">
+        <v>19</v>
+      </c>
+      <c r="H143" t="s">
+        <v>473</v>
+      </c>
+      <c r="I143" t="s">
+        <v>33</v>
+      </c>
+      <c r="J143" t="s">
+        <v>474</v>
+      </c>
+      <c r="K143" t="s">
+        <v>25</v>
+      </c>
+      <c r="L143" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M143" t="s">
+        <v>17</v>
+      </c>
+      <c r="N143" t="s">
+        <v>455</v>
+      </c>
+      <c r="O143" t="s">
+        <v>28</v>
+      </c>
+      <c r="P143" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>422</v>
+      </c>
+      <c r="B144" t="s">
+        <v>407</v>
+      </c>
+      <c r="C144" t="s">
+        <v>38</v>
+      </c>
+      <c r="D144" t="s">
+        <v>475</v>
+      </c>
+      <c r="E144" t="s">
+        <v>60</v>
+      </c>
+      <c r="F144" t="s">
+        <v>21</v>
+      </c>
+      <c r="G144">
+        <v>28</v>
+      </c>
+      <c r="H144" t="s">
+        <v>46</v>
+      </c>
+      <c r="I144" t="s">
+        <v>33</v>
+      </c>
+      <c r="J144" t="s">
+        <v>476</v>
+      </c>
+      <c r="K144" t="s">
+        <v>25</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M144" t="s">
+        <v>42</v>
+      </c>
+      <c r="N144" t="s">
+        <v>469</v>
+      </c>
+      <c r="O144" t="s">
+        <v>25</v>
+      </c>
+      <c r="P144" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>422</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D145" t="s">
+        <v>477</v>
+      </c>
+      <c r="E145" t="s">
+        <v>60</v>
+      </c>
+      <c r="F145" t="s">
+        <v>45</v>
+      </c>
+      <c r="G145">
+        <v>30</v>
+      </c>
+      <c r="H145" t="s">
+        <v>478</v>
+      </c>
+      <c r="I145" t="s">
+        <v>54</v>
+      </c>
+      <c r="J145" t="s">
+        <v>479</v>
+      </c>
+      <c r="K145" t="s">
+        <v>25</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M145" t="s">
+        <v>17</v>
+      </c>
+      <c r="N145" t="s">
+        <v>455</v>
+      </c>
+      <c r="O145" t="s">
+        <v>28</v>
+      </c>
+      <c r="P145" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>422</v>
+      </c>
+      <c r="B146" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" t="s">
+        <v>18</v>
+      </c>
+      <c r="D146" t="s">
+        <v>480</v>
+      </c>
+      <c r="E146" t="s">
+        <v>60</v>
+      </c>
+      <c r="F146" t="s">
+        <v>45</v>
+      </c>
+      <c r="G146">
+        <v>14</v>
+      </c>
+      <c r="H146" t="s">
+        <v>255</v>
+      </c>
+      <c r="I146" t="s">
+        <v>89</v>
+      </c>
+      <c r="J146" t="s">
+        <v>481</v>
+      </c>
+      <c r="K146" t="s">
+        <v>25</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M146" t="s">
+        <v>17</v>
+      </c>
+      <c r="N146" t="s">
+        <v>455</v>
+      </c>
+      <c r="O146" t="s">
+        <v>28</v>
+      </c>
+      <c r="P146" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>422</v>
+      </c>
+      <c r="B147" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" t="s">
+        <v>38</v>
+      </c>
+      <c r="D147" t="s">
+        <v>482</v>
+      </c>
+      <c r="E147" t="s">
+        <v>60</v>
+      </c>
+      <c r="F147" t="s">
+        <v>45</v>
+      </c>
+      <c r="G147">
+        <v>31</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" t="s">
+        <v>54</v>
+      </c>
+      <c r="J147" t="s">
+        <v>483</v>
+      </c>
+      <c r="K147" t="s">
+        <v>25</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M147" t="s">
+        <v>42</v>
+      </c>
+      <c r="N147" t="s">
+        <v>455</v>
+      </c>
+      <c r="O147" t="s">
+        <v>28</v>
+      </c>
+      <c r="P147" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>422</v>
+      </c>
+      <c r="B148" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" t="s">
+        <v>18</v>
+      </c>
+      <c r="D148" t="s">
+        <v>484</v>
+      </c>
+      <c r="E148" t="s">
+        <v>60</v>
+      </c>
+      <c r="F148" t="s">
+        <v>31</v>
+      </c>
+      <c r="G148">
+        <v>36</v>
+      </c>
+      <c r="H148" t="s">
+        <v>40</v>
+      </c>
+      <c r="I148" t="s">
+        <v>33</v>
+      </c>
+      <c r="J148" t="s">
+        <v>485</v>
+      </c>
+      <c r="K148" t="s">
+        <v>25</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M148" t="s">
+        <v>17</v>
+      </c>
+      <c r="N148" t="s">
+        <v>455</v>
+      </c>
+      <c r="O148" t="s">
+        <v>28</v>
+      </c>
+      <c r="P148" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>422</v>
+      </c>
+      <c r="B149" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" t="s">
+        <v>38</v>
+      </c>
+      <c r="D149" t="s">
+        <v>486</v>
+      </c>
+      <c r="E149" t="s">
+        <v>60</v>
+      </c>
+      <c r="F149" t="s">
+        <v>31</v>
+      </c>
+      <c r="G149">
+        <v>49</v>
+      </c>
+      <c r="H149" t="s">
+        <v>218</v>
+      </c>
+      <c r="I149" t="s">
+        <v>33</v>
+      </c>
+      <c r="J149" t="s">
+        <v>487</v>
+      </c>
+      <c r="K149" t="s">
+        <v>25</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M149" t="s">
+        <v>42</v>
+      </c>
+      <c r="N149" t="s">
+        <v>469</v>
+      </c>
+      <c r="O149" t="s">
+        <v>25</v>
+      </c>
+      <c r="P149" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>422</v>
+      </c>
+      <c r="B150" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" t="s">
+        <v>38</v>
+      </c>
+      <c r="D150" t="s">
+        <v>488</v>
+      </c>
+      <c r="E150" t="s">
+        <v>60</v>
+      </c>
+      <c r="F150" t="s">
+        <v>45</v>
+      </c>
+      <c r="G150">
+        <v>40</v>
+      </c>
+      <c r="H150" t="s">
+        <v>489</v>
+      </c>
+      <c r="I150" t="s">
+        <v>89</v>
+      </c>
+      <c r="J150" t="s">
+        <v>490</v>
+      </c>
+      <c r="K150" t="s">
+        <v>25</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M150" t="s">
+        <v>42</v>
+      </c>
+      <c r="N150" t="s">
+        <v>491</v>
+      </c>
+      <c r="O150" t="s">
+        <v>25</v>
+      </c>
+      <c r="P150" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>422</v>
+      </c>
+      <c r="B151" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" t="s">
+        <v>38</v>
+      </c>
+      <c r="D151" t="s">
+        <v>492</v>
+      </c>
+      <c r="E151" t="s">
+        <v>60</v>
+      </c>
+      <c r="F151" t="s">
+        <v>45</v>
+      </c>
+      <c r="G151">
+        <v>37</v>
+      </c>
+      <c r="H151" t="s">
+        <v>493</v>
+      </c>
+      <c r="I151" t="s">
+        <v>89</v>
+      </c>
+      <c r="J151" t="s">
+        <v>494</v>
+      </c>
+      <c r="K151" t="s">
+        <v>25</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M151" t="s">
+        <v>42</v>
+      </c>
+      <c r="N151" t="s">
+        <v>495</v>
+      </c>
+      <c r="O151" t="s">
+        <v>25</v>
+      </c>
+      <c r="P151" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>422</v>
+      </c>
+      <c r="B152" t="s">
+        <v>407</v>
+      </c>
+      <c r="C152" t="s">
+        <v>38</v>
+      </c>
+      <c r="D152" t="s">
+        <v>496</v>
+      </c>
+      <c r="E152" t="s">
+        <v>60</v>
+      </c>
+      <c r="F152" t="s">
+        <v>45</v>
+      </c>
+      <c r="G152">
+        <v>24</v>
+      </c>
+      <c r="H152" t="s">
+        <v>102</v>
+      </c>
+      <c r="I152" t="s">
+        <v>33</v>
+      </c>
+      <c r="J152" t="s">
+        <v>497</v>
+      </c>
+      <c r="K152" t="s">
+        <v>25</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M152" t="s">
+        <v>17</v>
+      </c>
+      <c r="N152" t="s">
+        <v>498</v>
+      </c>
+      <c r="O152" t="s">
+        <v>25</v>
+      </c>
+      <c r="P152" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>437</v>
+      </c>
+      <c r="B153" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" t="s">
+        <v>38</v>
+      </c>
+      <c r="D153" t="s">
+        <v>499</v>
+      </c>
+      <c r="E153" t="s">
+        <v>60</v>
+      </c>
+      <c r="F153" t="s">
+        <v>45</v>
+      </c>
+      <c r="G153">
+        <v>18</v>
+      </c>
+      <c r="H153" t="s">
+        <v>50</v>
+      </c>
+      <c r="I153" t="s">
+        <v>33</v>
+      </c>
+      <c r="J153" t="s">
+        <v>500</v>
+      </c>
+      <c r="K153" t="s">
+        <v>25</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M153" t="s">
+        <v>42</v>
+      </c>
+      <c r="N153" t="s">
+        <v>501</v>
+      </c>
+      <c r="O153" t="s">
+        <v>25</v>
+      </c>
+      <c r="P153" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>437</v>
+      </c>
+      <c r="B154" t="s">
+        <v>359</v>
+      </c>
+      <c r="C154" t="s">
+        <v>38</v>
+      </c>
+      <c r="D154" t="s">
+        <v>502</v>
+      </c>
+      <c r="E154" t="s">
+        <v>60</v>
+      </c>
+      <c r="F154" t="s">
+        <v>31</v>
+      </c>
+      <c r="G154">
+        <v>31</v>
+      </c>
+      <c r="H154" t="s">
+        <v>36</v>
+      </c>
+      <c r="I154" t="s">
+        <v>33</v>
+      </c>
+      <c r="J154" t="s">
+        <v>503</v>
+      </c>
+      <c r="K154" t="s">
+        <v>25</v>
+      </c>
+      <c r="L154" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M154" t="s">
+        <v>42</v>
+      </c>
+      <c r="N154" t="s">
+        <v>504</v>
+      </c>
+      <c r="O154" t="s">
+        <v>25</v>
+      </c>
+      <c r="P154" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>437</v>
+      </c>
+      <c r="B155" t="s">
+        <v>359</v>
+      </c>
+      <c r="C155" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155" t="s">
+        <v>505</v>
+      </c>
+      <c r="E155" t="s">
+        <v>60</v>
+      </c>
+      <c r="F155" t="s">
+        <v>45</v>
+      </c>
+      <c r="G155">
+        <v>29</v>
+      </c>
+      <c r="H155" t="s">
+        <v>40</v>
+      </c>
+      <c r="I155" t="s">
+        <v>33</v>
+      </c>
+      <c r="J155" t="s">
+        <v>506</v>
+      </c>
+      <c r="K155" t="s">
+        <v>25</v>
+      </c>
+      <c r="L155" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M155" t="s">
+        <v>17</v>
+      </c>
+      <c r="N155" t="s">
+        <v>469</v>
+      </c>
+      <c r="O155" t="s">
+        <v>25</v>
+      </c>
+      <c r="P155" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>437</v>
+      </c>
+      <c r="B156" t="s">
+        <v>359</v>
+      </c>
+      <c r="C156" t="s">
+        <v>38</v>
+      </c>
+      <c r="D156" t="s">
+        <v>507</v>
+      </c>
+      <c r="E156" t="s">
+        <v>60</v>
+      </c>
+      <c r="F156" t="s">
+        <v>31</v>
+      </c>
+      <c r="G156">
+        <v>32</v>
+      </c>
+      <c r="H156" t="s">
+        <v>46</v>
+      </c>
+      <c r="I156" t="s">
+        <v>33</v>
+      </c>
+      <c r="J156" t="s">
+        <v>508</v>
+      </c>
+      <c r="K156" t="s">
+        <v>25</v>
+      </c>
+      <c r="L156" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M156" t="s">
+        <v>17</v>
+      </c>
+      <c r="N156" t="s">
+        <v>455</v>
+      </c>
+      <c r="O156" t="s">
+        <v>28</v>
+      </c>
+      <c r="P156" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>437</v>
+      </c>
+      <c r="B157" t="s">
+        <v>359</v>
+      </c>
+      <c r="C157" t="s">
+        <v>18</v>
+      </c>
+      <c r="D157" t="s">
+        <v>509</v>
+      </c>
+      <c r="E157" t="s">
+        <v>60</v>
+      </c>
+      <c r="F157" t="s">
+        <v>45</v>
+      </c>
+      <c r="G157">
+        <v>50</v>
+      </c>
+      <c r="H157" t="s">
+        <v>510</v>
+      </c>
+      <c r="I157" t="s">
+        <v>33</v>
+      </c>
+      <c r="J157" t="s">
+        <v>511</v>
+      </c>
+      <c r="K157" t="s">
+        <v>25</v>
+      </c>
+      <c r="L157" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M157" t="s">
+        <v>17</v>
+      </c>
+      <c r="N157" t="s">
+        <v>455</v>
+      </c>
+      <c r="O157" t="s">
+        <v>28</v>
+      </c>
+      <c r="P157" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>437</v>
+      </c>
+      <c r="B158" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" t="s">
+        <v>18</v>
+      </c>
+      <c r="D158" t="s">
+        <v>512</v>
+      </c>
+      <c r="E158" t="s">
+        <v>60</v>
+      </c>
+      <c r="F158" t="s">
+        <v>45</v>
+      </c>
+      <c r="G158">
+        <v>15</v>
+      </c>
+      <c r="H158" t="s">
+        <v>61</v>
+      </c>
+      <c r="I158" t="s">
+        <v>33</v>
+      </c>
+      <c r="J158" t="s">
+        <v>513</v>
+      </c>
+      <c r="K158" t="s">
+        <v>25</v>
+      </c>
+      <c r="L158" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M158" t="s">
+        <v>17</v>
+      </c>
+      <c r="N158" t="s">
+        <v>514</v>
+      </c>
+      <c r="O158" t="s">
+        <v>172</v>
+      </c>
+      <c r="P158" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M159" s="1"/>
       <c r="N159"/>
     </row>
-    <row r="160" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M160" s="1"/>
       <c r="N160"/>
     </row>

--- a/Consolidado_Bridge_2026.xlsx
+++ b/Consolidado_Bridge_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08d87aadaabdc2cb/Documentos/nwb/bridge/dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="867" documentId="8_{C607EACA-C650-4A5E-95C7-07DDA7668303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E49C948F-4BC3-4AEC-8649-E5672CE4553E}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{C7AD892A-AB25-4EFD-AB7A-644C48CBC51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C8E30CC-0D4D-41BF-84A5-6A894D2DCAC9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEFB68E0-0739-433A-A945-0FEA615287DD}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2026 Consolidado" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026 Consolidado'!$A$1:$P$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026 Consolidado'!$A$1:$P$311</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4666" uniqueCount="919">
   <si>
     <t>Quando</t>
   </si>
@@ -1584,6 +1584,1218 @@
   </si>
   <si>
     <t>Encaminhada ao Nexteen</t>
+  </si>
+  <si>
+    <t>01/03/2026</t>
+  </si>
+  <si>
+    <t>Nilo Sérgio Leite Pereira Junior</t>
+  </si>
+  <si>
+    <t>21 99918-8803</t>
+  </si>
+  <si>
+    <t>Haroldo Athos De Sousa Dias</t>
+  </si>
+  <si>
+    <t>Higienópolis</t>
+  </si>
+  <si>
+    <t>21 99857-5516</t>
+  </si>
+  <si>
+    <t>Anderson Sampaio Da Fonseca</t>
+  </si>
+  <si>
+    <t>21 96963-0933</t>
+  </si>
+  <si>
+    <t>Hugo Sampaio</t>
+  </si>
+  <si>
+    <t>Praia Do Canto</t>
+  </si>
+  <si>
+    <t>Vitória / ES</t>
+  </si>
+  <si>
+    <t>21 98212-3311</t>
+  </si>
+  <si>
+    <t>Talyson Duarte</t>
+  </si>
+  <si>
+    <t>Barra Da Tijuca</t>
+  </si>
+  <si>
+    <t>21 99600-1300</t>
+  </si>
+  <si>
+    <t>álvaro Campos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom Sucesso </t>
+  </si>
+  <si>
+    <t>21 97610-4753</t>
+  </si>
+  <si>
+    <t>João Pedro</t>
+  </si>
+  <si>
+    <t>21 99248-3365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raimundo </t>
+  </si>
+  <si>
+    <t>21 91865-7470</t>
+  </si>
+  <si>
+    <t>Plínio Augusto</t>
+  </si>
+  <si>
+    <t>21 98341-7351</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>Samuel Oliveira</t>
+  </si>
+  <si>
+    <t>Santa Cecília</t>
+  </si>
+  <si>
+    <t>São Paulo / SP</t>
+  </si>
+  <si>
+    <t>11 91479-2326</t>
+  </si>
+  <si>
+    <t>Paula Machado</t>
+  </si>
+  <si>
+    <t>22 99747-3598</t>
+  </si>
+  <si>
+    <t>Danielle Mariano</t>
+  </si>
+  <si>
+    <t>Joselma Da Silva</t>
+  </si>
+  <si>
+    <t>21 98623-8321</t>
+  </si>
+  <si>
+    <t>Thais Rocha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engenho Novo </t>
+  </si>
+  <si>
+    <t>21 98290-9610</t>
+  </si>
+  <si>
+    <t>Esther De Souza Paez Sagrillo</t>
+  </si>
+  <si>
+    <t>Engenho De Dentro</t>
+  </si>
+  <si>
+    <t>21 98752-1311</t>
+  </si>
+  <si>
+    <t>Já está indo ao GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruth </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonsucesso </t>
+  </si>
+  <si>
+    <t>92 99264-2593</t>
+  </si>
+  <si>
+    <t>Edna Da Silva Nunes</t>
+  </si>
+  <si>
+    <t>21 98338-4294</t>
+  </si>
+  <si>
+    <t>Caroline Nunes</t>
+  </si>
+  <si>
+    <t>Braunes</t>
+  </si>
+  <si>
+    <t>Nova Friburgo / RJ</t>
+  </si>
+  <si>
+    <t>22 99727-8621</t>
+  </si>
+  <si>
+    <t>Priscila Kelly De Almeida Sousa</t>
+  </si>
+  <si>
+    <t>21 98306-3753</t>
+  </si>
+  <si>
+    <t>Encaminhada ao gc tijuca</t>
+  </si>
+  <si>
+    <t>Caroline Astorga</t>
+  </si>
+  <si>
+    <t>21 98133-8061</t>
+  </si>
+  <si>
+    <t>Natália Vilela</t>
+  </si>
+  <si>
+    <t>27 99869-6641</t>
+  </si>
+  <si>
+    <t>Milena Soares Dos Santos</t>
+  </si>
+  <si>
+    <t>Gamboa</t>
+  </si>
+  <si>
+    <t>21 97009-1324</t>
+  </si>
+  <si>
+    <t>Cida Sales</t>
+  </si>
+  <si>
+    <t>Karla Gonçalves Sampaio</t>
+  </si>
+  <si>
+    <t>21 99268-7215</t>
+  </si>
+  <si>
+    <t>Malu Correia</t>
+  </si>
+  <si>
+    <t>Rio Janeiro  / --</t>
+  </si>
+  <si>
+    <t>21 97906-3205</t>
+  </si>
+  <si>
+    <t>Encaminhada para o gc</t>
+  </si>
+  <si>
+    <t>Karolyn Santos</t>
+  </si>
+  <si>
+    <t>11 97749-9668</t>
+  </si>
+  <si>
+    <t>Marcela Almeida De Freitas</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>21 98145-5804</t>
+  </si>
+  <si>
+    <t>Alana Gabriela Silva</t>
+  </si>
+  <si>
+    <t>21 98334-7087</t>
+  </si>
+  <si>
+    <t>Bárbara Ximenes</t>
+  </si>
+  <si>
+    <t>21 97545-3327</t>
+  </si>
+  <si>
+    <t>Lorainy Ribeiro</t>
+  </si>
+  <si>
+    <t>24 99989-3731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virgínia </t>
+  </si>
+  <si>
+    <t>21 99777-4009</t>
+  </si>
+  <si>
+    <t>Cristiane Mariano</t>
+  </si>
+  <si>
+    <t>Helena Juca</t>
+  </si>
+  <si>
+    <t>21 99955-3971</t>
+  </si>
+  <si>
+    <t>Manuela Freitas</t>
+  </si>
+  <si>
+    <t>21 98038-4432</t>
+  </si>
+  <si>
+    <t>Samantha Pieralgele</t>
+  </si>
+  <si>
+    <t>21 9667-0894</t>
+  </si>
+  <si>
+    <t>Samantha Fernandes De Souza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Tereza </t>
+  </si>
+  <si>
+    <t>21 98276-4717</t>
+  </si>
+  <si>
+    <t>Alcilene Oliveira</t>
+  </si>
+  <si>
+    <t>21 98640-9471</t>
+  </si>
+  <si>
+    <t>08/03/2026</t>
+  </si>
+  <si>
+    <t>Thiago Assis</t>
+  </si>
+  <si>
+    <t>21 98228-0145</t>
+  </si>
+  <si>
+    <t>Theodomiro Vinicius</t>
+  </si>
+  <si>
+    <t>Lapa</t>
+  </si>
+  <si>
+    <t>21 98810-9881</t>
+  </si>
+  <si>
+    <t>Willian Estacio Martins</t>
+  </si>
+  <si>
+    <t>21 97408-3089</t>
+  </si>
+  <si>
+    <t>Ismael Agostinho Dos Santos</t>
+  </si>
+  <si>
+    <t>21 9594-2415</t>
+  </si>
+  <si>
+    <t>Número errado</t>
+  </si>
+  <si>
+    <t>Gabriel Sousa Da Silva</t>
+  </si>
+  <si>
+    <t>21 98146-4926</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>Antônio Carlos Nunes</t>
+  </si>
+  <si>
+    <t>21 97554-5516</t>
+  </si>
+  <si>
+    <t>Jose Nicacio Souto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penha Circular </t>
+  </si>
+  <si>
+    <t>21 98768-1871</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>culto next</t>
+  </si>
+  <si>
+    <t>Thomas Carvalho</t>
+  </si>
+  <si>
+    <t>Urca</t>
+  </si>
+  <si>
+    <t>21 99760-5808</t>
+  </si>
+  <si>
+    <t>Luis Freire</t>
+  </si>
+  <si>
+    <t>21 99849-3007</t>
+  </si>
+  <si>
+    <t>Alexsandro Da Silva</t>
+  </si>
+  <si>
+    <t>21 99075-7318</t>
+  </si>
+  <si>
+    <t>Pablo Silva</t>
+  </si>
+  <si>
+    <t>Humaitá</t>
+  </si>
+  <si>
+    <t>21 98566-7275</t>
+  </si>
+  <si>
+    <t>14/03/2026</t>
+  </si>
+  <si>
+    <t>Saulo Marcos Faria Castro Bastos</t>
+  </si>
+  <si>
+    <t>21 99109-0633</t>
+  </si>
+  <si>
+    <t>João Vitor Leocadio</t>
+  </si>
+  <si>
+    <t>21 21965-5504</t>
+  </si>
+  <si>
+    <t>Rayssa De Souza Bonfim</t>
+  </si>
+  <si>
+    <t>Lagoa</t>
+  </si>
+  <si>
+    <t>14 99875-2007</t>
+  </si>
+  <si>
+    <t>Flaviana Paulo De Almeida</t>
+  </si>
+  <si>
+    <t>Rua Sain Roma</t>
+  </si>
+  <si>
+    <t>21 98135-4697</t>
+  </si>
+  <si>
+    <t>Karine Gonzalez</t>
+  </si>
+  <si>
+    <t>21 99538-2293</t>
+  </si>
+  <si>
+    <t>Alexandra Lopes</t>
+  </si>
+  <si>
+    <t>21 97961-2855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">encaminhada ao gc tijuca </t>
+  </si>
+  <si>
+    <t>Paloma Silva</t>
+  </si>
+  <si>
+    <t>21 98256-9019</t>
+  </si>
+  <si>
+    <t>Matiele Medeiros</t>
+  </si>
+  <si>
+    <t>21 97911-6148</t>
+  </si>
+  <si>
+    <t>Virgínia Medeiros</t>
+  </si>
+  <si>
+    <t>Cassia Silva</t>
+  </si>
+  <si>
+    <t>21 99236-0502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">É de outra igreja </t>
+  </si>
+  <si>
+    <t>Maria Eduarda Souza</t>
+  </si>
+  <si>
+    <t>Vila Isabel</t>
+  </si>
+  <si>
+    <t>21 98318-8145</t>
+  </si>
+  <si>
+    <t>Thaina Ribeiro</t>
+  </si>
+  <si>
+    <t>21 96411-4656</t>
+  </si>
+  <si>
+    <t>Kimberley Cristine</t>
+  </si>
+  <si>
+    <t>21 96912-5100</t>
+  </si>
+  <si>
+    <t>Bárbara Yaisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tijuquinha Itanhanga </t>
+  </si>
+  <si>
+    <t>Tijuquinha  / RJ</t>
+  </si>
+  <si>
+    <t>21 97478-6128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">segunda vez </t>
+  </si>
+  <si>
+    <t>Anna Luiza</t>
+  </si>
+  <si>
+    <t>21 97533-8044</t>
+  </si>
+  <si>
+    <t>esta indo ao gc</t>
+  </si>
+  <si>
+    <t>Amanda Cardoso</t>
+  </si>
+  <si>
+    <t>21 96898-8249</t>
+  </si>
+  <si>
+    <t>15/03/2026</t>
+  </si>
+  <si>
+    <t>Juan Carlos Moreira França</t>
+  </si>
+  <si>
+    <t>Penha</t>
+  </si>
+  <si>
+    <t>21 97386-1432</t>
+  </si>
+  <si>
+    <t>Daniel Silva Schuindt Barbosa</t>
+  </si>
+  <si>
+    <t>Laranjeiras</t>
+  </si>
+  <si>
+    <t>21 97121-6436</t>
+  </si>
+  <si>
+    <t>Allan Da Conceicao</t>
+  </si>
+  <si>
+    <t>21 96555-8362</t>
+  </si>
+  <si>
+    <t>William Lamenha Fernandes</t>
+  </si>
+  <si>
+    <t>82 9995-1788</t>
+  </si>
+  <si>
+    <t>82 99951-7089</t>
+  </si>
+  <si>
+    <t>Ricardo Campos</t>
+  </si>
+  <si>
+    <t>21 96629-2018</t>
+  </si>
+  <si>
+    <t>Paulo Eduardo</t>
+  </si>
+  <si>
+    <t>21 99513-5833</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>Romulo Faria</t>
+  </si>
+  <si>
+    <t>21 99761-1265</t>
+  </si>
+  <si>
+    <t>culto maximos</t>
+  </si>
+  <si>
+    <t>Leonardo Moreno</t>
+  </si>
+  <si>
+    <t>21 99087-6138</t>
+  </si>
+  <si>
+    <t>Diego De Almeida</t>
+  </si>
+  <si>
+    <t>Santa Maria</t>
+  </si>
+  <si>
+    <t>Santos / SP</t>
+  </si>
+  <si>
+    <t>13 98170-9865</t>
+  </si>
+  <si>
+    <t>Aparecida Da Graça Ferreira</t>
+  </si>
+  <si>
+    <t>21 98094-2525</t>
+  </si>
+  <si>
+    <t>Amanda De Souza Paiva</t>
+  </si>
+  <si>
+    <t>21 98349-8643</t>
+  </si>
+  <si>
+    <t>Ana Julia Quaresma</t>
+  </si>
+  <si>
+    <t>Caju</t>
+  </si>
+  <si>
+    <t>Rio  / RJ</t>
+  </si>
+  <si>
+    <t>21 98258-4885</t>
+  </si>
+  <si>
+    <t>Laura Mendes De Souza</t>
+  </si>
+  <si>
+    <t>21 99399-1520</t>
+  </si>
+  <si>
+    <t>Stefanie Caroline Soares</t>
+  </si>
+  <si>
+    <t>21 98098-9781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segund vez à frente </t>
+  </si>
+  <si>
+    <t>Nathalia Bezerra</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>21 97951-9972</t>
+  </si>
+  <si>
+    <t>Bruna Santis Do Oliveira</t>
+  </si>
+  <si>
+    <t>21 96943-5216</t>
+  </si>
+  <si>
+    <t>Bianca De Paula Cola</t>
+  </si>
+  <si>
+    <t>21 99160-2037</t>
+  </si>
+  <si>
+    <t>Vitória Giovanna</t>
+  </si>
+  <si>
+    <t>21 97491-5671</t>
+  </si>
+  <si>
+    <t>Ana Beatriz</t>
+  </si>
+  <si>
+    <t>21 97691-6909</t>
+  </si>
+  <si>
+    <t>Encaminhada pink vidigal</t>
+  </si>
+  <si>
+    <t>culto pink</t>
+  </si>
+  <si>
+    <t>Yasmin Almeida De Souza</t>
+  </si>
+  <si>
+    <t>21 99079-7012</t>
+  </si>
+  <si>
+    <t>Nathiely Duarte</t>
+  </si>
+  <si>
+    <t>21 98215-5453</t>
+  </si>
+  <si>
+    <t>Enviado para 27+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lilian </t>
+  </si>
+  <si>
+    <t>21 98016-1176</t>
+  </si>
+  <si>
+    <t>Michelly Alves</t>
+  </si>
+  <si>
+    <t>21 97951-6269</t>
+  </si>
+  <si>
+    <t>Marcella Da Silva Nunes De Jesus</t>
+  </si>
+  <si>
+    <t>21 96468-4830</t>
+  </si>
+  <si>
+    <t>Geovana Tome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">São Cristóvão </t>
+  </si>
+  <si>
+    <t>21 97637-3582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letícia </t>
+  </si>
+  <si>
+    <t>21 9729-8601</t>
+  </si>
+  <si>
+    <t>27 +</t>
+  </si>
+  <si>
+    <t>Linda Carol Alves Mariano</t>
+  </si>
+  <si>
+    <t>21 99424-6663</t>
+  </si>
+  <si>
+    <t>Rhaylla Rodrigues Sales</t>
+  </si>
+  <si>
+    <t>Itanhangá</t>
+  </si>
+  <si>
+    <t>21 98267-8122</t>
+  </si>
+  <si>
+    <t>Enviada ao GC</t>
+  </si>
+  <si>
+    <t>Sophia Principe</t>
+  </si>
+  <si>
+    <t>21 99401-4521</t>
+  </si>
+  <si>
+    <t>Cássia Rocha</t>
+  </si>
+  <si>
+    <t>21 97593-8999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encaminhada para copacabana </t>
+  </si>
+  <si>
+    <t>Rebeca Marins</t>
+  </si>
+  <si>
+    <t>São Francisco Xavier</t>
+  </si>
+  <si>
+    <t>21 99520-1454</t>
+  </si>
+  <si>
+    <t>Fernanda Norberto De Andrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humaitá </t>
+  </si>
+  <si>
+    <t>21 97205-5760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segunda vez </t>
+  </si>
+  <si>
+    <t>Edineide Souza Moreira</t>
+  </si>
+  <si>
+    <t>21 96553-1399</t>
+  </si>
+  <si>
+    <t>Camila Ferreira</t>
+  </si>
+  <si>
+    <t>21 97966-2493</t>
+  </si>
+  <si>
+    <t>Maria Gerlane Rodrigues Mendes</t>
+  </si>
+  <si>
+    <t>21 98090-0753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">encaminhada ao barrinha </t>
+  </si>
+  <si>
+    <t>Daniele Teixeira Santos</t>
+  </si>
+  <si>
+    <t>21 96629-1310</t>
+  </si>
+  <si>
+    <t>22/03/2026</t>
+  </si>
+  <si>
+    <t>Bruno Mazzola</t>
+  </si>
+  <si>
+    <t>21 99850-1250</t>
+  </si>
+  <si>
+    <t>Cassio Felix</t>
+  </si>
+  <si>
+    <t>21 99781-5295</t>
+  </si>
+  <si>
+    <t>Victor Alexandre</t>
+  </si>
+  <si>
+    <t>21 98818-5173</t>
+  </si>
+  <si>
+    <t>Anderson Do Espírito Santo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vila Isabel </t>
+  </si>
+  <si>
+    <t>21 98120-1912</t>
+  </si>
+  <si>
+    <t>Guilherme Praseres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caju </t>
+  </si>
+  <si>
+    <t>21 98373-4988</t>
+  </si>
+  <si>
+    <t>Charles Aquino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilha Do Governador </t>
+  </si>
+  <si>
+    <t>21 99353-2423</t>
+  </si>
+  <si>
+    <t>Raimundo Jose Da Silva Dourado</t>
+  </si>
+  <si>
+    <t>21 99574-4970</t>
+  </si>
+  <si>
+    <t>João Gabriel De Souza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borges De Medeiros  </t>
+  </si>
+  <si>
+    <t>21 99875-3479</t>
+  </si>
+  <si>
+    <t>Glimari Souza</t>
+  </si>
+  <si>
+    <t>21 99309-1151</t>
+  </si>
+  <si>
+    <t>Celio De Carvalho Mattos</t>
+  </si>
+  <si>
+    <t>21 99663-1965</t>
+  </si>
+  <si>
+    <t>Wilmer Caicedo</t>
+  </si>
+  <si>
+    <t>21 99715-6162</t>
+  </si>
+  <si>
+    <t>Igor Cb</t>
+  </si>
+  <si>
+    <t>Manaus / --</t>
+  </si>
+  <si>
+    <t>92 99123-9150</t>
+  </si>
+  <si>
+    <t>Cosme Patricio</t>
+  </si>
+  <si>
+    <t>Piratininga</t>
+  </si>
+  <si>
+    <t>Niterói  / RJ</t>
+  </si>
+  <si>
+    <t>21 98240-1577</t>
+  </si>
+  <si>
+    <t>Gabriel Henrique</t>
+  </si>
+  <si>
+    <t>35 99935-3868</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>Ruan Paulo Francisco Junior</t>
+  </si>
+  <si>
+    <t>21 99094-3145</t>
+  </si>
+  <si>
+    <t>Alice Lima</t>
+  </si>
+  <si>
+    <t>Bonsucesso</t>
+  </si>
+  <si>
+    <t>21 97249-2686</t>
+  </si>
+  <si>
+    <t>tentando encaminhar para o GC</t>
+  </si>
+  <si>
+    <t>Joyce Muniz</t>
+  </si>
+  <si>
+    <t>Zumbi</t>
+  </si>
+  <si>
+    <t>21 96927-0059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">esta visitando igrejas e ainda não decidiu ficar </t>
+  </si>
+  <si>
+    <t>Miriam Célia</t>
+  </si>
+  <si>
+    <t>Piedade</t>
+  </si>
+  <si>
+    <t>Danielle Da Silva Pinheiro</t>
+  </si>
+  <si>
+    <t>Vila Da Penha</t>
+  </si>
+  <si>
+    <t>21 98251-5931</t>
+  </si>
+  <si>
+    <t>Maite Garrett</t>
+  </si>
+  <si>
+    <t>21 98116-6058</t>
+  </si>
+  <si>
+    <t>encaminhei para larisssa next</t>
+  </si>
+  <si>
+    <t>Nicoly De Sousa Frutuoso</t>
+  </si>
+  <si>
+    <t>21 98188-6862</t>
+  </si>
+  <si>
+    <t>Cristiane Moreira</t>
+  </si>
+  <si>
+    <t>21 99529-1067</t>
+  </si>
+  <si>
+    <t>Maria Rute</t>
+  </si>
+  <si>
+    <t>92 9264-2593</t>
+  </si>
+  <si>
+    <t>Claudia Cristina Da Costa</t>
+  </si>
+  <si>
+    <t>21 99924-4902</t>
+  </si>
+  <si>
+    <t>Encaminhei para a rajana</t>
+  </si>
+  <si>
+    <t>Maria Santos</t>
+  </si>
+  <si>
+    <t>21 96713-8459</t>
+  </si>
+  <si>
+    <t>Cassia Dos Santos</t>
+  </si>
+  <si>
+    <t>21 99305-0951</t>
+  </si>
+  <si>
+    <t>Gabriella Mendes</t>
+  </si>
+  <si>
+    <t>21 96650-8032</t>
+  </si>
+  <si>
+    <t>Rose Pereira</t>
+  </si>
+  <si>
+    <t>21 97403-1238</t>
+  </si>
+  <si>
+    <t>Natália Santana Pires</t>
+  </si>
+  <si>
+    <t>24 98847-4801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esta indo ao universitarios </t>
+  </si>
+  <si>
+    <t>Melissa Cb</t>
+  </si>
+  <si>
+    <t>Amazonas  / AM</t>
+  </si>
+  <si>
+    <t>92 98494-5696</t>
+  </si>
+  <si>
+    <t>Luanda Souza</t>
+  </si>
+  <si>
+    <t>Já esta indo ao GC</t>
+  </si>
+  <si>
+    <t>Izabella Dames</t>
+  </si>
+  <si>
+    <t>22 98122-4995</t>
+  </si>
+  <si>
+    <t>Talita Karla</t>
+  </si>
+  <si>
+    <t>21 99303-1249</t>
+  </si>
+  <si>
+    <t>Segunda vez à frente. Tentando encaminhar ao gc</t>
+  </si>
+  <si>
+    <t>Renielle Cardoso Marinho</t>
+  </si>
+  <si>
+    <t>21 97128-5211</t>
+  </si>
+  <si>
+    <t>Indo ao gc pink</t>
+  </si>
+  <si>
+    <t>Ester Verissimo Azevedo</t>
+  </si>
+  <si>
+    <t>22 99201-2882</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michelle </t>
+  </si>
+  <si>
+    <t>21 98921-0144</t>
+  </si>
+  <si>
+    <t>29/03/2026</t>
+  </si>
+  <si>
+    <t>Gustavo Castelo Branco</t>
+  </si>
+  <si>
+    <t>21 97267-0992</t>
+  </si>
+  <si>
+    <t>Thiago Dos Santos Silva</t>
+  </si>
+  <si>
+    <t>21 97628-5291</t>
+  </si>
+  <si>
+    <t>Carlos Henrique Medeiros</t>
+  </si>
+  <si>
+    <t>21 96993-1589</t>
+  </si>
+  <si>
+    <t>Alex Oliveira</t>
+  </si>
+  <si>
+    <t>21 98845-2222</t>
+  </si>
+  <si>
+    <t>Daniel Nunes</t>
+  </si>
+  <si>
+    <t>21 97581-6230</t>
+  </si>
+  <si>
+    <t>Tauan Faustino Gomes</t>
+  </si>
+  <si>
+    <t>Del Castilho</t>
+  </si>
+  <si>
+    <t>21 97439-8253</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>William Bispo</t>
+  </si>
+  <si>
+    <t>21 99063-2621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bianca </t>
+  </si>
+  <si>
+    <t>21 97899-4676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indo no de casais </t>
+  </si>
+  <si>
+    <t>Sofia Moulin</t>
+  </si>
+  <si>
+    <t>27 99943-0454</t>
+  </si>
+  <si>
+    <t>Esta indo no curso pink</t>
+  </si>
+  <si>
+    <t>Giovanna Santana De Souza</t>
+  </si>
+  <si>
+    <t>Ramos</t>
+  </si>
+  <si>
+    <t>21 99881-2030</t>
+  </si>
+  <si>
+    <t>Tentando encaminhar para o gc</t>
+  </si>
+  <si>
+    <t>Missisleia Fernandes</t>
+  </si>
+  <si>
+    <t>21 99615-1225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Já foi à frente </t>
+  </si>
+  <si>
+    <t>Mariane Scherer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Iguaçu </t>
+  </si>
+  <si>
+    <t>21 99924-8522</t>
+  </si>
+  <si>
+    <t>Encaminhada para o 27+</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Pereira</t>
+  </si>
+  <si>
+    <t>21 98450-9898</t>
+  </si>
+  <si>
+    <t>Renata Ferraz</t>
+  </si>
+  <si>
+    <t>21 99176-4778</t>
+  </si>
+  <si>
+    <t>Corrine Ribeiro De Barros</t>
+  </si>
+  <si>
+    <t>21 97747-9834</t>
+  </si>
+  <si>
+    <t>Victória Silva Fernandes</t>
+  </si>
+  <si>
+    <t>21 97614-0071</t>
+  </si>
+  <si>
+    <t>Ana Magalhães</t>
+  </si>
+  <si>
+    <t>21 97286-9983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encaminhada para o pink </t>
+  </si>
+  <si>
+    <t>Lorrayne Ramos</t>
+  </si>
+  <si>
+    <t>Rio / RJ</t>
+  </si>
+  <si>
+    <t>21 98707-8923</t>
+  </si>
+  <si>
+    <t>Fabiana Thomaz</t>
+  </si>
+  <si>
+    <t>21 99169-8006</t>
   </si>
 </sst>
 </file>
@@ -1997,23 +3209,23 @@
   <dimension ref="A1:P1440"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="33.88671875" customWidth="1"/>
-    <col min="9" max="9" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="26.5546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="51.109375" style="1" customWidth="1"/>
     <col min="15" max="15" width="29.109375" customWidth="1"/>
     <col min="16" max="16" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="56.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="56.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -9917,654 +11129,7688 @@
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M159" s="1"/>
-      <c r="N159"/>
+      <c r="A159" t="s">
+        <v>515</v>
+      </c>
+      <c r="B159" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" t="s">
+        <v>18</v>
+      </c>
+      <c r="D159" t="s">
+        <v>516</v>
+      </c>
+      <c r="E159" t="s">
+        <v>20</v>
+      </c>
+      <c r="F159" t="s">
+        <v>45</v>
+      </c>
+      <c r="G159">
+        <v>32</v>
+      </c>
+      <c r="H159" t="s">
+        <v>36</v>
+      </c>
+      <c r="I159" t="s">
+        <v>33</v>
+      </c>
+      <c r="J159" t="s">
+        <v>517</v>
+      </c>
+      <c r="K159" t="s">
+        <v>25</v>
+      </c>
+      <c r="L159" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M159" t="s">
+        <v>17</v>
+      </c>
+      <c r="N159" t="s">
+        <v>276</v>
+      </c>
+      <c r="O159" t="s">
+        <v>28</v>
+      </c>
+      <c r="P159" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="M160" s="1"/>
-      <c r="N160"/>
-    </row>
-    <row r="161" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M161" s="1"/>
-      <c r="N161"/>
-    </row>
-    <row r="162" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M162" s="1"/>
-      <c r="N162"/>
-    </row>
-    <row r="163" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M163" s="1"/>
-      <c r="N163"/>
-    </row>
-    <row r="164" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M164" s="1"/>
-      <c r="N164"/>
-    </row>
-    <row r="165" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M165" s="1"/>
-      <c r="N165"/>
-    </row>
-    <row r="166" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M166" s="1"/>
-      <c r="N166"/>
-    </row>
-    <row r="167" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M167" s="1"/>
-      <c r="N167"/>
-    </row>
-    <row r="168" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M168" s="1"/>
-      <c r="N168"/>
-    </row>
-    <row r="169" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M169" s="1"/>
-      <c r="N169"/>
-    </row>
-    <row r="170" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M170" s="1"/>
-      <c r="N170"/>
-    </row>
-    <row r="171" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M171" s="1"/>
-      <c r="N171"/>
-    </row>
-    <row r="172" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M172" s="1"/>
-      <c r="N172"/>
-    </row>
-    <row r="173" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M173" s="1"/>
-      <c r="N173"/>
-    </row>
-    <row r="174" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M174" s="1"/>
-      <c r="N174"/>
-    </row>
-    <row r="175" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M175" s="1"/>
-      <c r="N175"/>
-    </row>
-    <row r="176" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M176" s="1"/>
-      <c r="N176"/>
-    </row>
-    <row r="177" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M177" s="1"/>
-      <c r="N177"/>
-    </row>
-    <row r="178" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M178" s="1"/>
-      <c r="N178"/>
-    </row>
-    <row r="179" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M179" s="1"/>
-      <c r="N179"/>
-    </row>
-    <row r="180" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M180" s="1"/>
-      <c r="N180"/>
-    </row>
-    <row r="181" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M181" s="1"/>
-      <c r="N181"/>
-    </row>
-    <row r="182" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M182" s="1"/>
-      <c r="N182"/>
-    </row>
-    <row r="183" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M183" s="1"/>
-      <c r="N183"/>
-    </row>
-    <row r="184" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M184" s="1"/>
-      <c r="N184"/>
-    </row>
-    <row r="185" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M185" s="1"/>
-      <c r="N185"/>
-    </row>
-    <row r="186" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M186" s="1"/>
-      <c r="N186"/>
-    </row>
-    <row r="187" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M187" s="1"/>
-      <c r="N187"/>
-    </row>
-    <row r="188" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M188" s="1"/>
-      <c r="N188"/>
-    </row>
-    <row r="189" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M189" s="1"/>
-      <c r="N189"/>
-    </row>
-    <row r="190" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M190" s="1"/>
-      <c r="N190"/>
-    </row>
-    <row r="191" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M191" s="1"/>
-      <c r="N191"/>
-    </row>
-    <row r="192" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M192" s="1"/>
-      <c r="N192"/>
-    </row>
-    <row r="193" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M193" s="1"/>
-      <c r="N193"/>
-    </row>
-    <row r="194" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M194" s="1"/>
-      <c r="N194"/>
-    </row>
-    <row r="195" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M195" s="1"/>
-      <c r="N195"/>
-    </row>
-    <row r="196" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M196" s="1"/>
-      <c r="N196"/>
-    </row>
-    <row r="197" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M197" s="1"/>
-      <c r="N197"/>
-    </row>
-    <row r="198" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M198" s="1"/>
-      <c r="N198"/>
-    </row>
-    <row r="199" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M199" s="1"/>
-      <c r="N199"/>
-    </row>
-    <row r="200" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M200" s="1"/>
-      <c r="N200"/>
-    </row>
-    <row r="201" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M201" s="1"/>
-      <c r="N201"/>
-    </row>
-    <row r="202" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M202" s="1"/>
-      <c r="N202"/>
-    </row>
-    <row r="203" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M203" s="1"/>
-      <c r="N203"/>
-    </row>
-    <row r="204" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M204" s="1"/>
-      <c r="N204"/>
-    </row>
-    <row r="205" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M205" s="1"/>
-      <c r="N205"/>
-    </row>
-    <row r="206" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M206" s="1"/>
-      <c r="N206"/>
-    </row>
-    <row r="207" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M207" s="1"/>
-      <c r="N207"/>
-    </row>
-    <row r="208" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M208" s="1"/>
-      <c r="N208"/>
-    </row>
-    <row r="209" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M209" s="1"/>
-      <c r="N209"/>
-    </row>
-    <row r="210" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M210" s="1"/>
-      <c r="N210"/>
-    </row>
-    <row r="211" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M211" s="1"/>
-      <c r="N211"/>
-    </row>
-    <row r="212" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M212" s="1"/>
-      <c r="N212"/>
-    </row>
-    <row r="213" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M213" s="1"/>
-      <c r="N213"/>
-    </row>
-    <row r="214" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M214" s="1"/>
-      <c r="N214"/>
-    </row>
-    <row r="215" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M215" s="1"/>
-      <c r="N215"/>
-    </row>
-    <row r="216" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M216" s="1"/>
-      <c r="N216"/>
-    </row>
-    <row r="217" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M217" s="1"/>
-      <c r="N217"/>
-    </row>
-    <row r="218" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M218" s="1"/>
-      <c r="N218"/>
-    </row>
-    <row r="219" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M219" s="1"/>
-      <c r="N219"/>
-    </row>
-    <row r="220" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M220" s="1"/>
-      <c r="N220"/>
-    </row>
-    <row r="221" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M221" s="1"/>
-      <c r="N221"/>
-    </row>
-    <row r="222" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M222" s="1"/>
-      <c r="N222"/>
-    </row>
-    <row r="223" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M223" s="1"/>
-      <c r="N223"/>
-    </row>
-    <row r="224" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M224" s="1"/>
-      <c r="N224"/>
-    </row>
-    <row r="225" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M225" s="1"/>
-      <c r="N225"/>
-    </row>
-    <row r="226" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M226" s="1"/>
-      <c r="N226"/>
-    </row>
-    <row r="227" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M227" s="1"/>
-      <c r="N227"/>
-    </row>
-    <row r="228" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M228" s="1"/>
-      <c r="N228"/>
-    </row>
-    <row r="229" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M229" s="1"/>
-      <c r="N229"/>
-    </row>
-    <row r="230" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M230" s="1"/>
-      <c r="N230"/>
-    </row>
-    <row r="231" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M231" s="1"/>
-      <c r="N231"/>
-    </row>
-    <row r="232" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M232" s="1"/>
-      <c r="N232"/>
-    </row>
-    <row r="233" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M233" s="1"/>
-      <c r="N233"/>
-    </row>
-    <row r="234" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M234" s="1"/>
-      <c r="N234"/>
-    </row>
-    <row r="235" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M235" s="1"/>
-      <c r="N235"/>
-    </row>
-    <row r="236" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M236" s="1"/>
-      <c r="N236"/>
-    </row>
-    <row r="237" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M237" s="1"/>
-      <c r="N237"/>
-    </row>
-    <row r="238" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M238" s="1"/>
-      <c r="N238"/>
-    </row>
-    <row r="239" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M239" s="1"/>
-      <c r="N239"/>
-    </row>
-    <row r="240" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M240" s="1"/>
-      <c r="N240"/>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M241" s="1"/>
-      <c r="N241"/>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M242" s="1"/>
-      <c r="N242"/>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M243" s="1"/>
-      <c r="N243"/>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M244" s="1"/>
-      <c r="N244"/>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M245" s="1"/>
-      <c r="N245"/>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M246" s="1"/>
-      <c r="N246"/>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A247" s="6"/>
-      <c r="M247" s="1"/>
-      <c r="N247"/>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A248" s="6"/>
-      <c r="M248" s="1"/>
-      <c r="N248"/>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A249" s="5"/>
-      <c r="M249" s="1"/>
-      <c r="N249"/>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M250" s="1"/>
-      <c r="N250"/>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M251" s="1"/>
-      <c r="N251"/>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M252" s="1"/>
-      <c r="N252"/>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M253" s="1"/>
-      <c r="N253"/>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M254" s="1"/>
-      <c r="N254"/>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M255" s="1"/>
-      <c r="N255"/>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M256" s="1"/>
-      <c r="N256"/>
-    </row>
-    <row r="257" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M257" s="1"/>
-      <c r="N257"/>
-    </row>
-    <row r="258" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M258" s="1"/>
-      <c r="N258"/>
-    </row>
-    <row r="259" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M259" s="1"/>
-      <c r="N259"/>
-    </row>
-    <row r="260" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M260" s="1"/>
-      <c r="N260"/>
-    </row>
-    <row r="261" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M261" s="1"/>
-      <c r="N261"/>
-    </row>
-    <row r="262" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M262" s="1"/>
-      <c r="N262"/>
-    </row>
-    <row r="263" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M263" s="1"/>
-      <c r="N263"/>
-    </row>
-    <row r="264" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M264" s="1"/>
-      <c r="N264"/>
-    </row>
-    <row r="265" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M265" s="1"/>
-      <c r="N265"/>
-    </row>
-    <row r="266" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M266" s="1"/>
-      <c r="N266"/>
-    </row>
-    <row r="267" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M267" s="1"/>
-      <c r="N267"/>
-    </row>
-    <row r="268" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M268" s="1"/>
-      <c r="N268"/>
-    </row>
-    <row r="269" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M269" s="1"/>
-      <c r="N269"/>
-    </row>
-    <row r="270" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M270" s="1"/>
-      <c r="N270"/>
-    </row>
-    <row r="271" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M271" s="1"/>
-      <c r="N271"/>
-    </row>
-    <row r="272" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M272" s="1"/>
-      <c r="N272"/>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M273" s="1"/>
-      <c r="N273"/>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M274" s="1"/>
-      <c r="N274"/>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M275" s="1"/>
-      <c r="N275"/>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M276" s="1"/>
-      <c r="N276"/>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M277" s="1"/>
-      <c r="N277"/>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M278" s="1"/>
-      <c r="N278"/>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M279" s="1"/>
-      <c r="N279"/>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M280" s="1"/>
-      <c r="N280"/>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M281" s="1"/>
-      <c r="N281"/>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M282" s="1"/>
-      <c r="N282"/>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M283" s="1"/>
-      <c r="N283"/>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M284" s="1"/>
-      <c r="N284"/>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M285" s="1"/>
-      <c r="N285"/>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M286" s="1"/>
-      <c r="N286"/>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M287" s="1"/>
-      <c r="N287"/>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A288" s="7"/>
-      <c r="M288" s="1"/>
-      <c r="N288"/>
-    </row>
-    <row r="289" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M289" s="1"/>
-      <c r="N289"/>
-    </row>
-    <row r="290" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M290" s="1"/>
-      <c r="N290"/>
-    </row>
-    <row r="291" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M291" s="1"/>
-      <c r="N291"/>
-    </row>
-    <row r="292" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M292" s="1"/>
-      <c r="N292"/>
-    </row>
-    <row r="293" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M293" s="1"/>
-      <c r="N293"/>
-    </row>
-    <row r="294" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M294" s="1"/>
-      <c r="N294"/>
-    </row>
-    <row r="295" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M295" s="1"/>
-      <c r="N295"/>
-    </row>
-    <row r="296" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M296" s="1"/>
-      <c r="N296"/>
-    </row>
-    <row r="297" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M297" s="1"/>
-      <c r="N297"/>
-    </row>
-    <row r="298" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M298" s="1"/>
-      <c r="N298"/>
-    </row>
-    <row r="299" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M299" s="1"/>
-      <c r="N299"/>
-    </row>
-    <row r="300" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M300" s="1"/>
-      <c r="N300"/>
-    </row>
-    <row r="301" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M301" s="1"/>
-      <c r="N301"/>
-    </row>
-    <row r="302" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M302" s="1"/>
-      <c r="N302"/>
-    </row>
-    <row r="303" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M303" s="1"/>
-      <c r="N303"/>
-    </row>
-    <row r="304" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M304" s="1"/>
-      <c r="N304"/>
-    </row>
-    <row r="305" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M305" s="1"/>
-      <c r="N305"/>
-    </row>
-    <row r="306" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M306" s="1"/>
-      <c r="N306"/>
-    </row>
-    <row r="307" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M307" s="1"/>
-      <c r="N307"/>
-    </row>
-    <row r="308" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M308" s="1"/>
-      <c r="N308"/>
-    </row>
-    <row r="309" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M309" s="1"/>
-      <c r="N309"/>
-    </row>
-    <row r="310" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M310" s="1"/>
-      <c r="N310"/>
-    </row>
-    <row r="311" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M311" s="1"/>
-      <c r="N311"/>
-    </row>
-    <row r="312" spans="13:14" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>515</v>
+      </c>
+      <c r="B160" t="s">
+        <v>407</v>
+      </c>
+      <c r="C160" t="s">
+        <v>65</v>
+      </c>
+      <c r="D160" t="s">
+        <v>518</v>
+      </c>
+      <c r="E160" t="s">
+        <v>20</v>
+      </c>
+      <c r="F160" t="s">
+        <v>388</v>
+      </c>
+      <c r="G160">
+        <v>40</v>
+      </c>
+      <c r="H160" t="s">
+        <v>519</v>
+      </c>
+      <c r="I160" t="s">
+        <v>33</v>
+      </c>
+      <c r="J160" t="s">
+        <v>520</v>
+      </c>
+      <c r="K160" t="s">
+        <v>25</v>
+      </c>
+      <c r="L160" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M160" t="s">
+        <v>17</v>
+      </c>
+      <c r="N160" t="s">
+        <v>276</v>
+      </c>
+      <c r="O160" t="s">
+        <v>28</v>
+      </c>
+      <c r="P160" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>515</v>
+      </c>
+      <c r="B161" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" t="s">
+        <v>38</v>
+      </c>
+      <c r="D161" t="s">
+        <v>521</v>
+      </c>
+      <c r="E161" t="s">
+        <v>20</v>
+      </c>
+      <c r="F161" t="s">
+        <v>31</v>
+      </c>
+      <c r="G161">
+        <v>44</v>
+      </c>
+      <c r="H161" t="s">
+        <v>53</v>
+      </c>
+      <c r="I161" t="s">
+        <v>33</v>
+      </c>
+      <c r="J161" t="s">
+        <v>522</v>
+      </c>
+      <c r="K161" t="s">
+        <v>25</v>
+      </c>
+      <c r="L161" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M161" t="s">
+        <v>289</v>
+      </c>
+      <c r="N161" t="s">
+        <v>276</v>
+      </c>
+      <c r="O161" t="s">
+        <v>28</v>
+      </c>
+      <c r="P161" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>515</v>
+      </c>
+      <c r="B162" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" t="s">
+        <v>65</v>
+      </c>
+      <c r="D162" t="s">
+        <v>523</v>
+      </c>
+      <c r="E162" t="s">
+        <v>20</v>
+      </c>
+      <c r="F162" t="s">
+        <v>31</v>
+      </c>
+      <c r="G162">
+        <v>37</v>
+      </c>
+      <c r="H162" t="s">
+        <v>524</v>
+      </c>
+      <c r="I162" t="s">
+        <v>525</v>
+      </c>
+      <c r="J162" t="s">
+        <v>526</v>
+      </c>
+      <c r="K162" t="s">
+        <v>25</v>
+      </c>
+      <c r="L162" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M162" t="s">
+        <v>289</v>
+      </c>
+      <c r="N162" t="s">
+        <v>276</v>
+      </c>
+      <c r="O162" t="s">
+        <v>28</v>
+      </c>
+      <c r="P162" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>515</v>
+      </c>
+      <c r="B163" t="s">
+        <v>17</v>
+      </c>
+      <c r="C163" t="s">
+        <v>18</v>
+      </c>
+      <c r="D163" t="s">
+        <v>527</v>
+      </c>
+      <c r="E163" t="s">
+        <v>20</v>
+      </c>
+      <c r="F163" t="s">
+        <v>45</v>
+      </c>
+      <c r="G163">
+        <v>30</v>
+      </c>
+      <c r="H163" t="s">
+        <v>528</v>
+      </c>
+      <c r="I163" t="s">
+        <v>179</v>
+      </c>
+      <c r="J163" t="s">
+        <v>529</v>
+      </c>
+      <c r="K163" t="s">
+        <v>25</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M163" t="s">
+        <v>17</v>
+      </c>
+      <c r="N163" t="s">
+        <v>276</v>
+      </c>
+      <c r="O163" t="s">
+        <v>28</v>
+      </c>
+      <c r="P163" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>515</v>
+      </c>
+      <c r="B164" t="s">
+        <v>17</v>
+      </c>
+      <c r="C164" t="s">
+        <v>18</v>
+      </c>
+      <c r="D164" t="s">
+        <v>530</v>
+      </c>
+      <c r="E164" t="s">
+        <v>20</v>
+      </c>
+      <c r="F164" t="s">
+        <v>45</v>
+      </c>
+      <c r="G164">
+        <v>30</v>
+      </c>
+      <c r="H164" t="s">
+        <v>531</v>
+      </c>
+      <c r="I164" t="s">
+        <v>89</v>
+      </c>
+      <c r="J164" t="s">
+        <v>532</v>
+      </c>
+      <c r="K164" t="s">
+        <v>25</v>
+      </c>
+      <c r="L164" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M164" t="s">
+        <v>17</v>
+      </c>
+      <c r="N164" t="s">
+        <v>276</v>
+      </c>
+      <c r="O164" t="s">
+        <v>28</v>
+      </c>
+      <c r="P164" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>515</v>
+      </c>
+      <c r="B165" t="s">
+        <v>17</v>
+      </c>
+      <c r="C165" t="s">
+        <v>18</v>
+      </c>
+      <c r="D165" t="s">
+        <v>533</v>
+      </c>
+      <c r="E165" t="s">
+        <v>20</v>
+      </c>
+      <c r="F165" t="s">
+        <v>45</v>
+      </c>
+      <c r="G165">
+        <v>30</v>
+      </c>
+      <c r="H165" t="s">
+        <v>102</v>
+      </c>
+      <c r="I165" t="s">
+        <v>89</v>
+      </c>
+      <c r="J165" t="s">
+        <v>534</v>
+      </c>
+      <c r="K165" t="s">
+        <v>25</v>
+      </c>
+      <c r="L165" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M165" t="s">
+        <v>17</v>
+      </c>
+      <c r="N165" t="s">
+        <v>276</v>
+      </c>
+      <c r="O165" t="s">
+        <v>25</v>
+      </c>
+      <c r="P165" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>515</v>
+      </c>
+      <c r="B166" t="s">
+        <v>17</v>
+      </c>
+      <c r="C166" t="s">
+        <v>18</v>
+      </c>
+      <c r="D166" t="s">
+        <v>535</v>
+      </c>
+      <c r="E166" t="s">
+        <v>20</v>
+      </c>
+      <c r="F166" t="s">
+        <v>45</v>
+      </c>
+      <c r="G166">
+        <v>30</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" t="s">
+        <v>179</v>
+      </c>
+      <c r="J166" t="s">
+        <v>536</v>
+      </c>
+      <c r="K166" t="s">
+        <v>25</v>
+      </c>
+      <c r="L166" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M166" t="s">
+        <v>42</v>
+      </c>
+      <c r="N166" t="s">
+        <v>276</v>
+      </c>
+      <c r="O166" t="s">
+        <v>25</v>
+      </c>
+      <c r="P166" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>515</v>
+      </c>
+      <c r="B167" t="s">
+        <v>17</v>
+      </c>
+      <c r="C167" t="s">
+        <v>38</v>
+      </c>
+      <c r="D167" t="s">
+        <v>537</v>
+      </c>
+      <c r="E167" t="s">
+        <v>20</v>
+      </c>
+      <c r="F167" t="s">
+        <v>21</v>
+      </c>
+      <c r="G167">
+        <v>65</v>
+      </c>
+      <c r="H167" t="s">
+        <v>528</v>
+      </c>
+      <c r="I167" t="s">
+        <v>179</v>
+      </c>
+      <c r="J167" t="s">
+        <v>538</v>
+      </c>
+      <c r="K167" t="s">
+        <v>25</v>
+      </c>
+      <c r="L167" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M167" t="s">
+        <v>42</v>
+      </c>
+      <c r="N167" t="s">
+        <v>276</v>
+      </c>
+      <c r="O167" t="s">
+        <v>25</v>
+      </c>
+      <c r="P167" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>539</v>
+      </c>
+      <c r="B168" t="s">
+        <v>17</v>
+      </c>
+      <c r="C168" t="s">
+        <v>65</v>
+      </c>
+      <c r="D168" t="s">
+        <v>540</v>
+      </c>
+      <c r="E168" t="s">
+        <v>20</v>
+      </c>
+      <c r="F168" t="s">
+        <v>45</v>
+      </c>
+      <c r="G168">
+        <v>35</v>
+      </c>
+      <c r="H168" t="s">
+        <v>541</v>
+      </c>
+      <c r="I168" t="s">
+        <v>542</v>
+      </c>
+      <c r="J168" t="s">
+        <v>543</v>
+      </c>
+      <c r="K168" t="s">
+        <v>25</v>
+      </c>
+      <c r="L168" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M168" t="s">
+        <v>42</v>
+      </c>
+      <c r="N168" t="s">
+        <v>276</v>
+      </c>
+      <c r="O168" t="s">
+        <v>28</v>
+      </c>
+      <c r="P168" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>515</v>
+      </c>
+      <c r="B169" t="s">
+        <v>407</v>
+      </c>
+      <c r="C169" t="s">
+        <v>18</v>
+      </c>
+      <c r="D169" t="s">
+        <v>544</v>
+      </c>
+      <c r="E169" t="s">
+        <v>60</v>
+      </c>
+      <c r="F169" t="s">
+        <v>45</v>
+      </c>
+      <c r="G169">
+        <v>30</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" t="s">
+        <v>54</v>
+      </c>
+      <c r="J169" t="s">
+        <v>545</v>
+      </c>
+      <c r="K169" t="s">
+        <v>25</v>
+      </c>
+      <c r="L169" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M169" t="s">
+        <v>17</v>
+      </c>
+      <c r="N169" t="s">
+        <v>303</v>
+      </c>
+      <c r="O169" t="s">
+        <v>28</v>
+      </c>
+      <c r="P169" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>515</v>
+      </c>
+      <c r="B170" t="s">
+        <v>17</v>
+      </c>
+      <c r="C170" t="s">
+        <v>65</v>
+      </c>
+      <c r="D170" t="s">
+        <v>547</v>
+      </c>
+      <c r="E170" t="s">
+        <v>60</v>
+      </c>
+      <c r="F170" t="s">
+        <v>45</v>
+      </c>
+      <c r="G170">
+        <v>56</v>
+      </c>
+      <c r="H170" t="s">
+        <v>36</v>
+      </c>
+      <c r="I170" t="s">
+        <v>33</v>
+      </c>
+      <c r="J170" t="s">
+        <v>548</v>
+      </c>
+      <c r="K170" t="s">
+        <v>25</v>
+      </c>
+      <c r="L170" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M170" t="s">
+        <v>42</v>
+      </c>
+      <c r="N170" t="s">
+        <v>303</v>
+      </c>
+      <c r="O170" t="s">
+        <v>28</v>
+      </c>
+      <c r="P170" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>515</v>
+      </c>
+      <c r="B171" t="s">
+        <v>17</v>
+      </c>
+      <c r="C171" t="s">
+        <v>65</v>
+      </c>
+      <c r="D171" t="s">
+        <v>549</v>
+      </c>
+      <c r="E171" t="s">
+        <v>60</v>
+      </c>
+      <c r="F171" t="s">
+        <v>45</v>
+      </c>
+      <c r="G171">
+        <v>37</v>
+      </c>
+      <c r="H171" t="s">
+        <v>550</v>
+      </c>
+      <c r="I171" t="s">
+        <v>54</v>
+      </c>
+      <c r="J171" t="s">
+        <v>551</v>
+      </c>
+      <c r="K171" t="s">
+        <v>25</v>
+      </c>
+      <c r="L171" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M171" t="s">
+        <v>17</v>
+      </c>
+      <c r="N171" t="s">
+        <v>303</v>
+      </c>
+      <c r="O171" t="s">
+        <v>28</v>
+      </c>
+      <c r="P171" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>515</v>
+      </c>
+      <c r="B172" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" t="s">
+        <v>38</v>
+      </c>
+      <c r="D172" t="s">
+        <v>552</v>
+      </c>
+      <c r="E172" t="s">
+        <v>60</v>
+      </c>
+      <c r="F172" t="s">
+        <v>31</v>
+      </c>
+      <c r="G172">
+        <v>45</v>
+      </c>
+      <c r="H172" t="s">
+        <v>553</v>
+      </c>
+      <c r="I172" t="s">
+        <v>33</v>
+      </c>
+      <c r="J172" t="s">
+        <v>554</v>
+      </c>
+      <c r="K172" t="s">
+        <v>25</v>
+      </c>
+      <c r="L172" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M172" t="s">
+        <v>42</v>
+      </c>
+      <c r="N172" t="s">
+        <v>555</v>
+      </c>
+      <c r="O172" t="s">
+        <v>25</v>
+      </c>
+      <c r="P172" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>515</v>
+      </c>
+      <c r="B173" t="s">
+        <v>17</v>
+      </c>
+      <c r="C173" t="s">
+        <v>38</v>
+      </c>
+      <c r="D173" t="s">
+        <v>556</v>
+      </c>
+      <c r="E173" t="s">
+        <v>60</v>
+      </c>
+      <c r="F173" t="s">
+        <v>31</v>
+      </c>
+      <c r="G173">
+        <v>30</v>
+      </c>
+      <c r="H173" t="s">
+        <v>557</v>
+      </c>
+      <c r="I173" t="s">
+        <v>54</v>
+      </c>
+      <c r="J173" t="s">
+        <v>558</v>
+      </c>
+      <c r="K173" t="s">
+        <v>25</v>
+      </c>
+      <c r="L173" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M173" t="s">
+        <v>42</v>
+      </c>
+      <c r="N173" t="s">
+        <v>63</v>
+      </c>
+      <c r="O173" t="s">
+        <v>25</v>
+      </c>
+      <c r="P173" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>515</v>
+      </c>
+      <c r="B174" t="s">
+        <v>17</v>
+      </c>
+      <c r="C174" t="s">
+        <v>18</v>
+      </c>
+      <c r="D174" t="s">
+        <v>559</v>
+      </c>
+      <c r="E174" t="s">
+        <v>60</v>
+      </c>
+      <c r="F174" t="s">
+        <v>45</v>
+      </c>
+      <c r="G174">
+        <v>40</v>
+      </c>
+      <c r="H174" t="s">
+        <v>77</v>
+      </c>
+      <c r="I174" t="s">
+        <v>179</v>
+      </c>
+      <c r="J174" t="s">
+        <v>560</v>
+      </c>
+      <c r="K174" t="s">
+        <v>25</v>
+      </c>
+      <c r="L174" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M174" t="s">
+        <v>17</v>
+      </c>
+      <c r="N174" t="s">
+        <v>303</v>
+      </c>
+      <c r="O174" t="s">
+        <v>28</v>
+      </c>
+      <c r="P174" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>515</v>
+      </c>
+      <c r="B175" t="s">
+        <v>17</v>
+      </c>
+      <c r="C175" t="s">
+        <v>38</v>
+      </c>
+      <c r="D175" t="s">
+        <v>561</v>
+      </c>
+      <c r="E175" t="s">
+        <v>60</v>
+      </c>
+      <c r="F175" t="s">
+        <v>45</v>
+      </c>
+      <c r="G175">
+        <v>32</v>
+      </c>
+      <c r="H175" t="s">
+        <v>562</v>
+      </c>
+      <c r="I175" t="s">
+        <v>563</v>
+      </c>
+      <c r="J175" t="s">
+        <v>564</v>
+      </c>
+      <c r="K175" t="s">
+        <v>25</v>
+      </c>
+      <c r="L175" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M175" t="s">
+        <v>42</v>
+      </c>
+      <c r="N175" t="s">
+        <v>303</v>
+      </c>
+      <c r="O175" t="s">
+        <v>28</v>
+      </c>
+      <c r="P175" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>515</v>
+      </c>
+      <c r="B176" t="s">
+        <v>17</v>
+      </c>
+      <c r="C176" t="s">
+        <v>38</v>
+      </c>
+      <c r="D176" t="s">
+        <v>565</v>
+      </c>
+      <c r="E176" t="s">
+        <v>60</v>
+      </c>
+      <c r="F176" t="s">
+        <v>45</v>
+      </c>
+      <c r="G176">
+        <v>36</v>
+      </c>
+      <c r="H176" t="s">
+        <v>510</v>
+      </c>
+      <c r="I176" t="s">
+        <v>33</v>
+      </c>
+      <c r="J176" t="s">
+        <v>566</v>
+      </c>
+      <c r="K176" t="s">
+        <v>25</v>
+      </c>
+      <c r="L176" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M176" t="s">
+        <v>17</v>
+      </c>
+      <c r="N176" t="s">
+        <v>567</v>
+      </c>
+      <c r="O176" t="s">
+        <v>25</v>
+      </c>
+      <c r="P176" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>515</v>
+      </c>
+      <c r="B177" t="s">
+        <v>17</v>
+      </c>
+      <c r="C177" t="s">
+        <v>38</v>
+      </c>
+      <c r="D177" t="s">
+        <v>568</v>
+      </c>
+      <c r="E177" t="s">
+        <v>60</v>
+      </c>
+      <c r="F177" t="s">
+        <v>388</v>
+      </c>
+      <c r="G177">
+        <v>34</v>
+      </c>
+      <c r="H177" t="s">
+        <v>528</v>
+      </c>
+      <c r="I177" t="s">
+        <v>33</v>
+      </c>
+      <c r="J177" t="s">
+        <v>569</v>
+      </c>
+      <c r="K177" t="s">
+        <v>25</v>
+      </c>
+      <c r="L177" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M177" t="s">
+        <v>17</v>
+      </c>
+      <c r="N177" t="s">
+        <v>303</v>
+      </c>
+      <c r="O177" t="s">
+        <v>28</v>
+      </c>
+      <c r="P177" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>515</v>
+      </c>
+      <c r="B178" t="s">
+        <v>17</v>
+      </c>
+      <c r="C178" t="s">
+        <v>65</v>
+      </c>
+      <c r="D178" t="s">
+        <v>570</v>
+      </c>
+      <c r="E178" t="s">
+        <v>60</v>
+      </c>
+      <c r="F178" t="s">
+        <v>31</v>
+      </c>
+      <c r="G178">
+        <v>34</v>
+      </c>
+      <c r="H178" t="s">
+        <v>524</v>
+      </c>
+      <c r="I178" t="s">
+        <v>525</v>
+      </c>
+      <c r="J178" t="s">
+        <v>571</v>
+      </c>
+      <c r="K178" t="s">
+        <v>25</v>
+      </c>
+      <c r="L178" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M178" t="s">
+        <v>289</v>
+      </c>
+      <c r="N178" t="s">
+        <v>303</v>
+      </c>
+      <c r="O178" t="s">
+        <v>28</v>
+      </c>
+      <c r="P178" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>515</v>
+      </c>
+      <c r="B179" t="s">
+        <v>17</v>
+      </c>
+      <c r="C179" t="s">
+        <v>18</v>
+      </c>
+      <c r="D179" t="s">
+        <v>572</v>
+      </c>
+      <c r="E179" t="s">
+        <v>60</v>
+      </c>
+      <c r="F179" t="s">
+        <v>31</v>
+      </c>
+      <c r="G179">
+        <v>27</v>
+      </c>
+      <c r="H179" t="s">
+        <v>573</v>
+      </c>
+      <c r="I179" t="s">
+        <v>33</v>
+      </c>
+      <c r="J179" t="s">
+        <v>574</v>
+      </c>
+      <c r="K179" t="s">
+        <v>25</v>
+      </c>
+      <c r="L179" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M179" t="s">
+        <v>17</v>
+      </c>
+      <c r="N179" t="s">
+        <v>303</v>
+      </c>
+      <c r="O179" t="s">
+        <v>28</v>
+      </c>
+      <c r="P179" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>515</v>
+      </c>
+      <c r="B180" t="s">
+        <v>17</v>
+      </c>
+      <c r="C180" t="s">
+        <v>38</v>
+      </c>
+      <c r="D180" t="s">
+        <v>576</v>
+      </c>
+      <c r="E180" t="s">
+        <v>60</v>
+      </c>
+      <c r="F180" t="s">
+        <v>31</v>
+      </c>
+      <c r="G180">
+        <v>38</v>
+      </c>
+      <c r="H180" t="s">
+        <v>53</v>
+      </c>
+      <c r="I180" t="s">
+        <v>33</v>
+      </c>
+      <c r="J180" t="s">
+        <v>577</v>
+      </c>
+      <c r="K180" t="s">
+        <v>25</v>
+      </c>
+      <c r="L180" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M180" t="s">
+        <v>42</v>
+      </c>
+      <c r="N180" t="s">
+        <v>303</v>
+      </c>
+      <c r="O180" t="s">
+        <v>28</v>
+      </c>
+      <c r="P180" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>515</v>
+      </c>
+      <c r="B181" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" t="s">
+        <v>65</v>
+      </c>
+      <c r="D181" t="s">
+        <v>578</v>
+      </c>
+      <c r="E181" t="s">
+        <v>60</v>
+      </c>
+      <c r="F181" t="s">
+        <v>45</v>
+      </c>
+      <c r="G181">
+        <v>34</v>
+      </c>
+      <c r="H181" t="s">
+        <v>7</v>
+      </c>
+      <c r="I181" t="s">
+        <v>579</v>
+      </c>
+      <c r="J181" t="s">
+        <v>580</v>
+      </c>
+      <c r="K181" t="s">
+        <v>25</v>
+      </c>
+      <c r="L181" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M181" t="s">
+        <v>42</v>
+      </c>
+      <c r="N181" t="s">
+        <v>581</v>
+      </c>
+      <c r="O181" t="s">
+        <v>172</v>
+      </c>
+      <c r="P181" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>515</v>
+      </c>
+      <c r="B182" t="s">
+        <v>17</v>
+      </c>
+      <c r="C182" t="s">
+        <v>38</v>
+      </c>
+      <c r="D182" t="s">
+        <v>582</v>
+      </c>
+      <c r="E182" t="s">
+        <v>60</v>
+      </c>
+      <c r="F182" t="s">
+        <v>45</v>
+      </c>
+      <c r="G182">
+        <v>30</v>
+      </c>
+      <c r="H182" t="s">
+        <v>92</v>
+      </c>
+      <c r="I182" t="s">
+        <v>54</v>
+      </c>
+      <c r="J182" t="s">
+        <v>583</v>
+      </c>
+      <c r="K182" t="s">
+        <v>25</v>
+      </c>
+      <c r="L182" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M182" t="s">
+        <v>42</v>
+      </c>
+      <c r="N182" t="s">
+        <v>303</v>
+      </c>
+      <c r="O182" t="s">
+        <v>28</v>
+      </c>
+      <c r="P182" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>515</v>
+      </c>
+      <c r="B183" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" t="s">
+        <v>38</v>
+      </c>
+      <c r="D183" t="s">
+        <v>584</v>
+      </c>
+      <c r="E183" t="s">
+        <v>60</v>
+      </c>
+      <c r="F183" t="s">
+        <v>45</v>
+      </c>
+      <c r="G183">
+        <v>20</v>
+      </c>
+      <c r="H183" t="s">
+        <v>585</v>
+      </c>
+      <c r="I183" t="s">
+        <v>33</v>
+      </c>
+      <c r="J183" t="s">
+        <v>586</v>
+      </c>
+      <c r="K183" t="s">
+        <v>25</v>
+      </c>
+      <c r="L183" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M183" t="s">
+        <v>42</v>
+      </c>
+      <c r="N183" t="s">
+        <v>303</v>
+      </c>
+      <c r="O183" t="s">
+        <v>28</v>
+      </c>
+      <c r="P183" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>515</v>
+      </c>
+      <c r="B184" t="s">
+        <v>17</v>
+      </c>
+      <c r="C184" t="s">
+        <v>38</v>
+      </c>
+      <c r="D184" t="s">
+        <v>587</v>
+      </c>
+      <c r="E184" t="s">
+        <v>60</v>
+      </c>
+      <c r="F184" t="s">
+        <v>45</v>
+      </c>
+      <c r="G184">
+        <v>30</v>
+      </c>
+      <c r="H184" t="s">
+        <v>453</v>
+      </c>
+      <c r="I184" t="s">
+        <v>33</v>
+      </c>
+      <c r="J184" t="s">
+        <v>588</v>
+      </c>
+      <c r="K184" t="s">
+        <v>25</v>
+      </c>
+      <c r="L184" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M184" t="s">
+        <v>17</v>
+      </c>
+      <c r="N184" t="s">
+        <v>303</v>
+      </c>
+      <c r="O184" t="s">
+        <v>28</v>
+      </c>
+      <c r="P184" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>515</v>
+      </c>
+      <c r="B185" t="s">
+        <v>17</v>
+      </c>
+      <c r="C185" t="s">
+        <v>18</v>
+      </c>
+      <c r="D185" t="s">
+        <v>589</v>
+      </c>
+      <c r="E185" t="s">
+        <v>60</v>
+      </c>
+      <c r="F185" t="s">
+        <v>45</v>
+      </c>
+      <c r="G185">
+        <v>30</v>
+      </c>
+      <c r="H185" t="s">
+        <v>183</v>
+      </c>
+      <c r="I185" t="s">
+        <v>54</v>
+      </c>
+      <c r="J185" t="s">
+        <v>590</v>
+      </c>
+      <c r="K185" t="s">
+        <v>25</v>
+      </c>
+      <c r="L185" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M185" t="s">
+        <v>17</v>
+      </c>
+      <c r="N185" t="s">
+        <v>581</v>
+      </c>
+      <c r="O185" t="s">
+        <v>25</v>
+      </c>
+      <c r="P185" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>515</v>
+      </c>
+      <c r="B186" t="s">
+        <v>17</v>
+      </c>
+      <c r="C186" t="s">
+        <v>18</v>
+      </c>
+      <c r="D186" t="s">
+        <v>591</v>
+      </c>
+      <c r="E186" t="s">
+        <v>60</v>
+      </c>
+      <c r="F186" t="s">
+        <v>31</v>
+      </c>
+      <c r="G186">
+        <v>36</v>
+      </c>
+      <c r="H186" t="s">
+        <v>17</v>
+      </c>
+      <c r="I186" t="s">
+        <v>54</v>
+      </c>
+      <c r="J186" t="s">
+        <v>592</v>
+      </c>
+      <c r="K186" t="s">
+        <v>25</v>
+      </c>
+      <c r="L186" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M186" t="s">
+        <v>42</v>
+      </c>
+      <c r="N186" t="s">
+        <v>303</v>
+      </c>
+      <c r="O186" t="s">
+        <v>28</v>
+      </c>
+      <c r="P186" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>539</v>
+      </c>
+      <c r="B187" t="s">
+        <v>17</v>
+      </c>
+      <c r="C187" t="s">
+        <v>18</v>
+      </c>
+      <c r="D187" t="s">
+        <v>593</v>
+      </c>
+      <c r="E187" t="s">
+        <v>60</v>
+      </c>
+      <c r="F187" t="s">
+        <v>45</v>
+      </c>
+      <c r="G187">
+        <v>30</v>
+      </c>
+      <c r="H187" t="s">
+        <v>321</v>
+      </c>
+      <c r="I187" t="s">
+        <v>54</v>
+      </c>
+      <c r="J187" t="s">
+        <v>594</v>
+      </c>
+      <c r="K187" t="s">
+        <v>25</v>
+      </c>
+      <c r="L187" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M187" t="s">
+        <v>17</v>
+      </c>
+      <c r="N187" t="s">
+        <v>501</v>
+      </c>
+      <c r="O187" t="s">
+        <v>172</v>
+      </c>
+      <c r="P187" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>539</v>
+      </c>
+      <c r="B188" t="s">
+        <v>359</v>
+      </c>
+      <c r="C188" t="s">
+        <v>18</v>
+      </c>
+      <c r="D188" t="s">
+        <v>596</v>
+      </c>
+      <c r="E188" t="s">
+        <v>60</v>
+      </c>
+      <c r="F188" t="s">
+        <v>45</v>
+      </c>
+      <c r="G188">
+        <v>30</v>
+      </c>
+      <c r="H188" t="s">
+        <v>40</v>
+      </c>
+      <c r="I188" t="s">
+        <v>33</v>
+      </c>
+      <c r="J188" t="s">
+        <v>597</v>
+      </c>
+      <c r="K188" t="s">
+        <v>25</v>
+      </c>
+      <c r="L188" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M188" t="s">
+        <v>42</v>
+      </c>
+      <c r="N188" t="s">
+        <v>303</v>
+      </c>
+      <c r="O188" t="s">
+        <v>28</v>
+      </c>
+      <c r="P188" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>539</v>
+      </c>
+      <c r="B189" t="s">
+        <v>17</v>
+      </c>
+      <c r="C189" t="s">
+        <v>65</v>
+      </c>
+      <c r="D189" t="s">
+        <v>598</v>
+      </c>
+      <c r="E189" t="s">
+        <v>60</v>
+      </c>
+      <c r="F189" t="s">
+        <v>45</v>
+      </c>
+      <c r="G189">
+        <v>30</v>
+      </c>
+      <c r="H189" t="s">
+        <v>115</v>
+      </c>
+      <c r="I189" t="s">
+        <v>54</v>
+      </c>
+      <c r="J189" t="s">
+        <v>599</v>
+      </c>
+      <c r="K189" t="s">
+        <v>25</v>
+      </c>
+      <c r="L189" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M189" t="s">
+        <v>17</v>
+      </c>
+      <c r="N189" t="s">
+        <v>501</v>
+      </c>
+      <c r="O189" t="s">
+        <v>172</v>
+      </c>
+      <c r="P189" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>539</v>
+      </c>
+      <c r="B190" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" t="s">
+        <v>38</v>
+      </c>
+      <c r="D190" t="s">
+        <v>600</v>
+      </c>
+      <c r="E190" t="s">
+        <v>60</v>
+      </c>
+      <c r="F190" t="s">
+        <v>31</v>
+      </c>
+      <c r="G190">
+        <v>46</v>
+      </c>
+      <c r="H190" t="s">
+        <v>321</v>
+      </c>
+      <c r="I190" t="s">
+        <v>54</v>
+      </c>
+      <c r="J190" t="s">
+        <v>601</v>
+      </c>
+      <c r="K190" t="s">
+        <v>25</v>
+      </c>
+      <c r="L190" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M190" t="s">
+        <v>17</v>
+      </c>
+      <c r="N190" t="s">
+        <v>303</v>
+      </c>
+      <c r="O190" t="s">
+        <v>28</v>
+      </c>
+      <c r="P190" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>539</v>
+      </c>
+      <c r="B191" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" t="s">
+        <v>65</v>
+      </c>
+      <c r="D191" t="s">
+        <v>602</v>
+      </c>
+      <c r="E191" t="s">
+        <v>60</v>
+      </c>
+      <c r="F191" t="s">
+        <v>45</v>
+      </c>
+      <c r="G191">
+        <v>45</v>
+      </c>
+      <c r="H191" t="s">
+        <v>603</v>
+      </c>
+      <c r="I191" t="s">
+        <v>89</v>
+      </c>
+      <c r="J191" t="s">
+        <v>604</v>
+      </c>
+      <c r="K191" t="s">
+        <v>25</v>
+      </c>
+      <c r="L191" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M191" t="s">
+        <v>42</v>
+      </c>
+      <c r="N191" t="s">
+        <v>491</v>
+      </c>
+      <c r="O191" t="s">
+        <v>25</v>
+      </c>
+      <c r="P191" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>539</v>
+      </c>
+      <c r="B192" t="s">
+        <v>359</v>
+      </c>
+      <c r="C192" t="s">
+        <v>38</v>
+      </c>
+      <c r="D192" t="s">
+        <v>605</v>
+      </c>
+      <c r="E192" t="s">
+        <v>60</v>
+      </c>
+      <c r="F192" t="s">
+        <v>31</v>
+      </c>
+      <c r="G192">
+        <v>62</v>
+      </c>
+      <c r="H192" t="s">
+        <v>77</v>
+      </c>
+      <c r="I192" t="s">
+        <v>54</v>
+      </c>
+      <c r="J192" t="s">
+        <v>606</v>
+      </c>
+      <c r="K192" t="s">
+        <v>25</v>
+      </c>
+      <c r="L192" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M192" t="s">
+        <v>42</v>
+      </c>
+      <c r="N192" t="s">
+        <v>303</v>
+      </c>
+      <c r="O192" t="s">
+        <v>28</v>
+      </c>
+      <c r="P192" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>607</v>
+      </c>
+      <c r="B193" t="s">
+        <v>17</v>
+      </c>
+      <c r="C193" t="s">
+        <v>18</v>
+      </c>
+      <c r="D193" t="s">
+        <v>608</v>
+      </c>
+      <c r="E193" t="s">
+        <v>20</v>
+      </c>
+      <c r="F193" t="s">
+        <v>31</v>
+      </c>
+      <c r="G193">
+        <v>43</v>
+      </c>
+      <c r="H193" t="s">
+        <v>61</v>
+      </c>
+      <c r="I193" t="s">
+        <v>33</v>
+      </c>
+      <c r="J193" t="s">
+        <v>609</v>
+      </c>
+      <c r="K193" t="s">
+        <v>25</v>
+      </c>
+      <c r="L193" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M193" t="s">
+        <v>17</v>
+      </c>
+      <c r="N193" t="s">
+        <v>276</v>
+      </c>
+      <c r="O193" t="s">
+        <v>28</v>
+      </c>
+      <c r="P193" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>607</v>
+      </c>
+      <c r="B194" t="s">
+        <v>407</v>
+      </c>
+      <c r="C194" t="s">
+        <v>38</v>
+      </c>
+      <c r="D194" t="s">
+        <v>610</v>
+      </c>
+      <c r="E194" t="s">
+        <v>20</v>
+      </c>
+      <c r="F194" t="s">
+        <v>45</v>
+      </c>
+      <c r="G194">
+        <v>21</v>
+      </c>
+      <c r="H194" t="s">
+        <v>611</v>
+      </c>
+      <c r="I194" t="s">
+        <v>89</v>
+      </c>
+      <c r="J194" t="s">
+        <v>612</v>
+      </c>
+      <c r="K194" t="s">
+        <v>25</v>
+      </c>
+      <c r="L194" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M194" t="s">
+        <v>42</v>
+      </c>
+      <c r="N194" t="s">
+        <v>276</v>
+      </c>
+      <c r="O194" t="s">
+        <v>28</v>
+      </c>
+      <c r="P194" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>607</v>
+      </c>
+      <c r="B195" t="s">
+        <v>407</v>
+      </c>
+      <c r="C195" t="s">
+        <v>38</v>
+      </c>
+      <c r="D195" t="s">
+        <v>613</v>
+      </c>
+      <c r="E195" t="s">
+        <v>20</v>
+      </c>
+      <c r="F195" t="s">
+        <v>388</v>
+      </c>
+      <c r="G195">
+        <v>35</v>
+      </c>
+      <c r="H195" t="s">
+        <v>77</v>
+      </c>
+      <c r="I195" t="s">
+        <v>89</v>
+      </c>
+      <c r="J195" t="s">
+        <v>614</v>
+      </c>
+      <c r="K195" t="s">
+        <v>25</v>
+      </c>
+      <c r="L195" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M195" t="s">
+        <v>42</v>
+      </c>
+      <c r="N195" t="s">
+        <v>276</v>
+      </c>
+      <c r="O195" t="s">
+        <v>28</v>
+      </c>
+      <c r="P195" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>607</v>
+      </c>
+      <c r="B196" t="s">
+        <v>407</v>
+      </c>
+      <c r="C196" t="s">
+        <v>38</v>
+      </c>
+      <c r="D196" t="s">
+        <v>615</v>
+      </c>
+      <c r="E196" t="s">
+        <v>20</v>
+      </c>
+      <c r="F196" t="s">
+        <v>45</v>
+      </c>
+      <c r="G196">
+        <v>22</v>
+      </c>
+      <c r="H196" t="s">
+        <v>77</v>
+      </c>
+      <c r="I196" t="s">
+        <v>89</v>
+      </c>
+      <c r="J196" t="s">
+        <v>616</v>
+      </c>
+      <c r="K196" t="s">
+        <v>25</v>
+      </c>
+      <c r="L196" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M196" t="s">
+        <v>417</v>
+      </c>
+      <c r="N196" t="s">
+        <v>617</v>
+      </c>
+      <c r="O196" t="s">
+        <v>28</v>
+      </c>
+      <c r="P196" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>607</v>
+      </c>
+      <c r="B197" t="s">
+        <v>17</v>
+      </c>
+      <c r="C197" t="s">
+        <v>38</v>
+      </c>
+      <c r="D197" t="s">
+        <v>618</v>
+      </c>
+      <c r="E197" t="s">
+        <v>20</v>
+      </c>
+      <c r="F197" t="s">
+        <v>45</v>
+      </c>
+      <c r="G197">
+        <v>19</v>
+      </c>
+      <c r="H197" t="s">
+        <v>50</v>
+      </c>
+      <c r="I197" t="s">
+        <v>33</v>
+      </c>
+      <c r="J197" t="s">
+        <v>619</v>
+      </c>
+      <c r="K197" t="s">
+        <v>25</v>
+      </c>
+      <c r="L197" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M197" t="s">
+        <v>42</v>
+      </c>
+      <c r="N197" t="s">
+        <v>276</v>
+      </c>
+      <c r="O197" t="s">
+        <v>28</v>
+      </c>
+      <c r="P197" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>620</v>
+      </c>
+      <c r="B198" t="s">
+        <v>17</v>
+      </c>
+      <c r="C198" t="s">
+        <v>65</v>
+      </c>
+      <c r="D198" t="s">
+        <v>621</v>
+      </c>
+      <c r="E198" t="s">
+        <v>20</v>
+      </c>
+      <c r="F198" t="s">
+        <v>31</v>
+      </c>
+      <c r="G198">
+        <v>51</v>
+      </c>
+      <c r="H198" t="s">
+        <v>61</v>
+      </c>
+      <c r="I198" t="s">
+        <v>33</v>
+      </c>
+      <c r="J198" t="s">
+        <v>622</v>
+      </c>
+      <c r="K198" t="s">
+        <v>25</v>
+      </c>
+      <c r="L198" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M198" t="s">
+        <v>17</v>
+      </c>
+      <c r="N198" t="s">
+        <v>276</v>
+      </c>
+      <c r="O198" t="s">
+        <v>25</v>
+      </c>
+      <c r="P198" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>620</v>
+      </c>
+      <c r="B199" t="s">
+        <v>359</v>
+      </c>
+      <c r="C199" t="s">
+        <v>18</v>
+      </c>
+      <c r="D199" t="s">
+        <v>623</v>
+      </c>
+      <c r="E199" t="s">
+        <v>20</v>
+      </c>
+      <c r="F199" t="s">
+        <v>144</v>
+      </c>
+      <c r="G199">
+        <v>43</v>
+      </c>
+      <c r="H199" t="s">
+        <v>624</v>
+      </c>
+      <c r="I199" t="s">
+        <v>54</v>
+      </c>
+      <c r="J199" t="s">
+        <v>625</v>
+      </c>
+      <c r="K199" t="s">
+        <v>25</v>
+      </c>
+      <c r="L199" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M199" t="s">
+        <v>17</v>
+      </c>
+      <c r="N199" t="s">
+        <v>276</v>
+      </c>
+      <c r="O199" t="s">
+        <v>25</v>
+      </c>
+      <c r="P199" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>626</v>
+      </c>
+      <c r="B200" t="s">
+        <v>627</v>
+      </c>
+      <c r="C200" t="s">
+        <v>38</v>
+      </c>
+      <c r="D200" t="s">
+        <v>628</v>
+      </c>
+      <c r="E200" t="s">
+        <v>20</v>
+      </c>
+      <c r="F200" t="s">
+        <v>31</v>
+      </c>
+      <c r="G200">
+        <v>31</v>
+      </c>
+      <c r="H200" t="s">
+        <v>629</v>
+      </c>
+      <c r="I200" t="s">
+        <v>54</v>
+      </c>
+      <c r="J200" t="s">
+        <v>630</v>
+      </c>
+      <c r="K200" t="s">
+        <v>25</v>
+      </c>
+      <c r="L200" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M200" t="s">
+        <v>42</v>
+      </c>
+      <c r="N200" t="s">
+        <v>276</v>
+      </c>
+      <c r="O200" t="s">
+        <v>25</v>
+      </c>
+      <c r="P200" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>626</v>
+      </c>
+      <c r="B201" t="s">
+        <v>627</v>
+      </c>
+      <c r="C201" t="s">
+        <v>18</v>
+      </c>
+      <c r="D201" t="s">
+        <v>631</v>
+      </c>
+      <c r="E201" t="s">
+        <v>20</v>
+      </c>
+      <c r="F201" t="s">
+        <v>45</v>
+      </c>
+      <c r="G201">
+        <v>16</v>
+      </c>
+      <c r="H201" t="s">
+        <v>102</v>
+      </c>
+      <c r="I201" t="s">
+        <v>54</v>
+      </c>
+      <c r="J201" t="s">
+        <v>632</v>
+      </c>
+      <c r="K201" t="s">
+        <v>25</v>
+      </c>
+      <c r="L201" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M201" t="s">
+        <v>17</v>
+      </c>
+      <c r="N201" t="s">
+        <v>276</v>
+      </c>
+      <c r="O201" t="s">
+        <v>25</v>
+      </c>
+      <c r="P201" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>626</v>
+      </c>
+      <c r="B202" t="s">
+        <v>627</v>
+      </c>
+      <c r="C202" t="s">
+        <v>18</v>
+      </c>
+      <c r="D202" t="s">
+        <v>633</v>
+      </c>
+      <c r="E202" t="s">
+        <v>20</v>
+      </c>
+      <c r="F202" t="s">
+        <v>21</v>
+      </c>
+      <c r="G202">
+        <v>50</v>
+      </c>
+      <c r="H202" t="s">
+        <v>46</v>
+      </c>
+      <c r="I202" t="s">
+        <v>33</v>
+      </c>
+      <c r="J202" t="s">
+        <v>634</v>
+      </c>
+      <c r="K202" t="s">
+        <v>25</v>
+      </c>
+      <c r="L202" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M202" t="s">
+        <v>17</v>
+      </c>
+      <c r="N202" t="s">
+        <v>276</v>
+      </c>
+      <c r="O202" t="s">
+        <v>25</v>
+      </c>
+      <c r="P202" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>626</v>
+      </c>
+      <c r="B203" t="s">
+        <v>627</v>
+      </c>
+      <c r="C203" t="s">
+        <v>18</v>
+      </c>
+      <c r="D203" t="s">
+        <v>635</v>
+      </c>
+      <c r="E203" t="s">
+        <v>20</v>
+      </c>
+      <c r="F203" t="s">
+        <v>45</v>
+      </c>
+      <c r="G203">
+        <v>27</v>
+      </c>
+      <c r="H203" t="s">
+        <v>636</v>
+      </c>
+      <c r="I203" t="s">
+        <v>54</v>
+      </c>
+      <c r="J203" t="s">
+        <v>637</v>
+      </c>
+      <c r="K203" t="s">
+        <v>25</v>
+      </c>
+      <c r="L203" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M203" t="s">
+        <v>17</v>
+      </c>
+      <c r="N203" t="s">
+        <v>276</v>
+      </c>
+      <c r="O203" t="s">
+        <v>28</v>
+      </c>
+      <c r="P203" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>638</v>
+      </c>
+      <c r="B204" t="s">
+        <v>17</v>
+      </c>
+      <c r="C204" t="s">
+        <v>38</v>
+      </c>
+      <c r="D204" t="s">
+        <v>639</v>
+      </c>
+      <c r="E204" t="s">
+        <v>20</v>
+      </c>
+      <c r="F204" t="s">
+        <v>45</v>
+      </c>
+      <c r="G204">
+        <v>24</v>
+      </c>
+      <c r="H204" t="s">
+        <v>36</v>
+      </c>
+      <c r="I204" t="s">
+        <v>33</v>
+      </c>
+      <c r="J204" t="s">
+        <v>640</v>
+      </c>
+      <c r="K204" t="s">
+        <v>25</v>
+      </c>
+      <c r="L204" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M204" t="s">
+        <v>42</v>
+      </c>
+      <c r="N204" t="s">
+        <v>276</v>
+      </c>
+      <c r="O204" t="s">
+        <v>25</v>
+      </c>
+      <c r="P204" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>638</v>
+      </c>
+      <c r="B205" t="s">
+        <v>17</v>
+      </c>
+      <c r="C205" t="s">
+        <v>65</v>
+      </c>
+      <c r="D205" t="s">
+        <v>641</v>
+      </c>
+      <c r="E205" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205" t="s">
+        <v>45</v>
+      </c>
+      <c r="G205">
+        <v>24</v>
+      </c>
+      <c r="H205" t="s">
+        <v>17</v>
+      </c>
+      <c r="I205" t="s">
+        <v>179</v>
+      </c>
+      <c r="J205" t="s">
+        <v>642</v>
+      </c>
+      <c r="K205" t="s">
+        <v>25</v>
+      </c>
+      <c r="L205" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="M205" t="s">
+        <v>289</v>
+      </c>
+      <c r="N205" t="s">
+        <v>617</v>
+      </c>
+      <c r="O205" t="s">
+        <v>28</v>
+      </c>
+      <c r="P205" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>607</v>
+      </c>
+      <c r="B206" t="s">
+        <v>407</v>
+      </c>
+      <c r="C206" t="s">
+        <v>65</v>
+      </c>
+      <c r="D206" t="s">
+        <v>643</v>
+      </c>
+      <c r="E206" t="s">
+        <v>60</v>
+      </c>
+      <c r="F206" t="s">
+        <v>45</v>
+      </c>
+      <c r="G206">
+        <v>16</v>
+      </c>
+      <c r="H206" t="s">
+        <v>644</v>
+      </c>
+      <c r="I206" t="s">
+        <v>33</v>
+      </c>
+      <c r="J206" t="s">
+        <v>645</v>
+      </c>
+      <c r="K206" t="s">
+        <v>25</v>
+      </c>
+      <c r="L206" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M206" t="s">
+        <v>42</v>
+      </c>
+      <c r="N206" t="s">
+        <v>68</v>
+      </c>
+      <c r="O206" t="s">
+        <v>187</v>
+      </c>
+      <c r="P206" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>607</v>
+      </c>
+      <c r="B207" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" t="s">
+        <v>38</v>
+      </c>
+      <c r="D207" t="s">
+        <v>646</v>
+      </c>
+      <c r="E207" t="s">
+        <v>60</v>
+      </c>
+      <c r="F207" t="s">
+        <v>45</v>
+      </c>
+      <c r="G207">
+        <v>48</v>
+      </c>
+      <c r="H207" t="s">
+        <v>647</v>
+      </c>
+      <c r="I207" t="s">
+        <v>89</v>
+      </c>
+      <c r="J207" t="s">
+        <v>648</v>
+      </c>
+      <c r="K207" t="s">
+        <v>25</v>
+      </c>
+      <c r="L207" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M207" t="s">
+        <v>17</v>
+      </c>
+      <c r="N207" t="s">
+        <v>68</v>
+      </c>
+      <c r="O207" t="s">
+        <v>187</v>
+      </c>
+      <c r="P207" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>620</v>
+      </c>
+      <c r="B208" t="s">
+        <v>359</v>
+      </c>
+      <c r="C208" t="s">
+        <v>18</v>
+      </c>
+      <c r="D208" t="s">
+        <v>649</v>
+      </c>
+      <c r="E208" t="s">
+        <v>60</v>
+      </c>
+      <c r="F208" t="s">
+        <v>45</v>
+      </c>
+      <c r="G208">
+        <v>21</v>
+      </c>
+      <c r="H208" t="s">
+        <v>53</v>
+      </c>
+      <c r="I208" t="s">
+        <v>33</v>
+      </c>
+      <c r="J208" t="s">
+        <v>650</v>
+      </c>
+      <c r="K208" t="s">
+        <v>25</v>
+      </c>
+      <c r="L208" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M208" t="s">
+        <v>417</v>
+      </c>
+      <c r="N208" t="s">
+        <v>68</v>
+      </c>
+      <c r="O208" t="s">
+        <v>187</v>
+      </c>
+      <c r="P208" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>620</v>
+      </c>
+      <c r="B209" t="s">
+        <v>359</v>
+      </c>
+      <c r="C209" t="s">
+        <v>18</v>
+      </c>
+      <c r="D209" t="s">
+        <v>651</v>
+      </c>
+      <c r="E209" t="s">
+        <v>60</v>
+      </c>
+      <c r="F209" t="s">
+        <v>31</v>
+      </c>
+      <c r="G209">
+        <v>54</v>
+      </c>
+      <c r="H209" t="s">
+        <v>96</v>
+      </c>
+      <c r="I209" t="s">
+        <v>33</v>
+      </c>
+      <c r="J209" t="s">
+        <v>652</v>
+      </c>
+      <c r="K209" t="s">
+        <v>25</v>
+      </c>
+      <c r="L209" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M209" t="s">
+        <v>17</v>
+      </c>
+      <c r="N209" t="s">
+        <v>653</v>
+      </c>
+      <c r="O209" t="s">
+        <v>25</v>
+      </c>
+      <c r="P209" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>620</v>
+      </c>
+      <c r="B210" t="s">
+        <v>359</v>
+      </c>
+      <c r="C210" t="s">
+        <v>65</v>
+      </c>
+      <c r="D210" t="s">
+        <v>654</v>
+      </c>
+      <c r="E210" t="s">
+        <v>60</v>
+      </c>
+      <c r="F210" t="s">
+        <v>45</v>
+      </c>
+      <c r="G210">
+        <v>35</v>
+      </c>
+      <c r="H210" t="s">
+        <v>102</v>
+      </c>
+      <c r="I210" t="s">
+        <v>33</v>
+      </c>
+      <c r="J210" t="s">
+        <v>655</v>
+      </c>
+      <c r="K210" t="s">
+        <v>25</v>
+      </c>
+      <c r="L210" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M210" t="s">
+        <v>17</v>
+      </c>
+      <c r="N210" t="s">
+        <v>63</v>
+      </c>
+      <c r="O210" t="s">
+        <v>25</v>
+      </c>
+      <c r="P210" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>620</v>
+      </c>
+      <c r="B211" t="s">
+        <v>359</v>
+      </c>
+      <c r="C211" t="s">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>656</v>
+      </c>
+      <c r="E211" t="s">
+        <v>60</v>
+      </c>
+      <c r="F211" t="s">
+        <v>45</v>
+      </c>
+      <c r="G211">
+        <v>18</v>
+      </c>
+      <c r="H211" t="s">
+        <v>50</v>
+      </c>
+      <c r="I211" t="s">
+        <v>33</v>
+      </c>
+      <c r="J211" t="s">
+        <v>657</v>
+      </c>
+      <c r="K211" t="s">
+        <v>25</v>
+      </c>
+      <c r="L211" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M211" t="s">
+        <v>17</v>
+      </c>
+      <c r="N211" t="s">
+        <v>68</v>
+      </c>
+      <c r="O211" t="s">
+        <v>187</v>
+      </c>
+      <c r="P211" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>620</v>
+      </c>
+      <c r="B212" t="s">
+        <v>359</v>
+      </c>
+      <c r="C212" t="s">
+        <v>18</v>
+      </c>
+      <c r="D212" t="s">
+        <v>658</v>
+      </c>
+      <c r="E212" t="s">
+        <v>60</v>
+      </c>
+      <c r="F212" t="s">
+        <v>31</v>
+      </c>
+      <c r="G212">
+        <v>37</v>
+      </c>
+      <c r="H212" t="s">
+        <v>46</v>
+      </c>
+      <c r="I212" t="s">
+        <v>33</v>
+      </c>
+      <c r="J212" t="s">
+        <v>594</v>
+      </c>
+      <c r="K212" t="s">
+        <v>25</v>
+      </c>
+      <c r="L212" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M212" t="s">
+        <v>17</v>
+      </c>
+      <c r="N212" t="s">
+        <v>63</v>
+      </c>
+      <c r="O212" t="s">
+        <v>25</v>
+      </c>
+      <c r="P212" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>626</v>
+      </c>
+      <c r="B213" t="s">
+        <v>627</v>
+      </c>
+      <c r="C213" t="s">
+        <v>38</v>
+      </c>
+      <c r="D213" t="s">
+        <v>659</v>
+      </c>
+      <c r="E213" t="s">
+        <v>60</v>
+      </c>
+      <c r="F213" t="s">
+        <v>45</v>
+      </c>
+      <c r="G213">
+        <v>19</v>
+      </c>
+      <c r="H213" t="s">
+        <v>102</v>
+      </c>
+      <c r="I213" t="s">
+        <v>33</v>
+      </c>
+      <c r="J213" t="s">
+        <v>660</v>
+      </c>
+      <c r="K213" t="s">
+        <v>25</v>
+      </c>
+      <c r="L213" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M213" t="s">
+        <v>42</v>
+      </c>
+      <c r="N213" t="s">
+        <v>661</v>
+      </c>
+      <c r="O213" t="s">
+        <v>25</v>
+      </c>
+      <c r="P213" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>626</v>
+      </c>
+      <c r="B214" t="s">
+        <v>17</v>
+      </c>
+      <c r="C214" t="s">
+        <v>38</v>
+      </c>
+      <c r="D214" t="s">
+        <v>662</v>
+      </c>
+      <c r="E214" t="s">
+        <v>60</v>
+      </c>
+      <c r="F214" t="s">
+        <v>45</v>
+      </c>
+      <c r="G214">
+        <v>29</v>
+      </c>
+      <c r="H214" t="s">
+        <v>663</v>
+      </c>
+      <c r="I214" t="s">
+        <v>33</v>
+      </c>
+      <c r="J214" t="s">
+        <v>664</v>
+      </c>
+      <c r="K214" t="s">
+        <v>25</v>
+      </c>
+      <c r="L214" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M214" t="s">
+        <v>42</v>
+      </c>
+      <c r="N214" t="s">
+        <v>63</v>
+      </c>
+      <c r="O214" t="s">
+        <v>25</v>
+      </c>
+      <c r="P214" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>626</v>
+      </c>
+      <c r="B215" t="s">
+        <v>17</v>
+      </c>
+      <c r="C215" t="s">
+        <v>38</v>
+      </c>
+      <c r="D215" t="s">
+        <v>665</v>
+      </c>
+      <c r="E215" t="s">
+        <v>60</v>
+      </c>
+      <c r="F215" t="s">
+        <v>45</v>
+      </c>
+      <c r="G215">
+        <v>35</v>
+      </c>
+      <c r="H215" t="s">
+        <v>36</v>
+      </c>
+      <c r="I215" t="s">
+        <v>33</v>
+      </c>
+      <c r="J215" t="s">
+        <v>666</v>
+      </c>
+      <c r="K215" t="s">
+        <v>25</v>
+      </c>
+      <c r="L215" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M215" t="s">
+        <v>17</v>
+      </c>
+      <c r="N215" t="s">
+        <v>63</v>
+      </c>
+      <c r="O215" t="s">
+        <v>25</v>
+      </c>
+      <c r="P215" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>626</v>
+      </c>
+      <c r="B216" t="s">
+        <v>17</v>
+      </c>
+      <c r="C216" t="s">
+        <v>18</v>
+      </c>
+      <c r="D216" t="s">
+        <v>667</v>
+      </c>
+      <c r="E216" t="s">
+        <v>60</v>
+      </c>
+      <c r="F216" t="s">
+        <v>45</v>
+      </c>
+      <c r="G216">
+        <v>13</v>
+      </c>
+      <c r="H216" t="s">
+        <v>409</v>
+      </c>
+      <c r="I216" t="s">
+        <v>158</v>
+      </c>
+      <c r="J216" t="s">
+        <v>668</v>
+      </c>
+      <c r="K216" t="s">
+        <v>25</v>
+      </c>
+      <c r="L216" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M216" t="s">
+        <v>17</v>
+      </c>
+      <c r="N216" t="s">
+        <v>68</v>
+      </c>
+      <c r="O216" t="s">
+        <v>187</v>
+      </c>
+      <c r="P216" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>626</v>
+      </c>
+      <c r="B217" t="s">
+        <v>17</v>
+      </c>
+      <c r="C217" t="s">
+        <v>18</v>
+      </c>
+      <c r="D217" t="s">
+        <v>669</v>
+      </c>
+      <c r="E217" t="s">
+        <v>60</v>
+      </c>
+      <c r="F217" t="s">
+        <v>45</v>
+      </c>
+      <c r="G217">
+        <v>46</v>
+      </c>
+      <c r="H217" t="s">
+        <v>670</v>
+      </c>
+      <c r="I217" t="s">
+        <v>671</v>
+      </c>
+      <c r="J217" t="s">
+        <v>672</v>
+      </c>
+      <c r="K217" t="s">
+        <v>25</v>
+      </c>
+      <c r="L217" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M217" t="s">
+        <v>17</v>
+      </c>
+      <c r="N217" t="s">
+        <v>673</v>
+      </c>
+      <c r="O217" t="s">
+        <v>25</v>
+      </c>
+      <c r="P217" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>638</v>
+      </c>
+      <c r="B218" t="s">
+        <v>17</v>
+      </c>
+      <c r="C218" t="s">
+        <v>18</v>
+      </c>
+      <c r="D218" t="s">
+        <v>674</v>
+      </c>
+      <c r="E218" t="s">
+        <v>60</v>
+      </c>
+      <c r="F218" t="s">
+        <v>17</v>
+      </c>
+      <c r="G218">
+        <v>23</v>
+      </c>
+      <c r="H218" t="s">
+        <v>17</v>
+      </c>
+      <c r="I218" t="s">
+        <v>54</v>
+      </c>
+      <c r="J218" t="s">
+        <v>675</v>
+      </c>
+      <c r="K218" t="s">
+        <v>25</v>
+      </c>
+      <c r="L218" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M218" t="s">
+        <v>17</v>
+      </c>
+      <c r="N218" t="s">
+        <v>676</v>
+      </c>
+      <c r="O218" t="s">
+        <v>25</v>
+      </c>
+      <c r="P218" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>638</v>
+      </c>
+      <c r="B219" t="s">
+        <v>17</v>
+      </c>
+      <c r="C219" t="s">
+        <v>18</v>
+      </c>
+      <c r="D219" t="s">
+        <v>677</v>
+      </c>
+      <c r="E219" t="s">
+        <v>60</v>
+      </c>
+      <c r="F219" t="s">
+        <v>45</v>
+      </c>
+      <c r="G219">
+        <v>30</v>
+      </c>
+      <c r="H219" t="s">
+        <v>115</v>
+      </c>
+      <c r="I219" t="s">
+        <v>54</v>
+      </c>
+      <c r="J219" t="s">
+        <v>678</v>
+      </c>
+      <c r="K219" t="s">
+        <v>25</v>
+      </c>
+      <c r="L219" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M219" t="s">
+        <v>17</v>
+      </c>
+      <c r="N219" t="s">
+        <v>63</v>
+      </c>
+      <c r="O219" t="s">
+        <v>172</v>
+      </c>
+      <c r="P219" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>679</v>
+      </c>
+      <c r="B220" t="s">
+        <v>17</v>
+      </c>
+      <c r="C220" t="s">
+        <v>38</v>
+      </c>
+      <c r="D220" t="s">
+        <v>680</v>
+      </c>
+      <c r="E220" t="s">
+        <v>20</v>
+      </c>
+      <c r="F220" t="s">
+        <v>45</v>
+      </c>
+      <c r="G220">
+        <v>24</v>
+      </c>
+      <c r="H220" t="s">
+        <v>681</v>
+      </c>
+      <c r="I220" t="s">
+        <v>33</v>
+      </c>
+      <c r="J220" t="s">
+        <v>682</v>
+      </c>
+      <c r="K220" t="s">
+        <v>25</v>
+      </c>
+      <c r="L220" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M220" t="s">
+        <v>42</v>
+      </c>
+      <c r="N220" t="s">
+        <v>276</v>
+      </c>
+      <c r="O220" t="s">
+        <v>28</v>
+      </c>
+      <c r="P220" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>679</v>
+      </c>
+      <c r="B221" t="s">
+        <v>407</v>
+      </c>
+      <c r="C221" t="s">
+        <v>38</v>
+      </c>
+      <c r="D221" t="s">
+        <v>683</v>
+      </c>
+      <c r="E221" t="s">
+        <v>20</v>
+      </c>
+      <c r="F221" t="s">
+        <v>45</v>
+      </c>
+      <c r="G221">
+        <v>18</v>
+      </c>
+      <c r="H221" t="s">
+        <v>684</v>
+      </c>
+      <c r="I221" t="s">
+        <v>33</v>
+      </c>
+      <c r="J221" t="s">
+        <v>685</v>
+      </c>
+      <c r="K221" t="s">
+        <v>25</v>
+      </c>
+      <c r="L221" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M221" t="s">
+        <v>42</v>
+      </c>
+      <c r="N221" t="s">
+        <v>276</v>
+      </c>
+      <c r="O221" t="s">
+        <v>25</v>
+      </c>
+      <c r="P221" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>679</v>
+      </c>
+      <c r="B222" t="s">
+        <v>17</v>
+      </c>
+      <c r="C222" t="s">
+        <v>38</v>
+      </c>
+      <c r="D222" t="s">
+        <v>686</v>
+      </c>
+      <c r="E222" t="s">
+        <v>20</v>
+      </c>
+      <c r="F222" t="s">
+        <v>45</v>
+      </c>
+      <c r="G222">
+        <v>36</v>
+      </c>
+      <c r="H222" t="s">
+        <v>115</v>
+      </c>
+      <c r="I222" t="s">
+        <v>33</v>
+      </c>
+      <c r="J222" t="s">
+        <v>687</v>
+      </c>
+      <c r="K222" t="s">
+        <v>25</v>
+      </c>
+      <c r="L222" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M222" t="s">
+        <v>42</v>
+      </c>
+      <c r="N222" t="s">
+        <v>276</v>
+      </c>
+      <c r="O222" t="s">
+        <v>28</v>
+      </c>
+      <c r="P222" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>679</v>
+      </c>
+      <c r="B223" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" t="s">
+        <v>18</v>
+      </c>
+      <c r="D223" t="s">
+        <v>688</v>
+      </c>
+      <c r="E223" t="s">
+        <v>20</v>
+      </c>
+      <c r="F223" t="s">
+        <v>45</v>
+      </c>
+      <c r="G223">
+        <v>36</v>
+      </c>
+      <c r="H223" t="s">
+        <v>36</v>
+      </c>
+      <c r="I223" t="s">
+        <v>33</v>
+      </c>
+      <c r="J223" t="s">
+        <v>689</v>
+      </c>
+      <c r="K223" t="s">
+        <v>25</v>
+      </c>
+      <c r="L223" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M223" t="s">
+        <v>289</v>
+      </c>
+      <c r="N223" t="s">
+        <v>617</v>
+      </c>
+      <c r="O223" t="s">
+        <v>28</v>
+      </c>
+      <c r="P223" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>679</v>
+      </c>
+      <c r="B224" t="s">
+        <v>17</v>
+      </c>
+      <c r="C224" t="s">
+        <v>18</v>
+      </c>
+      <c r="D224" t="s">
+        <v>688</v>
+      </c>
+      <c r="E224" t="s">
+        <v>20</v>
+      </c>
+      <c r="F224" t="s">
+        <v>45</v>
+      </c>
+      <c r="G224">
+        <v>36</v>
+      </c>
+      <c r="H224" t="s">
+        <v>36</v>
+      </c>
+      <c r="I224" t="s">
+        <v>33</v>
+      </c>
+      <c r="J224" t="s">
+        <v>690</v>
+      </c>
+      <c r="K224" t="s">
+        <v>25</v>
+      </c>
+      <c r="L224" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M224" t="s">
+        <v>42</v>
+      </c>
+      <c r="N224" t="s">
+        <v>276</v>
+      </c>
+      <c r="O224" t="s">
+        <v>28</v>
+      </c>
+      <c r="P224" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>679</v>
+      </c>
+      <c r="B225" t="s">
+        <v>17</v>
+      </c>
+      <c r="C225" t="s">
+        <v>38</v>
+      </c>
+      <c r="D225" t="s">
+        <v>691</v>
+      </c>
+      <c r="E225" t="s">
+        <v>20</v>
+      </c>
+      <c r="F225" t="s">
+        <v>31</v>
+      </c>
+      <c r="G225">
+        <v>30</v>
+      </c>
+      <c r="H225" t="s">
+        <v>102</v>
+      </c>
+      <c r="I225" t="s">
+        <v>33</v>
+      </c>
+      <c r="J225" t="s">
+        <v>692</v>
+      </c>
+      <c r="K225" t="s">
+        <v>25</v>
+      </c>
+      <c r="L225" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M225" t="s">
+        <v>42</v>
+      </c>
+      <c r="N225" t="s">
+        <v>276</v>
+      </c>
+      <c r="O225" t="s">
+        <v>25</v>
+      </c>
+      <c r="P225" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>679</v>
+      </c>
+      <c r="B226" t="s">
+        <v>17</v>
+      </c>
+      <c r="C226" t="s">
+        <v>18</v>
+      </c>
+      <c r="D226" t="s">
+        <v>693</v>
+      </c>
+      <c r="E226" t="s">
+        <v>20</v>
+      </c>
+      <c r="F226" t="s">
+        <v>45</v>
+      </c>
+      <c r="G226">
+        <v>30</v>
+      </c>
+      <c r="H226" t="s">
+        <v>255</v>
+      </c>
+      <c r="I226" t="s">
+        <v>89</v>
+      </c>
+      <c r="J226" t="s">
+        <v>694</v>
+      </c>
+      <c r="K226" t="s">
+        <v>25</v>
+      </c>
+      <c r="L226" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M226" t="s">
+        <v>17</v>
+      </c>
+      <c r="N226" t="s">
+        <v>276</v>
+      </c>
+      <c r="O226" t="s">
+        <v>28</v>
+      </c>
+      <c r="P226" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>695</v>
+      </c>
+      <c r="B227" t="s">
+        <v>17</v>
+      </c>
+      <c r="C227" t="s">
+        <v>38</v>
+      </c>
+      <c r="D227" t="s">
+        <v>696</v>
+      </c>
+      <c r="E227" t="s">
+        <v>20</v>
+      </c>
+      <c r="F227" t="s">
+        <v>45</v>
+      </c>
+      <c r="G227">
+        <v>31</v>
+      </c>
+      <c r="H227" t="s">
+        <v>218</v>
+      </c>
+      <c r="I227" t="s">
+        <v>33</v>
+      </c>
+      <c r="J227" t="s">
+        <v>697</v>
+      </c>
+      <c r="K227" t="s">
+        <v>25</v>
+      </c>
+      <c r="L227" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M227" t="s">
+        <v>42</v>
+      </c>
+      <c r="N227" t="s">
+        <v>276</v>
+      </c>
+      <c r="O227" t="s">
+        <v>28</v>
+      </c>
+      <c r="P227" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>695</v>
+      </c>
+      <c r="B228" t="s">
+        <v>698</v>
+      </c>
+      <c r="C228" t="s">
+        <v>18</v>
+      </c>
+      <c r="D228" t="s">
+        <v>699</v>
+      </c>
+      <c r="E228" t="s">
+        <v>20</v>
+      </c>
+      <c r="F228" t="s">
+        <v>45</v>
+      </c>
+      <c r="G228">
+        <v>26</v>
+      </c>
+      <c r="H228" t="s">
+        <v>36</v>
+      </c>
+      <c r="I228" t="s">
+        <v>33</v>
+      </c>
+      <c r="J228" t="s">
+        <v>700</v>
+      </c>
+      <c r="K228" t="s">
+        <v>25</v>
+      </c>
+      <c r="L228" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M228" t="s">
+        <v>17</v>
+      </c>
+      <c r="N228" t="s">
+        <v>276</v>
+      </c>
+      <c r="O228" t="s">
+        <v>28</v>
+      </c>
+      <c r="P228" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>695</v>
+      </c>
+      <c r="B229" t="s">
+        <v>17</v>
+      </c>
+      <c r="C229" t="s">
+        <v>38</v>
+      </c>
+      <c r="D229" t="s">
+        <v>701</v>
+      </c>
+      <c r="E229" t="s">
+        <v>20</v>
+      </c>
+      <c r="F229" t="s">
+        <v>45</v>
+      </c>
+      <c r="G229">
+        <v>22</v>
+      </c>
+      <c r="H229" t="s">
+        <v>702</v>
+      </c>
+      <c r="I229" t="s">
+        <v>703</v>
+      </c>
+      <c r="J229" t="s">
+        <v>704</v>
+      </c>
+      <c r="K229" t="s">
+        <v>25</v>
+      </c>
+      <c r="L229" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M229" t="s">
+        <v>268</v>
+      </c>
+      <c r="N229" t="s">
+        <v>276</v>
+      </c>
+      <c r="O229" t="s">
+        <v>28</v>
+      </c>
+      <c r="P229" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>679</v>
+      </c>
+      <c r="B230" t="s">
+        <v>17</v>
+      </c>
+      <c r="C230" t="s">
+        <v>18</v>
+      </c>
+      <c r="D230" t="s">
+        <v>705</v>
+      </c>
+      <c r="E230" t="s">
+        <v>60</v>
+      </c>
+      <c r="F230" t="s">
+        <v>45</v>
+      </c>
+      <c r="G230">
+        <v>61</v>
+      </c>
+      <c r="H230" t="s">
+        <v>36</v>
+      </c>
+      <c r="I230" t="s">
+        <v>33</v>
+      </c>
+      <c r="J230" t="s">
+        <v>706</v>
+      </c>
+      <c r="K230" t="s">
+        <v>25</v>
+      </c>
+      <c r="L230" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M230" t="s">
+        <v>17</v>
+      </c>
+      <c r="N230" t="s">
+        <v>68</v>
+      </c>
+      <c r="O230" t="s">
+        <v>187</v>
+      </c>
+      <c r="P230" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>679</v>
+      </c>
+      <c r="B231" t="s">
+        <v>17</v>
+      </c>
+      <c r="C231" t="s">
+        <v>18</v>
+      </c>
+      <c r="D231" t="s">
+        <v>707</v>
+      </c>
+      <c r="E231" t="s">
+        <v>60</v>
+      </c>
+      <c r="F231" t="s">
+        <v>45</v>
+      </c>
+      <c r="G231">
+        <v>31</v>
+      </c>
+      <c r="H231" t="s">
+        <v>50</v>
+      </c>
+      <c r="I231" t="s">
+        <v>33</v>
+      </c>
+      <c r="J231" t="s">
+        <v>708</v>
+      </c>
+      <c r="K231" t="s">
+        <v>25</v>
+      </c>
+      <c r="L231" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M231" t="s">
+        <v>17</v>
+      </c>
+      <c r="N231" t="s">
+        <v>63</v>
+      </c>
+      <c r="O231" t="s">
+        <v>172</v>
+      </c>
+      <c r="P231" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>679</v>
+      </c>
+      <c r="B232" t="s">
+        <v>17</v>
+      </c>
+      <c r="C232" t="s">
+        <v>18</v>
+      </c>
+      <c r="D232" t="s">
+        <v>709</v>
+      </c>
+      <c r="E232" t="s">
+        <v>60</v>
+      </c>
+      <c r="F232" t="s">
+        <v>45</v>
+      </c>
+      <c r="G232">
+        <v>22</v>
+      </c>
+      <c r="H232" t="s">
+        <v>710</v>
+      </c>
+      <c r="I232" t="s">
+        <v>711</v>
+      </c>
+      <c r="J232" t="s">
+        <v>712</v>
+      </c>
+      <c r="K232" t="s">
+        <v>25</v>
+      </c>
+      <c r="L232" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M232" t="s">
+        <v>17</v>
+      </c>
+      <c r="N232" t="s">
+        <v>68</v>
+      </c>
+      <c r="O232" t="s">
+        <v>187</v>
+      </c>
+      <c r="P232" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>679</v>
+      </c>
+      <c r="B233" t="s">
+        <v>17</v>
+      </c>
+      <c r="C233" t="s">
+        <v>38</v>
+      </c>
+      <c r="D233" t="s">
+        <v>713</v>
+      </c>
+      <c r="E233" t="s">
+        <v>60</v>
+      </c>
+      <c r="F233" t="s">
+        <v>31</v>
+      </c>
+      <c r="G233">
+        <v>30</v>
+      </c>
+      <c r="H233" t="s">
+        <v>183</v>
+      </c>
+      <c r="I233" t="s">
+        <v>93</v>
+      </c>
+      <c r="J233" t="s">
+        <v>714</v>
+      </c>
+      <c r="K233" t="s">
+        <v>25</v>
+      </c>
+      <c r="L233" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M233" t="s">
+        <v>42</v>
+      </c>
+      <c r="N233" t="s">
+        <v>504</v>
+      </c>
+      <c r="O233" t="s">
+        <v>172</v>
+      </c>
+      <c r="P233" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>679</v>
+      </c>
+      <c r="B234" t="s">
+        <v>17</v>
+      </c>
+      <c r="C234" t="s">
+        <v>65</v>
+      </c>
+      <c r="D234" t="s">
+        <v>715</v>
+      </c>
+      <c r="E234" t="s">
+        <v>60</v>
+      </c>
+      <c r="F234" t="s">
+        <v>45</v>
+      </c>
+      <c r="G234">
+        <v>34</v>
+      </c>
+      <c r="H234" t="s">
+        <v>36</v>
+      </c>
+      <c r="I234" t="s">
+        <v>33</v>
+      </c>
+      <c r="J234" t="s">
+        <v>716</v>
+      </c>
+      <c r="K234" t="s">
+        <v>25</v>
+      </c>
+      <c r="L234" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M234" t="s">
+        <v>42</v>
+      </c>
+      <c r="N234" t="s">
+        <v>717</v>
+      </c>
+      <c r="O234" t="s">
+        <v>25</v>
+      </c>
+      <c r="P234" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>679</v>
+      </c>
+      <c r="B235" t="s">
+        <v>17</v>
+      </c>
+      <c r="C235" t="s">
+        <v>38</v>
+      </c>
+      <c r="D235" t="s">
+        <v>718</v>
+      </c>
+      <c r="E235" t="s">
+        <v>60</v>
+      </c>
+      <c r="F235" t="s">
+        <v>31</v>
+      </c>
+      <c r="G235">
+        <v>28</v>
+      </c>
+      <c r="H235" t="s">
+        <v>719</v>
+      </c>
+      <c r="I235" t="s">
+        <v>179</v>
+      </c>
+      <c r="J235" t="s">
+        <v>720</v>
+      </c>
+      <c r="K235" t="s">
+        <v>25</v>
+      </c>
+      <c r="L235" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M235" t="s">
+        <v>42</v>
+      </c>
+      <c r="N235" t="s">
+        <v>63</v>
+      </c>
+      <c r="O235" t="s">
+        <v>172</v>
+      </c>
+      <c r="P235" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>679</v>
+      </c>
+      <c r="B236" t="s">
+        <v>17</v>
+      </c>
+      <c r="C236" t="s">
+        <v>18</v>
+      </c>
+      <c r="D236" t="s">
+        <v>721</v>
+      </c>
+      <c r="E236" t="s">
+        <v>60</v>
+      </c>
+      <c r="F236" t="s">
+        <v>45</v>
+      </c>
+      <c r="G236">
+        <v>36</v>
+      </c>
+      <c r="H236" t="s">
+        <v>710</v>
+      </c>
+      <c r="I236" t="s">
+        <v>33</v>
+      </c>
+      <c r="J236" t="s">
+        <v>722</v>
+      </c>
+      <c r="K236" t="s">
+        <v>25</v>
+      </c>
+      <c r="L236" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M236" t="s">
+        <v>17</v>
+      </c>
+      <c r="N236" t="s">
+        <v>68</v>
+      </c>
+      <c r="O236" t="s">
+        <v>187</v>
+      </c>
+      <c r="P236" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>679</v>
+      </c>
+      <c r="B237" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237" t="s">
+        <v>38</v>
+      </c>
+      <c r="D237" t="s">
+        <v>723</v>
+      </c>
+      <c r="E237" t="s">
+        <v>60</v>
+      </c>
+      <c r="F237" t="s">
+        <v>45</v>
+      </c>
+      <c r="G237">
+        <v>30</v>
+      </c>
+      <c r="H237" t="s">
+        <v>92</v>
+      </c>
+      <c r="I237" t="s">
+        <v>33</v>
+      </c>
+      <c r="J237" t="s">
+        <v>724</v>
+      </c>
+      <c r="K237" t="s">
+        <v>25</v>
+      </c>
+      <c r="L237" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M237" t="s">
+        <v>42</v>
+      </c>
+      <c r="N237" t="s">
+        <v>63</v>
+      </c>
+      <c r="O237" t="s">
+        <v>25</v>
+      </c>
+      <c r="P237" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>679</v>
+      </c>
+      <c r="B238" t="s">
+        <v>17</v>
+      </c>
+      <c r="C238" t="s">
+        <v>38</v>
+      </c>
+      <c r="D238" t="s">
+        <v>725</v>
+      </c>
+      <c r="E238" t="s">
+        <v>60</v>
+      </c>
+      <c r="F238" t="s">
+        <v>45</v>
+      </c>
+      <c r="G238">
+        <v>30</v>
+      </c>
+      <c r="H238" t="s">
+        <v>183</v>
+      </c>
+      <c r="I238" t="s">
+        <v>54</v>
+      </c>
+      <c r="J238" t="s">
+        <v>726</v>
+      </c>
+      <c r="K238" t="s">
+        <v>25</v>
+      </c>
+      <c r="L238" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M238" t="s">
+        <v>42</v>
+      </c>
+      <c r="N238" t="s">
+        <v>63</v>
+      </c>
+      <c r="O238" t="s">
+        <v>25</v>
+      </c>
+      <c r="P238" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>695</v>
+      </c>
+      <c r="B239" t="s">
+        <v>17</v>
+      </c>
+      <c r="C239" t="s">
+        <v>38</v>
+      </c>
+      <c r="D239" t="s">
+        <v>727</v>
+      </c>
+      <c r="E239" t="s">
+        <v>60</v>
+      </c>
+      <c r="F239" t="s">
+        <v>45</v>
+      </c>
+      <c r="G239">
+        <v>27</v>
+      </c>
+      <c r="H239" t="s">
+        <v>102</v>
+      </c>
+      <c r="I239" t="s">
+        <v>158</v>
+      </c>
+      <c r="J239" t="s">
+        <v>728</v>
+      </c>
+      <c r="K239" t="s">
+        <v>25</v>
+      </c>
+      <c r="L239" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M239" t="s">
+        <v>42</v>
+      </c>
+      <c r="N239" t="s">
+        <v>729</v>
+      </c>
+      <c r="O239" t="s">
+        <v>25</v>
+      </c>
+      <c r="P239" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>695</v>
+      </c>
+      <c r="B240" t="s">
+        <v>730</v>
+      </c>
+      <c r="C240" t="s">
+        <v>18</v>
+      </c>
+      <c r="D240" t="s">
+        <v>731</v>
+      </c>
+      <c r="E240" t="s">
+        <v>60</v>
+      </c>
+      <c r="F240" t="s">
+        <v>45</v>
+      </c>
+      <c r="G240">
+        <v>31</v>
+      </c>
+      <c r="H240" t="s">
+        <v>36</v>
+      </c>
+      <c r="I240" t="s">
+        <v>33</v>
+      </c>
+      <c r="J240" t="s">
+        <v>732</v>
+      </c>
+      <c r="K240" t="s">
+        <v>25</v>
+      </c>
+      <c r="L240" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M240" t="s">
+        <v>17</v>
+      </c>
+      <c r="N240" t="s">
+        <v>68</v>
+      </c>
+      <c r="O240" t="s">
+        <v>187</v>
+      </c>
+      <c r="P240" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>695</v>
+      </c>
+      <c r="B241" t="s">
+        <v>17</v>
+      </c>
+      <c r="C241" t="s">
+        <v>18</v>
+      </c>
+      <c r="D241" t="s">
+        <v>733</v>
+      </c>
+      <c r="E241" t="s">
+        <v>60</v>
+      </c>
+      <c r="F241" t="s">
+        <v>31</v>
+      </c>
+      <c r="G241">
+        <v>30</v>
+      </c>
+      <c r="H241" t="s">
+        <v>489</v>
+      </c>
+      <c r="I241" t="s">
+        <v>54</v>
+      </c>
+      <c r="J241" t="s">
+        <v>734</v>
+      </c>
+      <c r="K241" t="s">
+        <v>25</v>
+      </c>
+      <c r="L241" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M241" t="s">
+        <v>42</v>
+      </c>
+      <c r="N241" t="s">
+        <v>735</v>
+      </c>
+      <c r="O241" t="s">
+        <v>172</v>
+      </c>
+      <c r="P241" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>695</v>
+      </c>
+      <c r="B242" t="s">
+        <v>17</v>
+      </c>
+      <c r="C242" t="s">
+        <v>38</v>
+      </c>
+      <c r="D242" t="s">
+        <v>736</v>
+      </c>
+      <c r="E242" t="s">
+        <v>60</v>
+      </c>
+      <c r="F242" t="s">
+        <v>45</v>
+      </c>
+      <c r="G242">
+        <v>35</v>
+      </c>
+      <c r="H242" t="s">
+        <v>255</v>
+      </c>
+      <c r="I242" t="s">
+        <v>579</v>
+      </c>
+      <c r="J242" t="s">
+        <v>737</v>
+      </c>
+      <c r="K242" t="s">
+        <v>25</v>
+      </c>
+      <c r="L242" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M242" t="s">
+        <v>42</v>
+      </c>
+      <c r="N242" t="s">
+        <v>68</v>
+      </c>
+      <c r="O242" t="s">
+        <v>187</v>
+      </c>
+      <c r="P242" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>695</v>
+      </c>
+      <c r="B243" t="s">
+        <v>17</v>
+      </c>
+      <c r="C243" t="s">
+        <v>38</v>
+      </c>
+      <c r="D243" t="s">
+        <v>738</v>
+      </c>
+      <c r="E243" t="s">
+        <v>60</v>
+      </c>
+      <c r="F243" t="s">
+        <v>45</v>
+      </c>
+      <c r="G243">
+        <v>24</v>
+      </c>
+      <c r="H243" t="s">
+        <v>462</v>
+      </c>
+      <c r="I243" t="s">
+        <v>33</v>
+      </c>
+      <c r="J243" t="s">
+        <v>739</v>
+      </c>
+      <c r="K243" t="s">
+        <v>25</v>
+      </c>
+      <c r="L243" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M243" t="s">
+        <v>42</v>
+      </c>
+      <c r="N243" t="s">
+        <v>63</v>
+      </c>
+      <c r="O243" t="s">
+        <v>25</v>
+      </c>
+      <c r="P243" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>695</v>
+      </c>
+      <c r="B244" t="s">
+        <v>730</v>
+      </c>
+      <c r="C244" t="s">
+        <v>18</v>
+      </c>
+      <c r="D244" t="s">
+        <v>740</v>
+      </c>
+      <c r="E244" t="s">
+        <v>60</v>
+      </c>
+      <c r="F244" t="s">
+        <v>45</v>
+      </c>
+      <c r="G244">
+        <v>27</v>
+      </c>
+      <c r="H244" t="s">
+        <v>36</v>
+      </c>
+      <c r="I244" t="s">
+        <v>54</v>
+      </c>
+      <c r="J244" t="s">
+        <v>741</v>
+      </c>
+      <c r="K244" t="s">
+        <v>25</v>
+      </c>
+      <c r="L244" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M244" t="s">
+        <v>17</v>
+      </c>
+      <c r="N244" t="s">
+        <v>68</v>
+      </c>
+      <c r="O244" t="s">
+        <v>187</v>
+      </c>
+      <c r="P244" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>695</v>
+      </c>
+      <c r="B245" t="s">
+        <v>730</v>
+      </c>
+      <c r="C245" t="s">
+        <v>18</v>
+      </c>
+      <c r="D245" t="s">
+        <v>742</v>
+      </c>
+      <c r="E245" t="s">
+        <v>60</v>
+      </c>
+      <c r="F245" t="s">
+        <v>45</v>
+      </c>
+      <c r="G245">
+        <v>22</v>
+      </c>
+      <c r="H245" t="s">
+        <v>743</v>
+      </c>
+      <c r="I245" t="s">
+        <v>54</v>
+      </c>
+      <c r="J245" t="s">
+        <v>744</v>
+      </c>
+      <c r="K245" t="s">
+        <v>25</v>
+      </c>
+      <c r="L245" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M245" t="s">
+        <v>17</v>
+      </c>
+      <c r="N245" t="s">
+        <v>68</v>
+      </c>
+      <c r="O245" t="s">
+        <v>187</v>
+      </c>
+      <c r="P245" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>695</v>
+      </c>
+      <c r="B246" t="s">
+        <v>17</v>
+      </c>
+      <c r="C246" t="s">
+        <v>18</v>
+      </c>
+      <c r="D246" t="s">
+        <v>745</v>
+      </c>
+      <c r="E246" t="s">
+        <v>60</v>
+      </c>
+      <c r="F246" t="s">
+        <v>45</v>
+      </c>
+      <c r="G246">
+        <v>30</v>
+      </c>
+      <c r="H246" t="s">
+        <v>255</v>
+      </c>
+      <c r="I246" t="s">
+        <v>93</v>
+      </c>
+      <c r="J246" t="s">
+        <v>746</v>
+      </c>
+      <c r="K246" t="s">
+        <v>25</v>
+      </c>
+      <c r="L246" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M246" t="s">
+        <v>17</v>
+      </c>
+      <c r="N246" t="s">
+        <v>747</v>
+      </c>
+      <c r="O246" t="s">
+        <v>25</v>
+      </c>
+      <c r="P246" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A247" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="B247" t="s">
+        <v>730</v>
+      </c>
+      <c r="C247" t="s">
+        <v>38</v>
+      </c>
+      <c r="D247" t="s">
+        <v>748</v>
+      </c>
+      <c r="E247" t="s">
+        <v>60</v>
+      </c>
+      <c r="F247" t="s">
+        <v>45</v>
+      </c>
+      <c r="G247">
+        <v>24</v>
+      </c>
+      <c r="H247" t="s">
+        <v>553</v>
+      </c>
+      <c r="I247" t="s">
+        <v>33</v>
+      </c>
+      <c r="J247" t="s">
+        <v>749</v>
+      </c>
+      <c r="K247" t="s">
+        <v>25</v>
+      </c>
+      <c r="L247" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M247" t="s">
+        <v>42</v>
+      </c>
+      <c r="N247" t="s">
+        <v>68</v>
+      </c>
+      <c r="O247" t="s">
+        <v>187</v>
+      </c>
+      <c r="P247" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A248" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="B248" t="s">
+        <v>17</v>
+      </c>
+      <c r="C248" t="s">
+        <v>38</v>
+      </c>
+      <c r="D248" t="s">
+        <v>750</v>
+      </c>
+      <c r="E248" t="s">
+        <v>60</v>
+      </c>
+      <c r="F248" t="s">
+        <v>45</v>
+      </c>
+      <c r="G248">
+        <v>32</v>
+      </c>
+      <c r="H248" t="s">
+        <v>751</v>
+      </c>
+      <c r="I248" t="s">
+        <v>33</v>
+      </c>
+      <c r="J248" t="s">
+        <v>752</v>
+      </c>
+      <c r="K248" t="s">
+        <v>25</v>
+      </c>
+      <c r="L248" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M248" t="s">
+        <v>42</v>
+      </c>
+      <c r="N248" t="s">
+        <v>753</v>
+      </c>
+      <c r="O248" t="s">
+        <v>25</v>
+      </c>
+      <c r="P248" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A249" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="B249" t="s">
+        <v>17</v>
+      </c>
+      <c r="C249" t="s">
+        <v>38</v>
+      </c>
+      <c r="D249" t="s">
+        <v>754</v>
+      </c>
+      <c r="E249" t="s">
+        <v>60</v>
+      </c>
+      <c r="F249" t="s">
+        <v>45</v>
+      </c>
+      <c r="G249">
+        <v>21</v>
+      </c>
+      <c r="H249" t="s">
+        <v>183</v>
+      </c>
+      <c r="I249" t="s">
+        <v>54</v>
+      </c>
+      <c r="J249" t="s">
+        <v>755</v>
+      </c>
+      <c r="K249" t="s">
+        <v>25</v>
+      </c>
+      <c r="L249" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M249" t="s">
+        <v>17</v>
+      </c>
+      <c r="N249" t="s">
+        <v>68</v>
+      </c>
+      <c r="O249" t="s">
+        <v>187</v>
+      </c>
+      <c r="P249" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>695</v>
+      </c>
+      <c r="B250" t="s">
+        <v>17</v>
+      </c>
+      <c r="C250" t="s">
+        <v>18</v>
+      </c>
+      <c r="D250" t="s">
+        <v>756</v>
+      </c>
+      <c r="E250" t="s">
+        <v>60</v>
+      </c>
+      <c r="F250" t="s">
+        <v>45</v>
+      </c>
+      <c r="G250">
+        <v>30</v>
+      </c>
+      <c r="H250" t="s">
+        <v>92</v>
+      </c>
+      <c r="I250" t="s">
+        <v>54</v>
+      </c>
+      <c r="J250" t="s">
+        <v>757</v>
+      </c>
+      <c r="K250" t="s">
+        <v>25</v>
+      </c>
+      <c r="L250" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M250" t="s">
+        <v>17</v>
+      </c>
+      <c r="N250" t="s">
+        <v>758</v>
+      </c>
+      <c r="O250" t="s">
+        <v>172</v>
+      </c>
+      <c r="P250" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>695</v>
+      </c>
+      <c r="B251" t="s">
+        <v>17</v>
+      </c>
+      <c r="C251" t="s">
+        <v>38</v>
+      </c>
+      <c r="D251" t="s">
+        <v>759</v>
+      </c>
+      <c r="E251" t="s">
+        <v>60</v>
+      </c>
+      <c r="F251" t="s">
+        <v>45</v>
+      </c>
+      <c r="G251">
+        <v>25</v>
+      </c>
+      <c r="H251" t="s">
+        <v>760</v>
+      </c>
+      <c r="I251" t="s">
+        <v>33</v>
+      </c>
+      <c r="J251" t="s">
+        <v>761</v>
+      </c>
+      <c r="K251" t="s">
+        <v>25</v>
+      </c>
+      <c r="L251" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M251" t="s">
+        <v>42</v>
+      </c>
+      <c r="N251" t="s">
+        <v>68</v>
+      </c>
+      <c r="O251" t="s">
+        <v>187</v>
+      </c>
+      <c r="P251" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>695</v>
+      </c>
+      <c r="B252" t="s">
+        <v>17</v>
+      </c>
+      <c r="C252" t="s">
+        <v>38</v>
+      </c>
+      <c r="D252" t="s">
+        <v>762</v>
+      </c>
+      <c r="E252" t="s">
+        <v>60</v>
+      </c>
+      <c r="F252" t="s">
+        <v>388</v>
+      </c>
+      <c r="G252">
+        <v>26</v>
+      </c>
+      <c r="H252" t="s">
+        <v>763</v>
+      </c>
+      <c r="I252" t="s">
+        <v>89</v>
+      </c>
+      <c r="J252" t="s">
+        <v>764</v>
+      </c>
+      <c r="K252" t="s">
+        <v>25</v>
+      </c>
+      <c r="L252" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M252" t="s">
+        <v>42</v>
+      </c>
+      <c r="N252" t="s">
+        <v>765</v>
+      </c>
+      <c r="O252" t="s">
+        <v>172</v>
+      </c>
+      <c r="P252" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>695</v>
+      </c>
+      <c r="B253" t="s">
+        <v>730</v>
+      </c>
+      <c r="C253" t="s">
+        <v>38</v>
+      </c>
+      <c r="D253" t="s">
+        <v>766</v>
+      </c>
+      <c r="E253" t="s">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>21</v>
+      </c>
+      <c r="G253">
+        <v>44</v>
+      </c>
+      <c r="H253" t="s">
+        <v>255</v>
+      </c>
+      <c r="I253" t="s">
+        <v>158</v>
+      </c>
+      <c r="J253" t="s">
+        <v>767</v>
+      </c>
+      <c r="K253" t="s">
+        <v>25</v>
+      </c>
+      <c r="L253" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M253" t="s">
+        <v>42</v>
+      </c>
+      <c r="N253" t="s">
+        <v>68</v>
+      </c>
+      <c r="O253" t="s">
+        <v>187</v>
+      </c>
+      <c r="P253" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>695</v>
+      </c>
+      <c r="B254" t="s">
+        <v>730</v>
+      </c>
+      <c r="C254" t="s">
+        <v>18</v>
+      </c>
+      <c r="D254" t="s">
+        <v>768</v>
+      </c>
+      <c r="E254" t="s">
+        <v>60</v>
+      </c>
+      <c r="F254" t="s">
+        <v>388</v>
+      </c>
+      <c r="G254">
+        <v>36</v>
+      </c>
+      <c r="H254" t="s">
+        <v>743</v>
+      </c>
+      <c r="I254" t="s">
+        <v>54</v>
+      </c>
+      <c r="J254" t="s">
+        <v>769</v>
+      </c>
+      <c r="K254" t="s">
+        <v>25</v>
+      </c>
+      <c r="L254" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M254" t="s">
+        <v>17</v>
+      </c>
+      <c r="N254" t="s">
+        <v>68</v>
+      </c>
+      <c r="O254" t="s">
+        <v>187</v>
+      </c>
+      <c r="P254" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>695</v>
+      </c>
+      <c r="B255" t="s">
+        <v>730</v>
+      </c>
+      <c r="C255" t="s">
+        <v>38</v>
+      </c>
+      <c r="D255" t="s">
+        <v>770</v>
+      </c>
+      <c r="E255" t="s">
+        <v>60</v>
+      </c>
+      <c r="F255" t="s">
+        <v>45</v>
+      </c>
+      <c r="G255">
+        <v>33</v>
+      </c>
+      <c r="H255" t="s">
+        <v>40</v>
+      </c>
+      <c r="I255" t="s">
+        <v>33</v>
+      </c>
+      <c r="J255" t="s">
+        <v>771</v>
+      </c>
+      <c r="K255" t="s">
+        <v>25</v>
+      </c>
+      <c r="L255" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="M255" t="s">
+        <v>42</v>
+      </c>
+      <c r="N255" t="s">
+        <v>772</v>
+      </c>
+      <c r="O255" t="s">
+        <v>25</v>
+      </c>
+      <c r="P255" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>695</v>
+      </c>
+      <c r="B256" t="s">
+        <v>17</v>
+      </c>
+      <c r="C256" t="s">
+        <v>38</v>
+      </c>
+      <c r="D256" t="s">
+        <v>773</v>
+      </c>
+      <c r="E256" t="s">
+        <v>60</v>
+      </c>
+      <c r="F256" t="s">
+        <v>45</v>
+      </c>
+      <c r="G256">
+        <v>43</v>
+      </c>
+      <c r="H256" t="s">
+        <v>207</v>
+      </c>
+      <c r="I256" t="s">
+        <v>33</v>
+      </c>
+      <c r="J256" t="s">
+        <v>774</v>
+      </c>
+      <c r="K256" t="s">
+        <v>25</v>
+      </c>
+      <c r="L256" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M256" t="s">
+        <v>42</v>
+      </c>
+      <c r="N256" t="s">
+        <v>63</v>
+      </c>
+      <c r="O256" t="s">
+        <v>172</v>
+      </c>
+      <c r="P256" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>775</v>
+      </c>
+      <c r="B257" t="s">
+        <v>407</v>
+      </c>
+      <c r="C257" t="s">
+        <v>38</v>
+      </c>
+      <c r="D257" t="s">
+        <v>776</v>
+      </c>
+      <c r="E257" t="s">
+        <v>20</v>
+      </c>
+      <c r="F257" t="s">
+        <v>45</v>
+      </c>
+      <c r="G257">
+        <v>30</v>
+      </c>
+      <c r="H257" t="s">
+        <v>763</v>
+      </c>
+      <c r="I257" t="s">
+        <v>54</v>
+      </c>
+      <c r="J257" t="s">
+        <v>777</v>
+      </c>
+      <c r="K257" t="s">
+        <v>25</v>
+      </c>
+      <c r="L257" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M257" t="s">
+        <v>42</v>
+      </c>
+      <c r="N257" t="s">
+        <v>276</v>
+      </c>
+      <c r="O257" t="s">
+        <v>28</v>
+      </c>
+      <c r="P257" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>775</v>
+      </c>
+      <c r="B258" t="s">
+        <v>407</v>
+      </c>
+      <c r="C258" t="s">
+        <v>38</v>
+      </c>
+      <c r="D258" t="s">
+        <v>778</v>
+      </c>
+      <c r="E258" t="s">
+        <v>20</v>
+      </c>
+      <c r="F258" t="s">
+        <v>31</v>
+      </c>
+      <c r="G258">
+        <v>34</v>
+      </c>
+      <c r="H258" t="s">
+        <v>53</v>
+      </c>
+      <c r="I258" t="s">
+        <v>89</v>
+      </c>
+      <c r="J258" t="s">
+        <v>779</v>
+      </c>
+      <c r="K258" t="s">
+        <v>25</v>
+      </c>
+      <c r="L258" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M258" t="s">
+        <v>42</v>
+      </c>
+      <c r="N258" t="s">
+        <v>276</v>
+      </c>
+      <c r="O258" t="s">
+        <v>28</v>
+      </c>
+      <c r="P258" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>775</v>
+      </c>
+      <c r="B259" t="s">
+        <v>407</v>
+      </c>
+      <c r="C259" t="s">
+        <v>38</v>
+      </c>
+      <c r="D259" t="s">
+        <v>780</v>
+      </c>
+      <c r="E259" t="s">
+        <v>20</v>
+      </c>
+      <c r="F259" t="s">
+        <v>31</v>
+      </c>
+      <c r="G259">
+        <v>22</v>
+      </c>
+      <c r="H259" t="s">
+        <v>36</v>
+      </c>
+      <c r="I259" t="s">
+        <v>54</v>
+      </c>
+      <c r="J259" t="s">
+        <v>781</v>
+      </c>
+      <c r="K259" t="s">
+        <v>25</v>
+      </c>
+      <c r="L259" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M259" t="s">
+        <v>17</v>
+      </c>
+      <c r="N259" t="s">
+        <v>617</v>
+      </c>
+      <c r="O259" t="s">
+        <v>28</v>
+      </c>
+      <c r="P259" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>775</v>
+      </c>
+      <c r="B260" t="s">
+        <v>407</v>
+      </c>
+      <c r="C260" t="s">
+        <v>38</v>
+      </c>
+      <c r="D260" t="s">
+        <v>782</v>
+      </c>
+      <c r="E260" t="s">
+        <v>20</v>
+      </c>
+      <c r="F260" t="s">
+        <v>31</v>
+      </c>
+      <c r="G260">
+        <v>30</v>
+      </c>
+      <c r="H260" t="s">
+        <v>783</v>
+      </c>
+      <c r="I260" t="s">
+        <v>54</v>
+      </c>
+      <c r="J260" t="s">
+        <v>784</v>
+      </c>
+      <c r="K260" t="s">
+        <v>25</v>
+      </c>
+      <c r="L260" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M260" t="s">
+        <v>289</v>
+      </c>
+      <c r="N260" t="s">
+        <v>276</v>
+      </c>
+      <c r="O260" t="s">
+        <v>28</v>
+      </c>
+      <c r="P260" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>775</v>
+      </c>
+      <c r="B261" t="s">
+        <v>407</v>
+      </c>
+      <c r="C261" t="s">
+        <v>18</v>
+      </c>
+      <c r="D261" t="s">
+        <v>785</v>
+      </c>
+      <c r="E261" t="s">
+        <v>20</v>
+      </c>
+      <c r="F261" t="s">
+        <v>21</v>
+      </c>
+      <c r="G261">
+        <v>30</v>
+      </c>
+      <c r="H261" t="s">
+        <v>786</v>
+      </c>
+      <c r="I261" t="s">
+        <v>54</v>
+      </c>
+      <c r="J261" t="s">
+        <v>787</v>
+      </c>
+      <c r="K261" t="s">
+        <v>25</v>
+      </c>
+      <c r="L261" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M261" t="s">
+        <v>17</v>
+      </c>
+      <c r="N261" t="s">
+        <v>276</v>
+      </c>
+      <c r="O261" t="s">
+        <v>25</v>
+      </c>
+      <c r="P261" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>775</v>
+      </c>
+      <c r="B262" t="s">
+        <v>407</v>
+      </c>
+      <c r="C262" t="s">
+        <v>38</v>
+      </c>
+      <c r="D262" t="s">
+        <v>788</v>
+      </c>
+      <c r="E262" t="s">
+        <v>20</v>
+      </c>
+      <c r="F262" t="s">
+        <v>31</v>
+      </c>
+      <c r="G262">
+        <v>37</v>
+      </c>
+      <c r="H262" t="s">
+        <v>789</v>
+      </c>
+      <c r="I262" t="s">
+        <v>179</v>
+      </c>
+      <c r="J262" t="s">
+        <v>790</v>
+      </c>
+      <c r="K262" t="s">
+        <v>25</v>
+      </c>
+      <c r="L262" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M262" t="s">
+        <v>42</v>
+      </c>
+      <c r="N262" t="s">
+        <v>276</v>
+      </c>
+      <c r="O262" t="s">
+        <v>28</v>
+      </c>
+      <c r="P262" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>775</v>
+      </c>
+      <c r="B263" t="s">
+        <v>407</v>
+      </c>
+      <c r="C263" t="s">
+        <v>38</v>
+      </c>
+      <c r="D263" t="s">
+        <v>791</v>
+      </c>
+      <c r="E263" t="s">
+        <v>20</v>
+      </c>
+      <c r="F263" t="s">
+        <v>31</v>
+      </c>
+      <c r="G263">
+        <v>46</v>
+      </c>
+      <c r="H263" t="s">
+        <v>77</v>
+      </c>
+      <c r="I263" t="s">
+        <v>33</v>
+      </c>
+      <c r="J263" t="s">
+        <v>792</v>
+      </c>
+      <c r="K263" t="s">
+        <v>25</v>
+      </c>
+      <c r="L263" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M263" t="s">
+        <v>42</v>
+      </c>
+      <c r="N263" t="s">
+        <v>276</v>
+      </c>
+      <c r="O263" t="s">
+        <v>25</v>
+      </c>
+      <c r="P263" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>775</v>
+      </c>
+      <c r="B264" t="s">
+        <v>407</v>
+      </c>
+      <c r="C264" t="s">
+        <v>65</v>
+      </c>
+      <c r="D264" t="s">
+        <v>793</v>
+      </c>
+      <c r="E264" t="s">
+        <v>20</v>
+      </c>
+      <c r="F264" t="s">
+        <v>45</v>
+      </c>
+      <c r="G264">
+        <v>30</v>
+      </c>
+      <c r="H264" t="s">
+        <v>794</v>
+      </c>
+      <c r="I264" t="s">
+        <v>54</v>
+      </c>
+      <c r="J264" t="s">
+        <v>795</v>
+      </c>
+      <c r="K264" t="s">
+        <v>25</v>
+      </c>
+      <c r="L264" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M264" t="s">
+        <v>17</v>
+      </c>
+      <c r="N264" t="s">
+        <v>276</v>
+      </c>
+      <c r="O264" t="s">
+        <v>28</v>
+      </c>
+      <c r="P264" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>775</v>
+      </c>
+      <c r="B265" t="s">
+        <v>407</v>
+      </c>
+      <c r="C265" t="s">
+        <v>18</v>
+      </c>
+      <c r="D265" t="s">
+        <v>796</v>
+      </c>
+      <c r="E265" t="s">
+        <v>20</v>
+      </c>
+      <c r="F265" t="s">
+        <v>45</v>
+      </c>
+      <c r="G265">
+        <v>30</v>
+      </c>
+      <c r="H265" t="s">
+        <v>255</v>
+      </c>
+      <c r="I265" t="s">
+        <v>54</v>
+      </c>
+      <c r="J265" t="s">
+        <v>797</v>
+      </c>
+      <c r="K265" t="s">
+        <v>25</v>
+      </c>
+      <c r="L265" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M265" t="s">
+        <v>42</v>
+      </c>
+      <c r="N265" t="s">
+        <v>276</v>
+      </c>
+      <c r="O265" t="s">
+        <v>28</v>
+      </c>
+      <c r="P265" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>775</v>
+      </c>
+      <c r="B266" t="s">
+        <v>407</v>
+      </c>
+      <c r="C266" t="s">
+        <v>18</v>
+      </c>
+      <c r="D266" t="s">
+        <v>798</v>
+      </c>
+      <c r="E266" t="s">
+        <v>20</v>
+      </c>
+      <c r="F266" t="s">
+        <v>45</v>
+      </c>
+      <c r="G266">
+        <v>61</v>
+      </c>
+      <c r="H266" t="s">
+        <v>53</v>
+      </c>
+      <c r="I266" t="s">
+        <v>54</v>
+      </c>
+      <c r="J266" t="s">
+        <v>799</v>
+      </c>
+      <c r="K266" t="s">
+        <v>25</v>
+      </c>
+      <c r="L266" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M266" t="s">
+        <v>17</v>
+      </c>
+      <c r="N266" t="s">
+        <v>276</v>
+      </c>
+      <c r="O266" t="s">
+        <v>25</v>
+      </c>
+      <c r="P266" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>775</v>
+      </c>
+      <c r="B267" t="s">
+        <v>17</v>
+      </c>
+      <c r="C267" t="s">
+        <v>18</v>
+      </c>
+      <c r="D267" t="s">
+        <v>800</v>
+      </c>
+      <c r="E267" t="s">
+        <v>20</v>
+      </c>
+      <c r="F267" t="s">
+        <v>45</v>
+      </c>
+      <c r="G267">
+        <v>29</v>
+      </c>
+      <c r="H267" t="s">
+        <v>719</v>
+      </c>
+      <c r="I267" t="s">
+        <v>33</v>
+      </c>
+      <c r="J267" t="s">
+        <v>801</v>
+      </c>
+      <c r="K267" t="s">
+        <v>25</v>
+      </c>
+      <c r="L267" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M267" t="s">
+        <v>17</v>
+      </c>
+      <c r="N267" t="s">
+        <v>276</v>
+      </c>
+      <c r="O267" t="s">
+        <v>25</v>
+      </c>
+      <c r="P267" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>775</v>
+      </c>
+      <c r="B268" t="s">
+        <v>17</v>
+      </c>
+      <c r="C268" t="s">
+        <v>38</v>
+      </c>
+      <c r="D268" t="s">
+        <v>802</v>
+      </c>
+      <c r="E268" t="s">
+        <v>20</v>
+      </c>
+      <c r="F268" t="s">
+        <v>31</v>
+      </c>
+      <c r="G268">
+        <v>22</v>
+      </c>
+      <c r="H268" t="s">
+        <v>17</v>
+      </c>
+      <c r="I268" t="s">
+        <v>803</v>
+      </c>
+      <c r="J268" t="s">
+        <v>804</v>
+      </c>
+      <c r="K268" t="s">
+        <v>25</v>
+      </c>
+      <c r="L268" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M268" t="s">
+        <v>42</v>
+      </c>
+      <c r="N268" t="s">
+        <v>276</v>
+      </c>
+      <c r="O268" t="s">
+        <v>28</v>
+      </c>
+      <c r="P268" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>775</v>
+      </c>
+      <c r="B269" t="s">
+        <v>17</v>
+      </c>
+      <c r="C269" t="s">
+        <v>38</v>
+      </c>
+      <c r="D269" t="s">
+        <v>805</v>
+      </c>
+      <c r="E269" t="s">
+        <v>20</v>
+      </c>
+      <c r="F269" t="s">
+        <v>21</v>
+      </c>
+      <c r="G269">
+        <v>58</v>
+      </c>
+      <c r="H269" t="s">
+        <v>806</v>
+      </c>
+      <c r="I269" t="s">
+        <v>807</v>
+      </c>
+      <c r="J269" t="s">
+        <v>808</v>
+      </c>
+      <c r="K269" t="s">
+        <v>25</v>
+      </c>
+      <c r="L269" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M269" t="s">
+        <v>42</v>
+      </c>
+      <c r="N269" t="s">
+        <v>276</v>
+      </c>
+      <c r="O269" t="s">
+        <v>28</v>
+      </c>
+      <c r="P269" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>775</v>
+      </c>
+      <c r="B270" t="s">
+        <v>17</v>
+      </c>
+      <c r="C270" t="s">
+        <v>38</v>
+      </c>
+      <c r="D270" t="s">
+        <v>809</v>
+      </c>
+      <c r="E270" t="s">
+        <v>20</v>
+      </c>
+      <c r="F270" t="s">
+        <v>45</v>
+      </c>
+      <c r="G270">
+        <v>30</v>
+      </c>
+      <c r="H270" t="s">
+        <v>255</v>
+      </c>
+      <c r="I270" t="s">
+        <v>33</v>
+      </c>
+      <c r="J270" t="s">
+        <v>810</v>
+      </c>
+      <c r="K270" t="s">
+        <v>25</v>
+      </c>
+      <c r="L270" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M270" t="s">
+        <v>268</v>
+      </c>
+      <c r="N270" t="s">
+        <v>276</v>
+      </c>
+      <c r="O270" t="s">
+        <v>25</v>
+      </c>
+      <c r="P270" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>811</v>
+      </c>
+      <c r="B271" t="s">
+        <v>17</v>
+      </c>
+      <c r="C271" t="s">
+        <v>18</v>
+      </c>
+      <c r="D271" t="s">
+        <v>812</v>
+      </c>
+      <c r="E271" t="s">
+        <v>20</v>
+      </c>
+      <c r="F271" t="s">
+        <v>45</v>
+      </c>
+      <c r="G271">
+        <v>24</v>
+      </c>
+      <c r="H271" t="s">
+        <v>46</v>
+      </c>
+      <c r="I271" t="s">
+        <v>33</v>
+      </c>
+      <c r="J271" t="s">
+        <v>813</v>
+      </c>
+      <c r="K271" t="s">
+        <v>25</v>
+      </c>
+      <c r="L271" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M271" t="s">
+        <v>42</v>
+      </c>
+      <c r="N271" t="s">
+        <v>276</v>
+      </c>
+      <c r="O271" t="s">
+        <v>28</v>
+      </c>
+      <c r="P271" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>775</v>
+      </c>
+      <c r="B272" t="s">
+        <v>407</v>
+      </c>
+      <c r="C272" t="s">
+        <v>38</v>
+      </c>
+      <c r="D272" t="s">
+        <v>814</v>
+      </c>
+      <c r="E272" t="s">
+        <v>60</v>
+      </c>
+      <c r="F272" t="s">
+        <v>45</v>
+      </c>
+      <c r="G272">
+        <v>26</v>
+      </c>
+      <c r="H272" t="s">
+        <v>815</v>
+      </c>
+      <c r="I272" t="s">
+        <v>33</v>
+      </c>
+      <c r="J272" t="s">
+        <v>816</v>
+      </c>
+      <c r="K272" t="s">
+        <v>25</v>
+      </c>
+      <c r="L272" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M272" t="s">
+        <v>42</v>
+      </c>
+      <c r="N272" t="s">
+        <v>817</v>
+      </c>
+      <c r="O272" t="s">
+        <v>25</v>
+      </c>
+      <c r="P272" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>775</v>
+      </c>
+      <c r="B273" t="s">
+        <v>407</v>
+      </c>
+      <c r="C273" t="s">
+        <v>38</v>
+      </c>
+      <c r="D273" t="s">
+        <v>818</v>
+      </c>
+      <c r="E273" t="s">
+        <v>60</v>
+      </c>
+      <c r="F273" t="s">
+        <v>17</v>
+      </c>
+      <c r="G273">
+        <v>30</v>
+      </c>
+      <c r="H273" t="s">
+        <v>819</v>
+      </c>
+      <c r="I273" t="s">
+        <v>33</v>
+      </c>
+      <c r="J273" t="s">
+        <v>820</v>
+      </c>
+      <c r="K273" t="s">
+        <v>25</v>
+      </c>
+      <c r="L273" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M273" t="s">
+        <v>42</v>
+      </c>
+      <c r="N273" t="s">
+        <v>821</v>
+      </c>
+      <c r="O273" t="s">
+        <v>172</v>
+      </c>
+      <c r="P273" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>775</v>
+      </c>
+      <c r="B274" t="s">
+        <v>407</v>
+      </c>
+      <c r="C274" t="s">
+        <v>38</v>
+      </c>
+      <c r="D274" t="s">
+        <v>822</v>
+      </c>
+      <c r="E274" t="s">
+        <v>60</v>
+      </c>
+      <c r="F274" t="s">
+        <v>45</v>
+      </c>
+      <c r="G274">
+        <v>54</v>
+      </c>
+      <c r="H274" t="s">
+        <v>823</v>
+      </c>
+      <c r="I274" t="s">
+        <v>33</v>
+      </c>
+      <c r="J274" t="s">
+        <v>152</v>
+      </c>
+      <c r="K274" t="s">
+        <v>25</v>
+      </c>
+      <c r="L274" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M274" t="s">
+        <v>17</v>
+      </c>
+      <c r="N274" t="s">
+        <v>68</v>
+      </c>
+      <c r="O274" t="s">
+        <v>28</v>
+      </c>
+      <c r="P274" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>775</v>
+      </c>
+      <c r="B275" t="s">
+        <v>407</v>
+      </c>
+      <c r="C275" t="s">
+        <v>38</v>
+      </c>
+      <c r="D275" t="s">
+        <v>824</v>
+      </c>
+      <c r="E275" t="s">
+        <v>60</v>
+      </c>
+      <c r="F275" t="s">
+        <v>21</v>
+      </c>
+      <c r="G275">
+        <v>44</v>
+      </c>
+      <c r="H275" t="s">
+        <v>825</v>
+      </c>
+      <c r="I275" t="s">
+        <v>33</v>
+      </c>
+      <c r="J275" t="s">
+        <v>826</v>
+      </c>
+      <c r="K275" t="s">
+        <v>25</v>
+      </c>
+      <c r="L275" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M275" t="s">
+        <v>42</v>
+      </c>
+      <c r="N275" t="s">
+        <v>68</v>
+      </c>
+      <c r="O275" t="s">
+        <v>28</v>
+      </c>
+      <c r="P275" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>775</v>
+      </c>
+      <c r="B276" t="s">
+        <v>407</v>
+      </c>
+      <c r="C276" t="s">
+        <v>18</v>
+      </c>
+      <c r="D276" t="s">
+        <v>827</v>
+      </c>
+      <c r="E276" t="s">
+        <v>60</v>
+      </c>
+      <c r="F276" t="s">
+        <v>45</v>
+      </c>
+      <c r="G276">
+        <v>18</v>
+      </c>
+      <c r="H276" t="s">
+        <v>528</v>
+      </c>
+      <c r="I276" t="s">
+        <v>33</v>
+      </c>
+      <c r="J276" t="s">
+        <v>828</v>
+      </c>
+      <c r="K276" t="s">
+        <v>25</v>
+      </c>
+      <c r="L276" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M276" t="s">
+        <v>17</v>
+      </c>
+      <c r="N276" t="s">
+        <v>829</v>
+      </c>
+      <c r="O276" t="s">
+        <v>25</v>
+      </c>
+      <c r="P276" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>775</v>
+      </c>
+      <c r="B277" t="s">
+        <v>407</v>
+      </c>
+      <c r="C277" t="s">
+        <v>38</v>
+      </c>
+      <c r="D277" t="s">
+        <v>830</v>
+      </c>
+      <c r="E277" t="s">
+        <v>60</v>
+      </c>
+      <c r="F277" t="s">
+        <v>17</v>
+      </c>
+      <c r="G277">
+        <v>30</v>
+      </c>
+      <c r="H277" t="s">
+        <v>36</v>
+      </c>
+      <c r="I277" t="s">
+        <v>33</v>
+      </c>
+      <c r="J277" t="s">
+        <v>831</v>
+      </c>
+      <c r="K277" t="s">
+        <v>25</v>
+      </c>
+      <c r="L277" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M277" t="s">
+        <v>42</v>
+      </c>
+      <c r="N277" t="s">
+        <v>68</v>
+      </c>
+      <c r="O277" t="s">
+        <v>28</v>
+      </c>
+      <c r="P277" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>775</v>
+      </c>
+      <c r="B278" t="s">
+        <v>407</v>
+      </c>
+      <c r="C278" t="s">
+        <v>18</v>
+      </c>
+      <c r="D278" t="s">
+        <v>832</v>
+      </c>
+      <c r="E278" t="s">
+        <v>60</v>
+      </c>
+      <c r="F278" t="s">
+        <v>21</v>
+      </c>
+      <c r="G278">
+        <v>51</v>
+      </c>
+      <c r="H278" t="s">
+        <v>57</v>
+      </c>
+      <c r="I278" t="s">
+        <v>33</v>
+      </c>
+      <c r="J278" t="s">
+        <v>833</v>
+      </c>
+      <c r="K278" t="s">
+        <v>25</v>
+      </c>
+      <c r="L278" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M278" t="s">
+        <v>42</v>
+      </c>
+      <c r="N278" t="s">
+        <v>817</v>
+      </c>
+      <c r="O278" t="s">
+        <v>25</v>
+      </c>
+      <c r="P278" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>775</v>
+      </c>
+      <c r="B279" t="s">
+        <v>407</v>
+      </c>
+      <c r="C279" t="s">
+        <v>38</v>
+      </c>
+      <c r="D279" t="s">
+        <v>834</v>
+      </c>
+      <c r="E279" t="s">
+        <v>60</v>
+      </c>
+      <c r="F279" t="s">
+        <v>31</v>
+      </c>
+      <c r="G279">
+        <v>51</v>
+      </c>
+      <c r="H279" t="s">
+        <v>17</v>
+      </c>
+      <c r="I279" t="s">
+        <v>54</v>
+      </c>
+      <c r="J279" t="s">
+        <v>835</v>
+      </c>
+      <c r="K279" t="s">
+        <v>25</v>
+      </c>
+      <c r="L279" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M279" t="s">
+        <v>42</v>
+      </c>
+      <c r="N279" t="s">
+        <v>68</v>
+      </c>
+      <c r="O279" t="s">
+        <v>28</v>
+      </c>
+      <c r="P279" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>775</v>
+      </c>
+      <c r="B280" t="s">
+        <v>407</v>
+      </c>
+      <c r="C280" t="s">
+        <v>38</v>
+      </c>
+      <c r="D280" t="s">
+        <v>836</v>
+      </c>
+      <c r="E280" t="s">
+        <v>60</v>
+      </c>
+      <c r="F280" t="s">
+        <v>45</v>
+      </c>
+      <c r="G280">
+        <v>51</v>
+      </c>
+      <c r="H280" t="s">
+        <v>321</v>
+      </c>
+      <c r="I280" t="s">
+        <v>33</v>
+      </c>
+      <c r="J280" t="s">
+        <v>837</v>
+      </c>
+      <c r="K280" t="s">
+        <v>25</v>
+      </c>
+      <c r="L280" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="M280" t="s">
+        <v>42</v>
+      </c>
+      <c r="N280" t="s">
+        <v>838</v>
+      </c>
+      <c r="O280" t="s">
+        <v>25</v>
+      </c>
+      <c r="P280" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>775</v>
+      </c>
+      <c r="B281" t="s">
+        <v>17</v>
+      </c>
+      <c r="C281" t="s">
+        <v>38</v>
+      </c>
+      <c r="D281" t="s">
+        <v>839</v>
+      </c>
+      <c r="E281" t="s">
+        <v>60</v>
+      </c>
+      <c r="F281" t="s">
+        <v>45</v>
+      </c>
+      <c r="G281">
+        <v>18</v>
+      </c>
+      <c r="H281" t="s">
+        <v>17</v>
+      </c>
+      <c r="I281" t="s">
+        <v>54</v>
+      </c>
+      <c r="J281" t="s">
+        <v>840</v>
+      </c>
+      <c r="K281" t="s">
+        <v>25</v>
+      </c>
+      <c r="L281" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M281" t="s">
+        <v>17</v>
+      </c>
+      <c r="N281" t="s">
+        <v>68</v>
+      </c>
+      <c r="O281" t="s">
+        <v>28</v>
+      </c>
+      <c r="P281" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>775</v>
+      </c>
+      <c r="B282" t="s">
+        <v>17</v>
+      </c>
+      <c r="C282" t="s">
+        <v>38</v>
+      </c>
+      <c r="D282" t="s">
+        <v>841</v>
+      </c>
+      <c r="E282" t="s">
+        <v>60</v>
+      </c>
+      <c r="F282" t="s">
+        <v>45</v>
+      </c>
+      <c r="G282">
+        <v>30</v>
+      </c>
+      <c r="H282" t="s">
+        <v>127</v>
+      </c>
+      <c r="I282" t="s">
+        <v>33</v>
+      </c>
+      <c r="J282" t="s">
+        <v>842</v>
+      </c>
+      <c r="K282" t="s">
+        <v>25</v>
+      </c>
+      <c r="L282" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M282" t="s">
+        <v>17</v>
+      </c>
+      <c r="N282" t="s">
+        <v>68</v>
+      </c>
+      <c r="O282" t="s">
+        <v>28</v>
+      </c>
+      <c r="P282" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>775</v>
+      </c>
+      <c r="B283" t="s">
+        <v>17</v>
+      </c>
+      <c r="C283" t="s">
+        <v>65</v>
+      </c>
+      <c r="D283" t="s">
+        <v>843</v>
+      </c>
+      <c r="E283" t="s">
+        <v>60</v>
+      </c>
+      <c r="F283" t="s">
+        <v>45</v>
+      </c>
+      <c r="G283">
+        <v>15</v>
+      </c>
+      <c r="H283" t="s">
+        <v>46</v>
+      </c>
+      <c r="I283" t="s">
+        <v>33</v>
+      </c>
+      <c r="J283" t="s">
+        <v>844</v>
+      </c>
+      <c r="K283" t="s">
+        <v>25</v>
+      </c>
+      <c r="L283" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M283" t="s">
+        <v>42</v>
+      </c>
+      <c r="N283" t="s">
+        <v>68</v>
+      </c>
+      <c r="O283" t="s">
+        <v>28</v>
+      </c>
+      <c r="P283" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>775</v>
+      </c>
+      <c r="B284" t="s">
+        <v>17</v>
+      </c>
+      <c r="C284" t="s">
+        <v>18</v>
+      </c>
+      <c r="D284" t="s">
+        <v>845</v>
+      </c>
+      <c r="E284" t="s">
+        <v>60</v>
+      </c>
+      <c r="F284" t="s">
+        <v>144</v>
+      </c>
+      <c r="G284">
+        <v>61</v>
+      </c>
+      <c r="H284" t="s">
+        <v>102</v>
+      </c>
+      <c r="I284" t="s">
+        <v>179</v>
+      </c>
+      <c r="J284" t="s">
+        <v>846</v>
+      </c>
+      <c r="K284" t="s">
+        <v>25</v>
+      </c>
+      <c r="L284" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M284" t="s">
+        <v>17</v>
+      </c>
+      <c r="N284" t="s">
+        <v>68</v>
+      </c>
+      <c r="O284" t="s">
+        <v>28</v>
+      </c>
+      <c r="P284" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>775</v>
+      </c>
+      <c r="B285" t="s">
+        <v>17</v>
+      </c>
+      <c r="C285" t="s">
+        <v>18</v>
+      </c>
+      <c r="D285" t="s">
+        <v>847</v>
+      </c>
+      <c r="E285" t="s">
+        <v>60</v>
+      </c>
+      <c r="F285" t="s">
+        <v>45</v>
+      </c>
+      <c r="G285">
+        <v>23</v>
+      </c>
+      <c r="H285" t="s">
+        <v>92</v>
+      </c>
+      <c r="I285" t="s">
+        <v>179</v>
+      </c>
+      <c r="J285" t="s">
+        <v>848</v>
+      </c>
+      <c r="K285" t="s">
+        <v>25</v>
+      </c>
+      <c r="L285" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M285" t="s">
+        <v>42</v>
+      </c>
+      <c r="N285" t="s">
+        <v>849</v>
+      </c>
+      <c r="O285" t="s">
+        <v>25</v>
+      </c>
+      <c r="P285" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>775</v>
+      </c>
+      <c r="B286" t="s">
+        <v>17</v>
+      </c>
+      <c r="C286" t="s">
+        <v>38</v>
+      </c>
+      <c r="D286" t="s">
+        <v>850</v>
+      </c>
+      <c r="E286" t="s">
+        <v>60</v>
+      </c>
+      <c r="F286" t="s">
+        <v>31</v>
+      </c>
+      <c r="G286">
+        <v>25</v>
+      </c>
+      <c r="H286" t="s">
+        <v>719</v>
+      </c>
+      <c r="I286" t="s">
+        <v>851</v>
+      </c>
+      <c r="J286" t="s">
+        <v>852</v>
+      </c>
+      <c r="K286" t="s">
+        <v>25</v>
+      </c>
+      <c r="L286" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M286" t="s">
+        <v>42</v>
+      </c>
+      <c r="N286" t="s">
+        <v>68</v>
+      </c>
+      <c r="O286" t="s">
+        <v>28</v>
+      </c>
+      <c r="P286" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>811</v>
+      </c>
+      <c r="B287" t="s">
+        <v>17</v>
+      </c>
+      <c r="C287" t="s">
+        <v>18</v>
+      </c>
+      <c r="D287" t="s">
+        <v>853</v>
+      </c>
+      <c r="E287" t="s">
+        <v>60</v>
+      </c>
+      <c r="F287" t="s">
+        <v>31</v>
+      </c>
+      <c r="G287">
+        <v>18</v>
+      </c>
+      <c r="H287" t="s">
+        <v>50</v>
+      </c>
+      <c r="I287" t="s">
+        <v>33</v>
+      </c>
+      <c r="J287" t="s">
+        <v>500</v>
+      </c>
+      <c r="K287" t="s">
+        <v>25</v>
+      </c>
+      <c r="L287" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M287" t="s">
+        <v>280</v>
+      </c>
+      <c r="N287" t="s">
+        <v>854</v>
+      </c>
+      <c r="O287" t="s">
+        <v>25</v>
+      </c>
+      <c r="P287" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A288" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="B288" t="s">
+        <v>17</v>
+      </c>
+      <c r="C288" t="s">
+        <v>18</v>
+      </c>
+      <c r="D288" t="s">
+        <v>855</v>
+      </c>
+      <c r="E288" t="s">
+        <v>60</v>
+      </c>
+      <c r="F288" t="s">
+        <v>45</v>
+      </c>
+      <c r="G288">
+        <v>19</v>
+      </c>
+      <c r="H288" t="s">
+        <v>40</v>
+      </c>
+      <c r="I288" t="s">
+        <v>33</v>
+      </c>
+      <c r="J288" t="s">
+        <v>856</v>
+      </c>
+      <c r="K288" t="s">
+        <v>25</v>
+      </c>
+      <c r="L288" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M288" t="s">
+        <v>17</v>
+      </c>
+      <c r="N288" t="s">
+        <v>854</v>
+      </c>
+      <c r="O288" t="s">
+        <v>25</v>
+      </c>
+      <c r="P288" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>811</v>
+      </c>
+      <c r="B289" t="s">
+        <v>359</v>
+      </c>
+      <c r="C289" t="s">
+        <v>38</v>
+      </c>
+      <c r="D289" t="s">
+        <v>857</v>
+      </c>
+      <c r="E289" t="s">
+        <v>60</v>
+      </c>
+      <c r="F289" t="s">
+        <v>45</v>
+      </c>
+      <c r="G289">
+        <v>21</v>
+      </c>
+      <c r="H289" t="s">
+        <v>135</v>
+      </c>
+      <c r="I289" t="s">
+        <v>33</v>
+      </c>
+      <c r="J289" t="s">
+        <v>858</v>
+      </c>
+      <c r="K289" t="s">
+        <v>25</v>
+      </c>
+      <c r="L289" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M289" t="s">
+        <v>17</v>
+      </c>
+      <c r="N289" t="s">
+        <v>859</v>
+      </c>
+      <c r="O289" t="s">
+        <v>25</v>
+      </c>
+      <c r="P289" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>811</v>
+      </c>
+      <c r="B290" t="s">
+        <v>17</v>
+      </c>
+      <c r="C290" t="s">
+        <v>38</v>
+      </c>
+      <c r="D290" t="s">
+        <v>860</v>
+      </c>
+      <c r="E290" t="s">
+        <v>60</v>
+      </c>
+      <c r="F290" t="s">
+        <v>21</v>
+      </c>
+      <c r="G290">
+        <v>48</v>
+      </c>
+      <c r="H290" t="s">
+        <v>40</v>
+      </c>
+      <c r="I290" t="s">
+        <v>33</v>
+      </c>
+      <c r="J290" t="s">
+        <v>861</v>
+      </c>
+      <c r="K290" t="s">
+        <v>25</v>
+      </c>
+      <c r="L290" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M290" t="s">
+        <v>17</v>
+      </c>
+      <c r="N290" t="s">
+        <v>862</v>
+      </c>
+      <c r="O290" t="s">
+        <v>25</v>
+      </c>
+      <c r="P290" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>811</v>
+      </c>
+      <c r="B291" t="s">
+        <v>359</v>
+      </c>
+      <c r="C291" t="s">
+        <v>38</v>
+      </c>
+      <c r="D291" t="s">
+        <v>863</v>
+      </c>
+      <c r="E291" t="s">
+        <v>60</v>
+      </c>
+      <c r="F291" t="s">
+        <v>45</v>
+      </c>
+      <c r="G291">
+        <v>20</v>
+      </c>
+      <c r="H291" t="s">
+        <v>40</v>
+      </c>
+      <c r="I291" t="s">
+        <v>33</v>
+      </c>
+      <c r="J291" t="s">
+        <v>864</v>
+      </c>
+      <c r="K291" t="s">
+        <v>25</v>
+      </c>
+      <c r="L291" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M291" t="s">
+        <v>42</v>
+      </c>
+      <c r="N291" t="s">
+        <v>817</v>
+      </c>
+      <c r="O291" t="s">
+        <v>25</v>
+      </c>
+      <c r="P291" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>865</v>
+      </c>
+      <c r="B292" t="s">
+        <v>17</v>
+      </c>
+      <c r="C292" t="s">
+        <v>65</v>
+      </c>
+      <c r="D292" t="s">
+        <v>866</v>
+      </c>
+      <c r="E292" t="s">
+        <v>60</v>
+      </c>
+      <c r="F292" t="s">
+        <v>45</v>
+      </c>
+      <c r="G292">
+        <v>30</v>
+      </c>
+      <c r="H292" t="s">
+        <v>17</v>
+      </c>
+      <c r="I292" t="s">
+        <v>54</v>
+      </c>
+      <c r="J292" t="s">
+        <v>867</v>
+      </c>
+      <c r="K292" t="s">
+        <v>25</v>
+      </c>
+      <c r="L292" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M292" t="s">
+        <v>17</v>
+      </c>
+      <c r="N292" t="s">
+        <v>817</v>
+      </c>
+      <c r="O292" t="s">
+        <v>25</v>
+      </c>
+      <c r="P292" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>868</v>
+      </c>
+      <c r="B293" t="s">
+        <v>17</v>
+      </c>
+      <c r="C293" t="s">
+        <v>18</v>
+      </c>
+      <c r="D293" t="s">
+        <v>869</v>
+      </c>
+      <c r="E293" t="s">
+        <v>20</v>
+      </c>
+      <c r="F293" t="s">
+        <v>45</v>
+      </c>
+      <c r="G293">
+        <v>19</v>
+      </c>
+      <c r="H293" t="s">
+        <v>151</v>
+      </c>
+      <c r="I293" t="s">
+        <v>33</v>
+      </c>
+      <c r="J293" t="s">
+        <v>870</v>
+      </c>
+      <c r="K293" t="s">
+        <v>25</v>
+      </c>
+      <c r="L293" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M293" t="s">
+        <v>289</v>
+      </c>
+      <c r="N293" t="s">
+        <v>276</v>
+      </c>
+      <c r="O293" t="s">
+        <v>28</v>
+      </c>
+      <c r="P293" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>868</v>
+      </c>
+      <c r="B294" t="s">
+        <v>407</v>
+      </c>
+      <c r="C294" t="s">
+        <v>38</v>
+      </c>
+      <c r="D294" t="s">
+        <v>871</v>
+      </c>
+      <c r="E294" t="s">
+        <v>20</v>
+      </c>
+      <c r="F294" t="s">
+        <v>31</v>
+      </c>
+      <c r="G294">
+        <v>37</v>
+      </c>
+      <c r="H294" t="s">
+        <v>102</v>
+      </c>
+      <c r="I294" t="s">
+        <v>33</v>
+      </c>
+      <c r="J294" t="s">
+        <v>872</v>
+      </c>
+      <c r="K294" t="s">
+        <v>25</v>
+      </c>
+      <c r="L294" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="M294" t="s">
+        <v>42</v>
+      </c>
+      <c r="N294" t="s">
+        <v>276</v>
+      </c>
+      <c r="O294" t="s">
+        <v>28</v>
+      </c>
+      <c r="P294" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>868</v>
+      </c>
+      <c r="B295" t="s">
+        <v>17</v>
+      </c>
+      <c r="C295" t="s">
+        <v>18</v>
+      </c>
+      <c r="D295" t="s">
+        <v>873</v>
+      </c>
+      <c r="E295" t="s">
+        <v>20</v>
+      </c>
+      <c r="F295" t="s">
+        <v>31</v>
+      </c>
+      <c r="G295">
+        <v>50</v>
+      </c>
+      <c r="H295" t="s">
+        <v>255</v>
+      </c>
+      <c r="I295" t="s">
+        <v>89</v>
+      </c>
+      <c r="J295" t="s">
+        <v>874</v>
+      </c>
+      <c r="K295" t="s">
+        <v>25</v>
+      </c>
+      <c r="L295" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M295" t="s">
+        <v>42</v>
+      </c>
+      <c r="N295" t="s">
+        <v>276</v>
+      </c>
+      <c r="O295" t="s">
+        <v>25</v>
+      </c>
+      <c r="P295" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>868</v>
+      </c>
+      <c r="B296" t="s">
+        <v>17</v>
+      </c>
+      <c r="C296" t="s">
+        <v>38</v>
+      </c>
+      <c r="D296" t="s">
+        <v>875</v>
+      </c>
+      <c r="E296" t="s">
+        <v>20</v>
+      </c>
+      <c r="F296" t="s">
+        <v>45</v>
+      </c>
+      <c r="G296">
+        <v>29</v>
+      </c>
+      <c r="H296" t="s">
+        <v>528</v>
+      </c>
+      <c r="I296" t="s">
+        <v>33</v>
+      </c>
+      <c r="J296" t="s">
+        <v>876</v>
+      </c>
+      <c r="K296" t="s">
+        <v>25</v>
+      </c>
+      <c r="L296" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M296" t="s">
+        <v>42</v>
+      </c>
+      <c r="N296" t="s">
+        <v>276</v>
+      </c>
+      <c r="O296" t="s">
+        <v>28</v>
+      </c>
+      <c r="P296" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>868</v>
+      </c>
+      <c r="B297" t="s">
+        <v>407</v>
+      </c>
+      <c r="C297" t="s">
+        <v>38</v>
+      </c>
+      <c r="D297" t="s">
+        <v>877</v>
+      </c>
+      <c r="E297" t="s">
+        <v>20</v>
+      </c>
+      <c r="F297" t="s">
+        <v>31</v>
+      </c>
+      <c r="G297">
+        <v>32</v>
+      </c>
+      <c r="H297" t="s">
+        <v>57</v>
+      </c>
+      <c r="I297" t="s">
+        <v>33</v>
+      </c>
+      <c r="J297" t="s">
+        <v>878</v>
+      </c>
+      <c r="K297" t="s">
+        <v>25</v>
+      </c>
+      <c r="L297" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M297" t="s">
+        <v>42</v>
+      </c>
+      <c r="N297" t="s">
+        <v>276</v>
+      </c>
+      <c r="O297" t="s">
+        <v>28</v>
+      </c>
+      <c r="P297" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>868</v>
+      </c>
+      <c r="B298" t="s">
+        <v>17</v>
+      </c>
+      <c r="C298" t="s">
+        <v>38</v>
+      </c>
+      <c r="D298" t="s">
+        <v>879</v>
+      </c>
+      <c r="E298" t="s">
+        <v>20</v>
+      </c>
+      <c r="F298" t="s">
+        <v>45</v>
+      </c>
+      <c r="G298">
+        <v>30</v>
+      </c>
+      <c r="H298" t="s">
+        <v>880</v>
+      </c>
+      <c r="I298" t="s">
+        <v>89</v>
+      </c>
+      <c r="J298" t="s">
+        <v>881</v>
+      </c>
+      <c r="K298" t="s">
+        <v>25</v>
+      </c>
+      <c r="L298" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M298" t="s">
+        <v>42</v>
+      </c>
+      <c r="N298" t="s">
+        <v>276</v>
+      </c>
+      <c r="O298" t="s">
+        <v>28</v>
+      </c>
+      <c r="P298" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>882</v>
+      </c>
+      <c r="B299" t="s">
+        <v>883</v>
+      </c>
+      <c r="C299" t="s">
+        <v>18</v>
+      </c>
+      <c r="D299" t="s">
+        <v>884</v>
+      </c>
+      <c r="E299" t="s">
+        <v>20</v>
+      </c>
+      <c r="F299" t="s">
+        <v>45</v>
+      </c>
+      <c r="G299">
+        <v>30</v>
+      </c>
+      <c r="H299" t="s">
+        <v>17</v>
+      </c>
+      <c r="I299" t="s">
+        <v>54</v>
+      </c>
+      <c r="J299" t="s">
+        <v>885</v>
+      </c>
+      <c r="K299" t="s">
+        <v>25</v>
+      </c>
+      <c r="L299" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M299" t="s">
+        <v>17</v>
+      </c>
+      <c r="N299" t="s">
+        <v>276</v>
+      </c>
+      <c r="O299" t="s">
+        <v>28</v>
+      </c>
+      <c r="P299" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>868</v>
+      </c>
+      <c r="B300" t="s">
+        <v>17</v>
+      </c>
+      <c r="C300" t="s">
+        <v>18</v>
+      </c>
+      <c r="D300" t="s">
+        <v>886</v>
+      </c>
+      <c r="E300" t="s">
+        <v>60</v>
+      </c>
+      <c r="F300" t="s">
+        <v>31</v>
+      </c>
+      <c r="G300">
+        <v>33</v>
+      </c>
+      <c r="H300" t="s">
+        <v>102</v>
+      </c>
+      <c r="I300" t="s">
+        <v>33</v>
+      </c>
+      <c r="J300" t="s">
+        <v>887</v>
+      </c>
+      <c r="K300" t="s">
+        <v>25</v>
+      </c>
+      <c r="L300" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M300" t="s">
+        <v>42</v>
+      </c>
+      <c r="N300" t="s">
+        <v>888</v>
+      </c>
+      <c r="O300" t="s">
+        <v>172</v>
+      </c>
+      <c r="P300" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>868</v>
+      </c>
+      <c r="B301" t="s">
+        <v>17</v>
+      </c>
+      <c r="C301" t="s">
+        <v>18</v>
+      </c>
+      <c r="D301" t="s">
+        <v>889</v>
+      </c>
+      <c r="E301" t="s">
+        <v>60</v>
+      </c>
+      <c r="F301" t="s">
+        <v>45</v>
+      </c>
+      <c r="G301">
+        <v>31</v>
+      </c>
+      <c r="H301" t="s">
+        <v>46</v>
+      </c>
+      <c r="I301" t="s">
+        <v>33</v>
+      </c>
+      <c r="J301" t="s">
+        <v>890</v>
+      </c>
+      <c r="K301" t="s">
+        <v>25</v>
+      </c>
+      <c r="L301" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M301" t="s">
+        <v>42</v>
+      </c>
+      <c r="N301" t="s">
+        <v>891</v>
+      </c>
+      <c r="O301" t="s">
+        <v>25</v>
+      </c>
+      <c r="P301" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>868</v>
+      </c>
+      <c r="B302" t="s">
+        <v>407</v>
+      </c>
+      <c r="C302" t="s">
+        <v>18</v>
+      </c>
+      <c r="D302" t="s">
+        <v>892</v>
+      </c>
+      <c r="E302" t="s">
+        <v>60</v>
+      </c>
+      <c r="F302" t="s">
+        <v>45</v>
+      </c>
+      <c r="G302">
+        <v>19</v>
+      </c>
+      <c r="H302" t="s">
+        <v>893</v>
+      </c>
+      <c r="I302" t="s">
+        <v>33</v>
+      </c>
+      <c r="J302" t="s">
+        <v>894</v>
+      </c>
+      <c r="K302" t="s">
+        <v>25</v>
+      </c>
+      <c r="L302" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M302" t="s">
+        <v>17</v>
+      </c>
+      <c r="N302" t="s">
+        <v>895</v>
+      </c>
+      <c r="O302" t="s">
+        <v>28</v>
+      </c>
+      <c r="P302" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>868</v>
+      </c>
+      <c r="B303" t="s">
+        <v>17</v>
+      </c>
+      <c r="C303" t="s">
+        <v>38</v>
+      </c>
+      <c r="D303" t="s">
+        <v>896</v>
+      </c>
+      <c r="E303" t="s">
+        <v>60</v>
+      </c>
+      <c r="F303" t="s">
+        <v>45</v>
+      </c>
+      <c r="G303">
+        <v>30</v>
+      </c>
+      <c r="H303" t="s">
+        <v>17</v>
+      </c>
+      <c r="I303" t="s">
+        <v>54</v>
+      </c>
+      <c r="J303" t="s">
+        <v>897</v>
+      </c>
+      <c r="K303" t="s">
+        <v>25</v>
+      </c>
+      <c r="L303" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M303" t="s">
+        <v>42</v>
+      </c>
+      <c r="N303" t="s">
+        <v>898</v>
+      </c>
+      <c r="O303" t="s">
+        <v>172</v>
+      </c>
+      <c r="P303" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>868</v>
+      </c>
+      <c r="B304" t="s">
+        <v>17</v>
+      </c>
+      <c r="C304" t="s">
+        <v>38</v>
+      </c>
+      <c r="D304" t="s">
+        <v>899</v>
+      </c>
+      <c r="E304" t="s">
+        <v>60</v>
+      </c>
+      <c r="F304" t="s">
+        <v>45</v>
+      </c>
+      <c r="G304">
+        <v>31</v>
+      </c>
+      <c r="H304" t="s">
+        <v>900</v>
+      </c>
+      <c r="I304" t="s">
+        <v>158</v>
+      </c>
+      <c r="J304" t="s">
+        <v>901</v>
+      </c>
+      <c r="K304" t="s">
+        <v>25</v>
+      </c>
+      <c r="L304" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M304" t="s">
+        <v>42</v>
+      </c>
+      <c r="N304" t="s">
+        <v>902</v>
+      </c>
+      <c r="O304" t="s">
+        <v>25</v>
+      </c>
+      <c r="P304" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>868</v>
+      </c>
+      <c r="B305" t="s">
+        <v>17</v>
+      </c>
+      <c r="C305" t="s">
+        <v>38</v>
+      </c>
+      <c r="D305" t="s">
+        <v>903</v>
+      </c>
+      <c r="E305" t="s">
+        <v>60</v>
+      </c>
+      <c r="F305" t="s">
+        <v>21</v>
+      </c>
+      <c r="G305">
+        <v>30</v>
+      </c>
+      <c r="H305" t="s">
+        <v>317</v>
+      </c>
+      <c r="I305" t="s">
+        <v>54</v>
+      </c>
+      <c r="J305" t="s">
+        <v>904</v>
+      </c>
+      <c r="K305" t="s">
+        <v>25</v>
+      </c>
+      <c r="L305" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M305" t="s">
+        <v>17</v>
+      </c>
+      <c r="N305" t="s">
+        <v>68</v>
+      </c>
+      <c r="O305" t="s">
+        <v>28</v>
+      </c>
+      <c r="P305" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>868</v>
+      </c>
+      <c r="B306" t="s">
+        <v>17</v>
+      </c>
+      <c r="C306" t="s">
+        <v>18</v>
+      </c>
+      <c r="D306" t="s">
+        <v>905</v>
+      </c>
+      <c r="E306" t="s">
+        <v>60</v>
+      </c>
+      <c r="F306" t="s">
+        <v>21</v>
+      </c>
+      <c r="G306">
+        <v>47</v>
+      </c>
+      <c r="H306" t="s">
+        <v>46</v>
+      </c>
+      <c r="I306" t="s">
+        <v>33</v>
+      </c>
+      <c r="J306" t="s">
+        <v>906</v>
+      </c>
+      <c r="K306" t="s">
+        <v>25</v>
+      </c>
+      <c r="L306" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M306" t="s">
+        <v>17</v>
+      </c>
+      <c r="N306" t="s">
+        <v>68</v>
+      </c>
+      <c r="O306" t="s">
+        <v>28</v>
+      </c>
+      <c r="P306" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="307" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>868</v>
+      </c>
+      <c r="B307" t="s">
+        <v>407</v>
+      </c>
+      <c r="C307" t="s">
+        <v>18</v>
+      </c>
+      <c r="D307" t="s">
+        <v>907</v>
+      </c>
+      <c r="E307" t="s">
+        <v>60</v>
+      </c>
+      <c r="F307" t="s">
+        <v>45</v>
+      </c>
+      <c r="G307">
+        <v>21</v>
+      </c>
+      <c r="H307" t="s">
+        <v>46</v>
+      </c>
+      <c r="I307" t="s">
+        <v>256</v>
+      </c>
+      <c r="J307" t="s">
+        <v>908</v>
+      </c>
+      <c r="K307" t="s">
+        <v>25</v>
+      </c>
+      <c r="L307" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M307" t="s">
+        <v>17</v>
+      </c>
+      <c r="N307" t="s">
+        <v>68</v>
+      </c>
+      <c r="O307" t="s">
+        <v>28</v>
+      </c>
+      <c r="P307" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>868</v>
+      </c>
+      <c r="B308" t="s">
+        <v>17</v>
+      </c>
+      <c r="C308" t="s">
+        <v>38</v>
+      </c>
+      <c r="D308" t="s">
+        <v>909</v>
+      </c>
+      <c r="E308" t="s">
+        <v>60</v>
+      </c>
+      <c r="F308" t="s">
+        <v>45</v>
+      </c>
+      <c r="G308">
+        <v>28</v>
+      </c>
+      <c r="H308" t="s">
+        <v>40</v>
+      </c>
+      <c r="I308" t="s">
+        <v>89</v>
+      </c>
+      <c r="J308" t="s">
+        <v>910</v>
+      </c>
+      <c r="K308" t="s">
+        <v>25</v>
+      </c>
+      <c r="L308" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M308" t="s">
+        <v>42</v>
+      </c>
+      <c r="N308" t="s">
+        <v>68</v>
+      </c>
+      <c r="O308" t="s">
+        <v>28</v>
+      </c>
+      <c r="P308" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>868</v>
+      </c>
+      <c r="B309" t="s">
+        <v>407</v>
+      </c>
+      <c r="C309" t="s">
+        <v>38</v>
+      </c>
+      <c r="D309" t="s">
+        <v>911</v>
+      </c>
+      <c r="E309" t="s">
+        <v>60</v>
+      </c>
+      <c r="F309" t="s">
+        <v>31</v>
+      </c>
+      <c r="G309">
+        <v>48</v>
+      </c>
+      <c r="H309" t="s">
+        <v>40</v>
+      </c>
+      <c r="I309" t="s">
+        <v>54</v>
+      </c>
+      <c r="J309" t="s">
+        <v>912</v>
+      </c>
+      <c r="K309" t="s">
+        <v>25</v>
+      </c>
+      <c r="L309" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M309" t="s">
+        <v>42</v>
+      </c>
+      <c r="N309" t="s">
+        <v>913</v>
+      </c>
+      <c r="O309" t="s">
+        <v>172</v>
+      </c>
+      <c r="P309" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="310" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>868</v>
+      </c>
+      <c r="B310" t="s">
+        <v>17</v>
+      </c>
+      <c r="C310" t="s">
+        <v>18</v>
+      </c>
+      <c r="D310" t="s">
+        <v>914</v>
+      </c>
+      <c r="E310" t="s">
+        <v>60</v>
+      </c>
+      <c r="F310" t="s">
+        <v>31</v>
+      </c>
+      <c r="G310">
+        <v>26</v>
+      </c>
+      <c r="H310" t="s">
+        <v>57</v>
+      </c>
+      <c r="I310" t="s">
+        <v>915</v>
+      </c>
+      <c r="J310" t="s">
+        <v>916</v>
+      </c>
+      <c r="K310" t="s">
+        <v>25</v>
+      </c>
+      <c r="L310" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="M310" t="s">
+        <v>280</v>
+      </c>
+      <c r="N310" t="s">
+        <v>895</v>
+      </c>
+      <c r="O310" t="s">
+        <v>25</v>
+      </c>
+      <c r="P310" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="311" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>868</v>
+      </c>
+      <c r="B311" t="s">
+        <v>17</v>
+      </c>
+      <c r="C311" t="s">
+        <v>38</v>
+      </c>
+      <c r="D311" t="s">
+        <v>917</v>
+      </c>
+      <c r="E311" t="s">
+        <v>60</v>
+      </c>
+      <c r="F311" t="s">
+        <v>31</v>
+      </c>
+      <c r="G311">
+        <v>40</v>
+      </c>
+      <c r="H311" t="s">
+        <v>321</v>
+      </c>
+      <c r="I311" t="s">
+        <v>54</v>
+      </c>
+      <c r="J311" t="s">
+        <v>918</v>
+      </c>
+      <c r="K311" t="s">
+        <v>25</v>
+      </c>
+      <c r="L311" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M311" t="s">
+        <v>42</v>
+      </c>
+      <c r="N311" t="s">
+        <v>895</v>
+      </c>
+      <c r="O311" t="s">
+        <v>25</v>
+      </c>
+      <c r="P311" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="312" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M312" s="1"/>
       <c r="N312"/>
     </row>
-    <row r="313" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M313" s="1"/>
       <c r="N313"/>
     </row>
-    <row r="314" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M314" s="1"/>
       <c r="N314"/>
     </row>
-    <row r="315" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M315" s="1"/>
       <c r="N315"/>
     </row>
-    <row r="316" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M316" s="1"/>
       <c r="N316"/>
     </row>
-    <row r="317" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M317" s="1"/>
       <c r="N317"/>
     </row>
-    <row r="318" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M318" s="1"/>
       <c r="N318"/>
     </row>
-    <row r="319" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M319" s="1"/>
       <c r="N319"/>
     </row>
-    <row r="320" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.3">
       <c r="M320" s="1"/>
       <c r="N320"/>
     </row>
